--- a/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
@@ -20,12 +20,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'사용자'!$A$4:$N$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'입력'!$A$4:$N$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'분석'!$A$4:$N$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'챗봇'!$A$4:$N$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'입력'!$A$4:$N$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'분석'!$A$4:$N$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'챗봇'!$A$4:$N$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'실천·보상'!$A$4:$N$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'마스터'!$A$4:$N$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'FHIR 대응'!$A$5:$H$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'FHIR 대응'!$A$5:$H$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -876,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -910,6 +910,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
@@ -1725,44 +1726,40 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>ocr_jobs</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="inlineStr">
-        <is>
-          <t>queued → requested / running → in-progress / done → completed / failed → failed</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H26" s="15" t="inlineStr">
-        <is>
-          <t>v1.2 · OCR 비동기 작업</t>
+      <c r="B26" s="37" t="inlineStr">
+        <is>
+          <t>prescriptions</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>content_key</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="n"/>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>FHIR 외</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>같은 처방전 판별용 내부 값</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1771,7 @@
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>prescription_diseases</t>
+          <t>ocr_jobs</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
@@ -1784,17 +1781,17 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="F27" s="15" t="inlineStr">
         <is>
-          <t>처방전 질병분류기호 1개 = Condition 1개</t>
+          <t>queued → requested / running → in-progress / done → completed / failed → failed</t>
         </is>
       </c>
       <c r="G27" s="16" t="inlineStr">
@@ -1804,7 +1801,7 @@
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>MedicationRequest.reasonReference로 연결</t>
+          <t>v1.2 · OCR 비동기 작업</t>
         </is>
       </c>
     </row>
@@ -1814,39 +1811,35 @@
           <t>입력</t>
         </is>
       </c>
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t>prescription_diseases</t>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>ocr_jobs</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>disease_code</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>Condition</t>
+          <t>duplicates</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>Condition.code.coding</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="inlineStr">
-        <is>
-          <t>system = KCD (코드 시스템 URI 팀 정의 필요)</t>
-        </is>
-      </c>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="n"/>
       <c r="G28" s="16" t="inlineStr">
         <is>
-          <t>변환</t>
+          <t>확장</t>
         </is>
       </c>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>KCD는 ICD-10 기반이라 ICD-10 코드 병기 가능</t>
+          <t>중복 사진 기록은 내부 처리 정보</t>
         </is>
       </c>
     </row>
@@ -1856,29 +1849,29 @@
           <t>입력</t>
         </is>
       </c>
-      <c r="B29" s="33" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>prescription_diseases</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>is_main</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>Encounter</t>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>Condition</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>Encounter.diagnosis.rank</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
-          <t>주상병 → rank 1</t>
+          <t>처방전 질병분류기호 1개 = Condition 1개</t>
         </is>
       </c>
       <c r="G29" s="16" t="inlineStr">
@@ -1888,47 +1881,51 @@
       </c>
       <c r="H29" s="15" t="inlineStr">
         <is>
-          <t>진료(Encounter) 정보가 없으면 extension</t>
+          <t>MedicationRequest.reasonReference로 연결</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B30" s="38" t="inlineStr">
-        <is>
-          <t>prescription_items</t>
-        </is>
-      </c>
-      <c r="C30" s="32" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D30" s="39" t="inlineStr">
-        <is>
-          <t>MedicationRequest</t>
-        </is>
-      </c>
-      <c r="E30" s="32" t="inlineStr">
-        <is>
-          <t>MedicationRequest</t>
-        </is>
-      </c>
-      <c r="F30" s="32" t="inlineStr">
-        <is>
-          <t>약 1줄 = MedicationRequest 1개</t>
-        </is>
-      </c>
-      <c r="G30" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H30" s="32" t="inlineStr"/>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>prescription_diseases</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>disease_code</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>Condition.code.coding</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>system = KCD (코드 시스템 URI 팀 정의 필요)</t>
+        </is>
+      </c>
+      <c r="G30" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="inlineStr">
+        <is>
+          <t>KCD는 ICD-10 기반이라 ICD-10 코드 병기 가능</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
@@ -1938,27 +1935,27 @@
       </c>
       <c r="B31" s="33" t="inlineStr">
         <is>
-          <t>prescription_items</t>
+          <t>prescription_diseases</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>edi_code</t>
+          <t>is_main</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>MedicationRequest</t>
+          <t>Encounter</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>MedicationRequest.medicationCodeableConcept.coding</t>
+          <t>Encounter.diagnosis.rank</t>
         </is>
       </c>
       <c r="F31" s="15" t="inlineStr">
         <is>
-          <t>system = 심평원 EDI 제품코드</t>
+          <t>주상병 → rank 1</t>
         </is>
       </c>
       <c r="G31" s="16" t="inlineStr">
@@ -1966,7 +1963,11 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H31" s="15" t="inlineStr"/>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>진료(Encounter) 정보가 없으면 extension</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="30" t="inlineStr">
@@ -1974,151 +1975,151 @@
           <t>입력</t>
         </is>
       </c>
-      <c r="B32" s="31" t="inlineStr">
+      <c r="B32" s="38" t="inlineStr">
         <is>
           <t>prescription_items</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
         <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D32" s="39" t="inlineStr">
+        <is>
+          <t>MedicationRequest</t>
+        </is>
+      </c>
+      <c r="E32" s="32" t="inlineStr">
+        <is>
+          <t>MedicationRequest</t>
+        </is>
+      </c>
+      <c r="F32" s="32" t="inlineStr">
+        <is>
+          <t>약 1줄 = MedicationRequest 1개</t>
+        </is>
+      </c>
+      <c r="G32" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H32" s="32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B33" s="33" t="inlineStr">
+        <is>
+          <t>prescription_items</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>edi_code</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>MedicationRequest</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>MedicationRequest.medicationCodeableConcept.coding</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>system = 심평원 EDI 제품코드</t>
+        </is>
+      </c>
+      <c r="G33" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="inlineStr">
+        <is>
+          <t>prescription_items</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="inlineStr">
+        <is>
           <t>raw_name</t>
         </is>
       </c>
-      <c r="D32" s="32" t="inlineStr">
+      <c r="D34" s="32" t="inlineStr">
         <is>
           <t>MedicationRequest</t>
         </is>
       </c>
-      <c r="E32" s="32" t="inlineStr">
+      <c r="E34" s="32" t="inlineStr">
         <is>
           <t>MedicationRequest.medicationCodeableConcept.text</t>
         </is>
       </c>
-      <c r="F32" s="32" t="inlineStr">
+      <c r="F34" s="32" t="inlineStr">
         <is>
           <t>OCR이 읽은 원문 약품명</t>
         </is>
       </c>
-      <c r="G32" s="30" t="inlineStr">
+      <c r="G34" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H32" s="32" t="inlineStr">
+      <c r="H34" s="32" t="inlineStr">
         <is>
           <t>매칭 실패해도 text는 남음</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="30" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="30" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B33" s="31" t="inlineStr">
+      <c r="B35" s="31" t="inlineStr">
         <is>
           <t>prescription_items</t>
         </is>
       </c>
-      <c r="C33" s="32" t="inlineStr">
+      <c r="C35" s="32" t="inlineStr">
         <is>
           <t>dose_per_time</t>
         </is>
       </c>
-      <c r="D33" s="32" t="inlineStr">
+      <c r="D35" s="32" t="inlineStr">
         <is>
           <t>MedicationRequest</t>
         </is>
       </c>
-      <c r="E33" s="32" t="inlineStr">
+      <c r="E35" s="32" t="inlineStr">
         <is>
           <t>MedicationRequest.dosageInstruction.doseAndRate.doseQuantity</t>
         </is>
       </c>
-      <c r="F33" s="32" t="inlineStr"/>
-      <c r="G33" s="30" t="inlineStr">
+      <c r="F35" s="32" t="inlineStr"/>
+      <c r="G35" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H33" s="32" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="B34" s="33" t="inlineStr">
-        <is>
-          <t>prescription_items</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>times_per_day</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>MedicationRequest</t>
-        </is>
-      </c>
-      <c r="E34" s="15" t="inlineStr">
-        <is>
-          <t>MedicationRequest.dosageInstruction.timing.repeat.frequency</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="inlineStr">
-        <is>
-          <t>period = 1, periodUnit = d</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H34" s="15" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="B35" s="33" t="inlineStr">
-        <is>
-          <t>prescription_items</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="inlineStr">
-        <is>
-          <t>total_days</t>
-        </is>
-      </c>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>MedicationRequest</t>
-        </is>
-      </c>
-      <c r="E35" s="15" t="inlineStr">
-        <is>
-          <t>MedicationRequest.dispenseRequest.expectedSupplyDuration</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="inlineStr">
-        <is>
-          <t>단위 d(일)</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H35" s="15" t="inlineStr"/>
+      <c r="H35" s="32" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
@@ -2133,7 +2134,7 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>times_per_day</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
@@ -2143,12 +2144,12 @@
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>MedicationRequest.dosageInstruction.timing.repeat.when</t>
+          <t>MedicationRequest.dosageInstruction.timing.repeat.frequency</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>아침 식후 → PCM, 저녁 식후 → PCV, 취침 전 → HS 등 + text 원문</t>
+          <t>period = 1, periodUnit = d</t>
         </is>
       </c>
       <c r="G36" s="16" t="inlineStr">
@@ -2171,106 +2172,106 @@
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
+          <t>total_days</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>MedicationRequest</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>MedicationRequest.dispenseRequest.expectedSupplyDuration</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>단위 d(일)</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B38" s="33" t="inlineStr">
+        <is>
+          <t>prescription_items</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>MedicationRequest</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>MedicationRequest.dosageInstruction.timing.repeat.when</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>아침 식후 → PCM, 저녁 식후 → PCV, 취침 전 → HS 등 + text 원문</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B39" s="33" t="inlineStr">
+        <is>
+          <t>prescription_items</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
           <t>guidance</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D39" s="15" t="inlineStr">
         <is>
           <t>MedicationRequest</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr">
+      <c r="E39" s="15" t="inlineStr">
         <is>
           <t>MedicationRequest.dosageInstruction.patientInstruction</t>
         </is>
       </c>
-      <c r="F37" s="15" t="inlineStr">
+      <c r="F39" s="15" t="inlineStr">
         <is>
           <t>문장 목록 → 줄바꿈으로 이어 붙인 text</t>
         </is>
       </c>
-      <c r="G37" s="16" t="inlineStr">
+      <c r="G39" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H37" s="15" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="22" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="B38" s="37" t="inlineStr">
-        <is>
-          <t>prescription_items</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="inlineStr">
-        <is>
-          <t>match_status · match_score</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E38" s="21" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="F38" s="21" t="inlineStr"/>
-      <c r="G38" s="22" t="inlineStr">
-        <is>
-          <t>확장</t>
-        </is>
-      </c>
-      <c r="H38" s="21" t="inlineStr">
-        <is>
-          <t>약품 매칭 상태는 내부 처리 정보</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="34" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="B39" s="40" t="inlineStr">
-        <is>
-          <t>prescription_item_candidates</t>
-        </is>
-      </c>
-      <c r="C39" s="36" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E39" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F39" s="36" t="inlineStr"/>
-      <c r="G39" s="34" t="inlineStr">
-        <is>
-          <t>FHIR 외</t>
-        </is>
-      </c>
-      <c r="H39" s="36" t="inlineStr">
-        <is>
-          <t>약품 매칭 후보 (내부 처리)</t>
-        </is>
-      </c>
+      <c r="H39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
@@ -2278,191 +2279,195 @@
           <t>입력</t>
         </is>
       </c>
-      <c r="B40" s="19" t="inlineStr">
+      <c r="B40" s="33" t="inlineStr">
+        <is>
+          <t>prescription_items</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>suggested_by</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="16" t="inlineStr">
+        <is>
+          <t>FHIR 외</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="inlineStr">
+        <is>
+          <t>화면 표시용 추천 출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B41" s="37" t="inlineStr">
+        <is>
+          <t>prescription_items</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>match_status · match_score</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr"/>
+      <c r="G41" s="22" t="inlineStr">
+        <is>
+          <t>확장</t>
+        </is>
+      </c>
+      <c r="H41" s="21" t="inlineStr">
+        <is>
+          <t>약품 매칭 상태는 내부 처리 정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="34" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B42" s="40" t="inlineStr">
+        <is>
+          <t>prescription_item_candidates</t>
+        </is>
+      </c>
+      <c r="C42" s="36" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="36" t="inlineStr"/>
+      <c r="G42" s="34" t="inlineStr">
+        <is>
+          <t>FHIR 외</t>
+        </is>
+      </c>
+      <c r="H42" s="36" t="inlineStr">
+        <is>
+          <t>약품 매칭 후보 (내부 처리)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
         <is>
           <t>health_checkups · checkup_results</t>
         </is>
       </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D40" s="14" t="inlineStr">
+      <c r="D43" s="14" t="inlineStr">
         <is>
           <t>DiagnosticReport · Observation</t>
         </is>
       </c>
-      <c r="E40" s="15" t="inlineStr">
+      <c r="E43" s="15" t="inlineStr">
         <is>
           <t>Observation.code / valueQuantity</t>
         </is>
       </c>
-      <c r="F40" s="15" t="inlineStr">
+      <c r="F43" s="15" t="inlineStr">
         <is>
           <t>검진 항목 코드 → Observation.code</t>
         </is>
       </c>
-      <c r="G40" s="16" t="inlineStr">
+      <c r="G43" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H40" s="15" t="inlineStr">
+      <c r="H43" s="15" t="inlineStr">
         <is>
           <t>보류 (REQ-015)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B41" s="19" t="inlineStr">
+      <c r="B44" s="19" t="inlineStr">
         <is>
           <t>analyses</t>
         </is>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C44" s="15" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D41" s="14" t="inlineStr">
+      <c r="D44" s="14" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="E41" s="15" t="inlineStr">
+      <c r="E44" s="15" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="F41" s="15" t="inlineStr">
+      <c r="F44" s="15" t="inlineStr">
         <is>
           <t>분석 작업 1건 = Task 1개</t>
         </is>
       </c>
-      <c r="G41" s="16" t="inlineStr">
+      <c r="G44" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H41" s="15" t="inlineStr">
+      <c r="H44" s="15" t="inlineStr">
         <is>
           <t>비동기 작업 상태를 Task로 표현</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B42" s="33" t="inlineStr">
-        <is>
-          <t>analyses</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="D42" s="15" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="E42" s="15" t="inlineStr">
-        <is>
-          <t>Task.status</t>
-        </is>
-      </c>
-      <c r="F42" s="15" t="inlineStr">
-        <is>
-          <t>queued → requested / running → in-progress / done → completed / failed → failed</t>
-        </is>
-      </c>
-      <c r="G42" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H42" s="15" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="22" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B43" s="37" t="inlineStr">
-        <is>
-          <t>analyses</t>
-        </is>
-      </c>
-      <c r="C43" s="21" t="inlineStr">
-        <is>
-          <t>current_step · failed_step · retry_count · error_code</t>
-        </is>
-      </c>
-      <c r="D43" s="21" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="E43" s="21" t="inlineStr">
-        <is>
-          <t>Task.businessStatus · Task.statusReason</t>
-        </is>
-      </c>
-      <c r="F43" s="21" t="inlineStr"/>
-      <c r="G43" s="22" t="inlineStr">
-        <is>
-          <t>확장</t>
-        </is>
-      </c>
-      <c r="H43" s="21" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="34" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B44" s="35" t="inlineStr">
-        <is>
-          <t>analyses</t>
-        </is>
-      </c>
-      <c r="C44" s="36" t="inlineStr">
-        <is>
-          <t>user_birth_year</t>
-        </is>
-      </c>
-      <c r="D44" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E44" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F44" s="36" t="inlineStr"/>
-      <c r="G44" s="34" t="inlineStr">
-        <is>
-          <t>FHIR 외</t>
-        </is>
-      </c>
-      <c r="H44" s="36" t="inlineStr">
-        <is>
-          <t>분석 시점 스냅샷 (내부)</t>
         </is>
       </c>
     </row>
@@ -2472,157 +2477,149 @@
           <t>분석</t>
         </is>
       </c>
-      <c r="B45" s="19" t="inlineStr">
+      <c r="B45" s="33" t="inlineStr">
+        <is>
+          <t>analyses</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>Task.status</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>queued → requested / running → in-progress / done → completed / failed → failed</t>
+        </is>
+      </c>
+      <c r="G45" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B46" s="37" t="inlineStr">
+        <is>
+          <t>analyses</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>current_step · failed_step · retry_count · error_code</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="E46" s="21" t="inlineStr">
+        <is>
+          <t>Task.businessStatus · Task.statusReason</t>
+        </is>
+      </c>
+      <c r="F46" s="21" t="inlineStr"/>
+      <c r="G46" s="22" t="inlineStr">
+        <is>
+          <t>확장</t>
+        </is>
+      </c>
+      <c r="H46" s="21" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="34" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B47" s="35" t="inlineStr">
+        <is>
+          <t>analyses</t>
+        </is>
+      </c>
+      <c r="C47" s="36" t="inlineStr">
+        <is>
+          <t>user_birth_year</t>
+        </is>
+      </c>
+      <c r="D47" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="36" t="inlineStr"/>
+      <c r="G47" s="34" t="inlineStr">
+        <is>
+          <t>FHIR 외</t>
+        </is>
+      </c>
+      <c r="H47" s="36" t="inlineStr">
+        <is>
+          <t>분석 시점 스냅샷 (내부)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
         <is>
           <t>analysis_prescriptions</t>
         </is>
       </c>
-      <c r="C45" s="15" t="inlineStr">
+      <c r="C48" s="15" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D45" s="14" t="inlineStr">
+      <c r="D48" s="14" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="E45" s="15" t="inlineStr">
+      <c r="E48" s="15" t="inlineStr">
         <is>
           <t>Task.input</t>
         </is>
       </c>
-      <c r="F45" s="15" t="inlineStr">
+      <c r="F48" s="15" t="inlineStr">
         <is>
           <t>valueReference = MedicationRequest</t>
         </is>
       </c>
-      <c r="G45" s="16" t="inlineStr">
+      <c r="G48" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H45" s="15" t="inlineStr">
+      <c r="H48" s="15" t="inlineStr">
         <is>
           <t>분석에 넣은 처방 목록</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="16" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B46" s="19" t="inlineStr">
-        <is>
-          <t>analysis_diseases</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D46" s="14" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E46" s="15" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="F46" s="15" t="inlineStr"/>
-      <c r="G46" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H46" s="15" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B47" s="33" t="inlineStr">
-        <is>
-          <t>analysis_diseases</t>
-        </is>
-      </c>
-      <c r="C47" s="15" t="inlineStr">
-        <is>
-          <t>origin</t>
-        </is>
-      </c>
-      <c r="D47" s="15" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E47" s="15" t="inlineStr">
-        <is>
-          <t>Condition.asserter</t>
-        </is>
-      </c>
-      <c r="F47" s="15" t="inlineStr">
-        <is>
-          <t>prescription → 처방전에서 옴 / user → asserter = Patient (직접 선택)</t>
-        </is>
-      </c>
-      <c r="G47" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H47" s="15" t="inlineStr">
-        <is>
-          <t>누가 주장한 질환인지 구분</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="30" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B48" s="38" t="inlineStr">
-        <is>
-          <t>analysis_warnings</t>
-        </is>
-      </c>
-      <c r="C48" s="32" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D48" s="39" t="inlineStr">
-        <is>
-          <t>DetectedIssue</t>
-        </is>
-      </c>
-      <c r="E48" s="32" t="inlineStr">
-        <is>
-          <t>DetectedIssue</t>
-        </is>
-      </c>
-      <c r="F48" s="32" t="inlineStr">
-        <is>
-          <t>경고 1건 = DetectedIssue 1개</t>
-        </is>
-      </c>
-      <c r="G48" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H48" s="32" t="inlineStr">
-        <is>
-          <t>FHIR에 "약물 문제 감지" 전용 리소스가 있음 — 가장 잘 맞는 부분</t>
         </is>
       </c>
     </row>
@@ -2632,41 +2629,33 @@
           <t>분석</t>
         </is>
       </c>
-      <c r="B49" s="33" t="inlineStr">
-        <is>
-          <t>analysis_warnings</t>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>analysis_diseases</t>
         </is>
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>warning_type</t>
-        </is>
-      </c>
-      <c r="D49" s="15" t="inlineStr">
-        <is>
-          <t>DetectedIssue</t>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>Condition</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>DetectedIssue.code</t>
-        </is>
-      </c>
-      <c r="F49" s="15" t="inlineStr">
-        <is>
-          <t>interaction → DRG / duplicate_* → DUPTHPY / dose_exceed → DOSEHIGH / age → AGE / elderly · pregnancy · polypharmacy → 자체 코드</t>
-        </is>
-      </c>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="inlineStr"/>
       <c r="G49" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H49" s="15" t="inlineStr">
-        <is>
-          <t>HL7 v3 ActCode 후보 — 구현 시 코드 확인 필요</t>
-        </is>
-      </c>
+      <c r="H49" s="15" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
@@ -2676,27 +2665,27 @@
       </c>
       <c r="B50" s="33" t="inlineStr">
         <is>
-          <t>analysis_warnings</t>
+          <t>analysis_diseases</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>origin</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>DetectedIssue</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>DetectedIssue.severity</t>
+          <t>Condition.asserter</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
         <is>
-          <t>danger → high / caution → moderate / info → low</t>
+          <t>prescription → 처방전에서 옴 / user → asserter = Patient (직접 선택)</t>
         </is>
       </c>
       <c r="G50" s="16" t="inlineStr">
@@ -2704,7 +2693,11 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H50" s="15" t="inlineStr"/>
+      <c r="H50" s="15" t="inlineStr">
+        <is>
+          <t>누가 주장한 질환인지 구분</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="30" t="inlineStr">
@@ -2712,29 +2705,29 @@
           <t>분석</t>
         </is>
       </c>
-      <c r="B51" s="31" t="inlineStr">
+      <c r="B51" s="38" t="inlineStr">
         <is>
           <t>analysis_warnings</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
         <is>
-          <t>item_id_a · item_id_b</t>
-        </is>
-      </c>
-      <c r="D51" s="32" t="inlineStr">
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D51" s="39" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
       <c r="E51" s="32" t="inlineStr">
         <is>
-          <t>DetectedIssue.implicated</t>
+          <t>DetectedIssue</t>
         </is>
       </c>
       <c r="F51" s="32" t="inlineStr">
         <is>
-          <t>Reference(MedicationRequest) 2개</t>
+          <t>경고 1건 = DetectedIssue 1개</t>
         </is>
       </c>
       <c r="G51" s="30" t="inlineStr">
@@ -2742,45 +2735,53 @@
           <t>일치</t>
         </is>
       </c>
-      <c r="H51" s="32" t="inlineStr"/>
+      <c r="H51" s="32" t="inlineStr">
+        <is>
+          <t>FHIR에 "약물 문제 감지" 전용 리소스가 있음 — 가장 잘 맞는 부분</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="30" t="inlineStr">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B52" s="31" t="inlineStr">
+      <c r="B52" s="33" t="inlineStr">
         <is>
           <t>analysis_warnings</t>
         </is>
       </c>
-      <c r="C52" s="32" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
-      <c r="D52" s="32" t="inlineStr">
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>warning_type</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
-      <c r="E52" s="32" t="inlineStr">
-        <is>
-          <t>DetectedIssue.detail</t>
-        </is>
-      </c>
-      <c r="F52" s="32" t="inlineStr">
-        <is>
-          <t>DUR 금기 사유 원문</t>
-        </is>
-      </c>
-      <c r="G52" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H52" s="32" t="inlineStr"/>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>DetectedIssue.code</t>
+        </is>
+      </c>
+      <c r="F52" s="15" t="inlineStr">
+        <is>
+          <t>interaction → DRG / duplicate_* → DUPTHPY / dose_exceed → DOSEHIGH / age → AGE / elderly · pregnancy · polypharmacy → 자체 코드</t>
+        </is>
+      </c>
+      <c r="G52" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="inlineStr">
+        <is>
+          <t>HL7 v3 ActCode 후보 — 구현 시 코드 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
@@ -2795,432 +2796,444 @@
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>DetectedIssue</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>DetectedIssue.severity</t>
+        </is>
+      </c>
+      <c r="F53" s="15" t="inlineStr">
+        <is>
+          <t>danger → high / caution → moderate / info → low</t>
+        </is>
+      </c>
+      <c r="G53" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="30" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B54" s="31" t="inlineStr">
+        <is>
+          <t>analysis_warnings</t>
+        </is>
+      </c>
+      <c r="C54" s="32" t="inlineStr">
+        <is>
+          <t>item_id_a · item_id_b</t>
+        </is>
+      </c>
+      <c r="D54" s="32" t="inlineStr">
+        <is>
+          <t>DetectedIssue</t>
+        </is>
+      </c>
+      <c r="E54" s="32" t="inlineStr">
+        <is>
+          <t>DetectedIssue.implicated</t>
+        </is>
+      </c>
+      <c r="F54" s="32" t="inlineStr">
+        <is>
+          <t>Reference(MedicationRequest) 2개</t>
+        </is>
+      </c>
+      <c r="G54" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H54" s="32" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="30" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B55" s="31" t="inlineStr">
+        <is>
+          <t>analysis_warnings</t>
+        </is>
+      </c>
+      <c r="C55" s="32" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="D55" s="32" t="inlineStr">
+        <is>
+          <t>DetectedIssue</t>
+        </is>
+      </c>
+      <c r="E55" s="32" t="inlineStr">
+        <is>
+          <t>DetectedIssue.detail</t>
+        </is>
+      </c>
+      <c r="F55" s="32" t="inlineStr">
+        <is>
+          <t>DUR 금기 사유 원문</t>
+        </is>
+      </c>
+      <c r="G55" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H55" s="32" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B56" s="33" t="inlineStr">
+        <is>
+          <t>analysis_warnings</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
           <t>source · notice_date</t>
         </is>
       </c>
-      <c r="D53" s="15" t="inlineStr">
+      <c r="D56" s="15" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
-      <c r="E53" s="15" t="inlineStr">
+      <c r="E56" s="15" t="inlineStr">
         <is>
           <t>DetectedIssue.reference</t>
         </is>
       </c>
-      <c r="F53" s="15" t="inlineStr">
+      <c r="F56" s="15" t="inlineStr">
         <is>
           <t>식약처 고시 출처</t>
         </is>
       </c>
-      <c r="G53" s="16" t="inlineStr">
+      <c r="G56" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H53" s="15" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="22" t="inlineStr">
+      <c r="H56" s="15" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B54" s="37" t="inlineStr">
+      <c r="B57" s="37" t="inlineStr">
         <is>
           <t>analysis_warnings</t>
         </is>
       </c>
-      <c r="C54" s="21" t="inlineStr">
+      <c r="C57" s="21" t="inlineStr">
         <is>
           <t>summary · daily_total · max_daily</t>
         </is>
       </c>
-      <c r="D54" s="21" t="inlineStr">
+      <c r="D57" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E54" s="21" t="inlineStr">
+      <c r="E57" s="21" t="inlineStr">
         <is>
           <t>extension</t>
         </is>
       </c>
-      <c r="F54" s="21" t="inlineStr"/>
-      <c r="G54" s="22" t="inlineStr">
+      <c r="F57" s="21" t="inlineStr"/>
+      <c r="G57" s="22" t="inlineStr">
         <is>
           <t>확장</t>
         </is>
       </c>
-      <c r="H54" s="21" t="inlineStr">
+      <c r="H57" s="21" t="inlineStr">
         <is>
           <t>화면 문장 · 용량 계산값</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="34" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B55" s="40" t="inlineStr">
+      <c r="B58" s="37" t="inlineStr">
+        <is>
+          <t>analysis_warnings</t>
+        </is>
+      </c>
+      <c r="C58" s="21" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="D58" s="21" t="inlineStr">
+        <is>
+          <t>DetectedIssue</t>
+        </is>
+      </c>
+      <c r="E58" s="21" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="F58" s="21" t="n"/>
+      <c r="G58" s="22" t="inlineStr">
+        <is>
+          <t>확장</t>
+        </is>
+      </c>
+      <c r="H58" s="21" t="inlineStr">
+        <is>
+          <t>3개 이상 경고의 전체 약 목록은 표준 요소가 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="34" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B59" s="40" t="inlineStr">
         <is>
           <t>guides</t>
         </is>
       </c>
-      <c r="C55" s="36" t="inlineStr">
+      <c r="C59" s="36" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D55" s="17" t="inlineStr">
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E55" s="36" t="inlineStr">
+      <c r="E59" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F55" s="36" t="inlineStr"/>
-      <c r="G55" s="34" t="inlineStr">
+      <c r="F59" s="36" t="inlineStr"/>
+      <c r="G59" s="34" t="inlineStr">
         <is>
           <t>FHIR 외</t>
         </is>
       </c>
-      <c r="H55" s="36" t="inlineStr">
+      <c r="H59" s="36" t="inlineStr">
         <is>
           <t>AI 생성 안내문 (의료 기록 아님). 필요하면 DocumentReference로 보관</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="34" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="34" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B56" s="40" t="inlineStr">
+      <c r="B60" s="40" t="inlineStr">
         <is>
           <t>feedbacks</t>
         </is>
       </c>
-      <c r="C56" s="36" t="inlineStr">
+      <c r="C60" s="36" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D56" s="17" t="inlineStr">
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E56" s="36" t="inlineStr">
+      <c r="E60" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F56" s="36" t="inlineStr"/>
-      <c r="G56" s="34" t="inlineStr">
+      <c r="F60" s="36" t="inlineStr"/>
+      <c r="G60" s="34" t="inlineStr">
         <is>
           <t>FHIR 외</t>
         </is>
       </c>
-      <c r="H56" s="36" t="inlineStr">
+      <c r="H60" s="36" t="inlineStr">
         <is>
           <t>서비스 피드백</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="34" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="34" t="inlineStr">
         <is>
           <t>챗봇</t>
         </is>
       </c>
-      <c r="B57" s="40" t="inlineStr">
+      <c r="B61" s="40" t="inlineStr">
         <is>
           <t>chat_sessions</t>
         </is>
       </c>
-      <c r="C57" s="36" t="inlineStr">
+      <c r="C61" s="36" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D57" s="17" t="inlineStr">
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E57" s="36" t="inlineStr">
+      <c r="E61" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F57" s="36" t="inlineStr"/>
-      <c r="G57" s="34" t="inlineStr">
+      <c r="F61" s="36" t="inlineStr"/>
+      <c r="G61" s="34" t="inlineStr">
         <is>
           <t>FHIR 외</t>
         </is>
       </c>
-      <c r="H57" s="36" t="inlineStr">
+      <c r="H61" s="36" t="inlineStr">
         <is>
           <t>대화 묶음 (내부)</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="16" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
         <is>
           <t>챗봇</t>
         </is>
       </c>
-      <c r="B58" s="19" t="inlineStr">
+      <c r="B62" s="19" t="inlineStr">
         <is>
           <t>chat_messages</t>
         </is>
       </c>
-      <c r="C58" s="15" t="inlineStr">
+      <c r="C62" s="15" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D58" s="14" t="inlineStr">
+      <c r="D62" s="14" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="E58" s="15" t="inlineStr">
+      <c r="E62" s="15" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="F58" s="15" t="inlineStr"/>
-      <c r="G58" s="16" t="inlineStr">
+      <c r="F62" s="15" t="inlineStr"/>
+      <c r="G62" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H58" s="15" t="inlineStr">
+      <c r="H62" s="15" t="inlineStr">
         <is>
           <t>의료 기록으로 보관할 필요가 생길 때만</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="16" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>챗봇</t>
         </is>
       </c>
-      <c r="B59" s="33" t="inlineStr">
+      <c r="B63" s="33" t="inlineStr">
         <is>
           <t>chat_messages</t>
         </is>
       </c>
-      <c r="C59" s="15" t="inlineStr">
+      <c r="C63" s="15" t="inlineStr">
         <is>
           <t>role · content · created_at</t>
         </is>
       </c>
-      <c r="D59" s="15" t="inlineStr">
+      <c r="D63" s="15" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="E59" s="15" t="inlineStr">
+      <c r="E63" s="15" t="inlineStr">
         <is>
           <t>Communication.sender · payload.contentString · sent</t>
         </is>
       </c>
-      <c r="F59" s="15" t="inlineStr"/>
-      <c r="G59" s="16" t="inlineStr">
+      <c r="F63" s="15" t="inlineStr"/>
+      <c r="G63" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H59" s="15" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="16" t="inlineStr">
-        <is>
-          <t>실천·보상</t>
-        </is>
-      </c>
-      <c r="B60" s="19" t="inlineStr">
-        <is>
-          <t>recommendations</t>
-        </is>
-      </c>
-      <c r="C60" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D60" s="14" t="inlineStr">
-        <is>
-          <t>CarePlan</t>
-        </is>
-      </c>
-      <c r="E60" s="15" t="inlineStr">
-        <is>
-          <t>CarePlan.activity</t>
-        </is>
-      </c>
-      <c r="F60" s="15" t="inlineStr">
-        <is>
-          <t>추천 1개 = activity 1개 (status = not-started)</t>
-        </is>
-      </c>
-      <c r="G60" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H60" s="15" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="30" t="inlineStr">
-        <is>
-          <t>실천·보상</t>
-        </is>
-      </c>
-      <c r="B61" s="38" t="inlineStr">
-        <is>
-          <t>habit_goals</t>
-        </is>
-      </c>
-      <c r="C61" s="32" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D61" s="39" t="inlineStr">
-        <is>
-          <t>Goal</t>
-        </is>
-      </c>
-      <c r="E61" s="32" t="inlineStr">
-        <is>
-          <t>Goal</t>
-        </is>
-      </c>
-      <c r="F61" s="32" t="inlineStr"/>
-      <c r="G61" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H61" s="32" t="inlineStr">
-        <is>
-          <t>FHIR Goal = 환자 건강 목표</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="30" t="inlineStr">
-        <is>
-          <t>실천·보상</t>
-        </is>
-      </c>
-      <c r="B62" s="31" t="inlineStr">
-        <is>
-          <t>habit_goals</t>
-        </is>
-      </c>
-      <c r="C62" s="32" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D62" s="32" t="inlineStr">
-        <is>
-          <t>Goal</t>
-        </is>
-      </c>
-      <c r="E62" s="32" t="inlineStr">
-        <is>
-          <t>Goal.description.text</t>
-        </is>
-      </c>
-      <c r="F62" s="32" t="inlineStr"/>
-      <c r="G62" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H62" s="32" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="30" t="inlineStr">
-        <is>
-          <t>실천·보상</t>
-        </is>
-      </c>
-      <c r="B63" s="31" t="inlineStr">
-        <is>
-          <t>habit_goals</t>
-        </is>
-      </c>
-      <c r="C63" s="32" t="inlineStr">
-        <is>
-          <t>target_value · unit</t>
-        </is>
-      </c>
-      <c r="D63" s="32" t="inlineStr">
-        <is>
-          <t>Goal</t>
-        </is>
-      </c>
-      <c r="E63" s="32" t="inlineStr">
-        <is>
-          <t>Goal.target.detailQuantity</t>
-        </is>
-      </c>
-      <c r="F63" s="32" t="inlineStr"/>
-      <c r="G63" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H63" s="32" t="inlineStr"/>
+      <c r="H63" s="15" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="30" t="inlineStr">
-        <is>
-          <t>실천·보상</t>
-        </is>
-      </c>
-      <c r="B64" s="31" t="inlineStr">
-        <is>
-          <t>habit_goals</t>
-        </is>
-      </c>
-      <c r="C64" s="32" t="inlineStr">
-        <is>
-          <t>start_date · end_date</t>
-        </is>
-      </c>
-      <c r="D64" s="32" t="inlineStr">
-        <is>
-          <t>Goal</t>
-        </is>
-      </c>
-      <c r="E64" s="32" t="inlineStr">
-        <is>
-          <t>Goal.startDate · Goal.target.dueDate</t>
-        </is>
-      </c>
-      <c r="F64" s="32" t="inlineStr"/>
-      <c r="G64" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H64" s="32" t="inlineStr"/>
+      <c r="A64" s="16" t="inlineStr">
+        <is>
+          <t>챗봇</t>
+        </is>
+      </c>
+      <c r="B64" s="33" t="inlineStr">
+        <is>
+          <t>chat_messages</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="inlineStr">
+        <is>
+          <t>safety_card · status · model · prompt_tokens · completion_tokens · latency_ms</t>
+        </is>
+      </c>
+      <c r="D64" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E64" s="15" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="F64" s="15" t="n"/>
+      <c r="G64" s="16" t="inlineStr">
+        <is>
+          <t>FHIR 외</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="inlineStr">
+        <is>
+          <t>답변 상태와 비용 기록은 서비스 내부 정보</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
@@ -3228,211 +3241,207 @@
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B65" s="33" t="inlineStr">
+      <c r="B65" s="19" t="inlineStr">
+        <is>
+          <t>recommendations</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>CarePlan</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>CarePlan.activity</t>
+        </is>
+      </c>
+      <c r="F65" s="15" t="inlineStr">
+        <is>
+          <t>추천 1개 = activity 1개 (status = not-started)</t>
+        </is>
+      </c>
+      <c r="G65" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="30" t="inlineStr">
+        <is>
+          <t>실천·보상</t>
+        </is>
+      </c>
+      <c r="B66" s="38" t="inlineStr">
         <is>
           <t>habit_goals</t>
         </is>
       </c>
-      <c r="C65" s="15" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="D65" s="15" t="inlineStr">
+      <c r="C66" s="32" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D66" s="39" t="inlineStr">
         <is>
           <t>Goal</t>
         </is>
       </c>
-      <c r="E65" s="15" t="inlineStr">
-        <is>
-          <t>Goal.lifecycleStatus</t>
-        </is>
-      </c>
-      <c r="F65" s="15" t="inlineStr">
-        <is>
-          <t>active → active / ended → completed</t>
-        </is>
-      </c>
-      <c r="G65" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H65" s="15" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="16" t="inlineStr">
+      <c r="E66" s="32" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="F66" s="32" t="inlineStr"/>
+      <c r="G66" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H66" s="32" t="inlineStr">
+        <is>
+          <t>FHIR Goal = 환자 건강 목표</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
         <is>
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B66" s="19" t="inlineStr">
-        <is>
-          <t>habit_records</t>
-        </is>
-      </c>
-      <c r="C66" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D66" s="14" t="inlineStr">
-        <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="E66" s="15" t="inlineStr">
-        <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="F66" s="15" t="inlineStr">
-        <is>
-          <t>기록 1건 = Observation 1개 (focus = Goal)</t>
-        </is>
-      </c>
-      <c r="G66" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H66" s="15" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="16" t="inlineStr">
+      <c r="B67" s="31" t="inlineStr">
+        <is>
+          <t>habit_goals</t>
+        </is>
+      </c>
+      <c r="C67" s="32" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D67" s="32" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="E67" s="32" t="inlineStr">
+        <is>
+          <t>Goal.description.text</t>
+        </is>
+      </c>
+      <c r="F67" s="32" t="inlineStr"/>
+      <c r="G67" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H67" s="32" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
         <is>
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B67" s="33" t="inlineStr">
-        <is>
-          <t>habit_records</t>
-        </is>
-      </c>
-      <c r="C67" s="15" t="inlineStr">
-        <is>
-          <t>value · completed · record_date</t>
-        </is>
-      </c>
-      <c r="D67" s="15" t="inlineStr">
-        <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="E67" s="15" t="inlineStr">
-        <is>
-          <t>Observation.valueQuantity / valueBoolean · effectiveDateTime</t>
-        </is>
-      </c>
-      <c r="F67" s="15" t="inlineStr"/>
-      <c r="G67" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H67" s="15" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="34" t="inlineStr">
+      <c r="B68" s="31" t="inlineStr">
+        <is>
+          <t>habit_goals</t>
+        </is>
+      </c>
+      <c r="C68" s="32" t="inlineStr">
+        <is>
+          <t>target_value · unit</t>
+        </is>
+      </c>
+      <c r="D68" s="32" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="E68" s="32" t="inlineStr">
+        <is>
+          <t>Goal.target.detailQuantity</t>
+        </is>
+      </c>
+      <c r="F68" s="32" t="inlineStr"/>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H68" s="32" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B68" s="40" t="inlineStr">
-        <is>
-          <t>rewards</t>
-        </is>
-      </c>
-      <c r="C68" s="36" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D68" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="36" t="inlineStr"/>
-      <c r="G68" s="34" t="inlineStr">
-        <is>
-          <t>FHIR 외</t>
-        </is>
-      </c>
-      <c r="H68" s="36" t="inlineStr">
-        <is>
-          <t>포인트 (서비스 보상)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="16" t="inlineStr">
-        <is>
-          <t>마스터</t>
-        </is>
-      </c>
-      <c r="B69" s="19" t="inlineStr">
-        <is>
-          <t>drug_products</t>
-        </is>
-      </c>
-      <c r="C69" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D69" s="14" t="inlineStr">
-        <is>
-          <t>Medication</t>
-        </is>
-      </c>
-      <c r="E69" s="15" t="inlineStr">
-        <is>
-          <t>Medication</t>
-        </is>
-      </c>
-      <c r="F69" s="15" t="inlineStr"/>
-      <c r="G69" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H69" s="15" t="inlineStr"/>
+      <c r="B69" s="31" t="inlineStr">
+        <is>
+          <t>habit_goals</t>
+        </is>
+      </c>
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>start_date · end_date</t>
+        </is>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>Goal.startDate · Goal.target.dueDate</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr"/>
+      <c r="G69" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H69" s="32" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>마스터</t>
+          <t>실천·보상</t>
         </is>
       </c>
       <c r="B70" s="33" t="inlineStr">
         <is>
-          <t>drug_products</t>
+          <t>habit_goals</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>edi_code</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>Medication</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Medication.code.coding</t>
+          <t>Goal.lifecycleStatus</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>system = 심평원 EDI 제품코드</t>
+          <t>active → active / ended → completed</t>
         </is>
       </c>
       <c r="G70" s="16" t="inlineStr">
@@ -3445,32 +3454,32 @@
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>마스터</t>
-        </is>
-      </c>
-      <c r="B71" s="33" t="inlineStr">
-        <is>
-          <t>drug_products</t>
+          <t>실천·보상</t>
+        </is>
+      </c>
+      <c r="B71" s="19" t="inlineStr">
+        <is>
+          <t>habit_records</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>ingr_code</t>
-        </is>
-      </c>
-      <c r="D71" s="15" t="inlineStr">
-        <is>
-          <t>Medication</t>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>Observation</t>
         </is>
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>Medication.ingredient.itemCodeableConcept</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>system = 심평원 주성분코드</t>
+          <t>기록 1건 = Observation 1개 (focus = Goal)</t>
         </is>
       </c>
       <c r="G71" s="16" t="inlineStr">
@@ -3483,27 +3492,27 @@
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>마스터</t>
+          <t>실천·보상</t>
         </is>
       </c>
       <c r="B72" s="33" t="inlineStr">
         <is>
-          <t>drug_products</t>
+          <t>habit_records</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>entp_name</t>
+          <t>value · completed · record_date</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Medication.manufacturer → Organization.name</t>
+          <t>Observation.valueQuantity / valueBoolean · effectiveDateTime</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr"/>
@@ -3515,38 +3524,42 @@
       <c r="H72" s="15" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="16" t="inlineStr">
-        <is>
-          <t>마스터</t>
-        </is>
-      </c>
-      <c r="B73" s="33" t="inlineStr">
-        <is>
-          <t>drug_products</t>
-        </is>
-      </c>
-      <c r="C73" s="15" t="inlineStr">
-        <is>
-          <t>spec_value · spec_unit</t>
-        </is>
-      </c>
-      <c r="D73" s="15" t="inlineStr">
-        <is>
-          <t>Medication</t>
-        </is>
-      </c>
-      <c r="E73" s="15" t="inlineStr">
-        <is>
-          <t>Medication.ingredient.strength</t>
-        </is>
-      </c>
-      <c r="F73" s="15" t="inlineStr"/>
-      <c r="G73" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H73" s="15" t="inlineStr"/>
+      <c r="A73" s="34" t="inlineStr">
+        <is>
+          <t>실천·보상</t>
+        </is>
+      </c>
+      <c r="B73" s="40" t="inlineStr">
+        <is>
+          <t>rewards</t>
+        </is>
+      </c>
+      <c r="C73" s="36" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D73" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="36" t="inlineStr"/>
+      <c r="G73" s="34" t="inlineStr">
+        <is>
+          <t>FHIR 외</t>
+        </is>
+      </c>
+      <c r="H73" s="36" t="inlineStr">
+        <is>
+          <t>포인트 (서비스 보상)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="16" t="inlineStr">
@@ -3556,7 +3569,7 @@
       </c>
       <c r="B74" s="19" t="inlineStr">
         <is>
-          <t>drug_ingredients</t>
+          <t>drug_products</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
@@ -3566,12 +3579,12 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>Substance</t>
+          <t>Medication</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>Substance.code</t>
+          <t>Medication</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr"/>
@@ -3588,29 +3601,29 @@
           <t>마스터</t>
         </is>
       </c>
-      <c r="B75" s="19" t="inlineStr">
-        <is>
-          <t>drug_details</t>
+      <c r="B75" s="33" t="inlineStr">
+        <is>
+          <t>drug_products</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D75" s="14" t="inlineStr">
-        <is>
-          <t>MedicationKnowledge</t>
+          <t>edi_code</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
+          <t>Medication</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>MedicationKnowledge</t>
+          <t>Medication.code.coding</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>효능효과 · 용법용량 · 주의사항</t>
+          <t>system = 심평원 EDI 제품코드</t>
         </is>
       </c>
       <c r="G75" s="16" t="inlineStr">
@@ -3618,11 +3631,7 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H75" s="15" t="inlineStr">
-        <is>
-          <t>RAG 검색 원문</t>
-        </is>
-      </c>
+      <c r="H75" s="15" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="16" t="inlineStr">
@@ -3630,29 +3639,29 @@
           <t>마스터</t>
         </is>
       </c>
-      <c r="B76" s="19" t="inlineStr">
-        <is>
-          <t>dur_interaction · dur_interaction_exception</t>
+      <c r="B76" s="33" t="inlineStr">
+        <is>
+          <t>drug_products</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D76" s="14" t="inlineStr">
-        <is>
-          <t>ClinicalUseDefinition (R5)</t>
+          <t>ingr_code</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>Medication</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>ClinicalUseDefinition.interaction</t>
+          <t>Medication.ingredient.itemCodeableConcept</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>type = interaction</t>
+          <t>system = 심평원 주성분코드</t>
         </is>
       </c>
       <c r="G76" s="16" t="inlineStr">
@@ -3660,11 +3669,7 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H76" s="15" t="inlineStr">
-        <is>
-          <t>R4에는 전용 리소스 없음 — R5 참고</t>
-        </is>
-      </c>
+      <c r="H76" s="15" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
@@ -3672,41 +3677,33 @@
           <t>마스터</t>
         </is>
       </c>
-      <c r="B77" s="19" t="inlineStr">
-        <is>
-          <t>dur_elderly · dur_age_limit · dur_pregnancy</t>
+      <c r="B77" s="33" t="inlineStr">
+        <is>
+          <t>drug_products</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D77" s="14" t="inlineStr">
-        <is>
-          <t>ClinicalUseDefinition (R5)</t>
+          <t>entp_name</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>Organization</t>
         </is>
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>ClinicalUseDefinition.contraindication</t>
-        </is>
-      </c>
-      <c r="F77" s="15" t="inlineStr">
-        <is>
-          <t>type = contraindication, population = 나이 · 임부</t>
-        </is>
-      </c>
+          <t>Medication.manufacturer → Organization.name</t>
+        </is>
+      </c>
+      <c r="F77" s="15" t="inlineStr"/>
       <c r="G77" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H77" s="15" t="inlineStr">
-        <is>
-          <t>R5 참고</t>
-        </is>
-      </c>
+      <c r="H77" s="15" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="16" t="inlineStr">
@@ -3714,75 +3711,67 @@
           <t>마스터</t>
         </is>
       </c>
-      <c r="B78" s="19" t="inlineStr">
-        <is>
-          <t>dur_dose_limit</t>
+      <c r="B78" s="33" t="inlineStr">
+        <is>
+          <t>drug_products</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
+          <t>spec_value · spec_unit</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>Medication</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>Medication.ingredient.strength</t>
+        </is>
+      </c>
+      <c r="F78" s="15" t="inlineStr"/>
+      <c r="G78" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>마스터</t>
+        </is>
+      </c>
+      <c r="B79" s="19" t="inlineStr">
+        <is>
+          <t>drug_ingredients</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="inlineStr">
+        <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D78" s="14" t="inlineStr">
-        <is>
-          <t>MedicationKnowledge</t>
-        </is>
-      </c>
-      <c r="E78" s="15" t="inlineStr">
-        <is>
-          <t>MedicationKnowledge.administrationGuidelines.dosage</t>
-        </is>
-      </c>
-      <c r="F78" s="15" t="inlineStr">
-        <is>
-          <t>1일 최대 투여량</t>
-        </is>
-      </c>
-      <c r="G78" s="16" t="inlineStr">
+      <c r="D79" s="14" t="inlineStr">
+        <is>
+          <t>Substance</t>
+        </is>
+      </c>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>Substance.code</t>
+        </is>
+      </c>
+      <c r="F79" s="15" t="inlineStr"/>
+      <c r="G79" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H78" s="15" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="34" t="inlineStr">
-        <is>
-          <t>마스터</t>
-        </is>
-      </c>
-      <c r="B79" s="40" t="inlineStr">
-        <is>
-          <t>dup_ingredient · dup_efficacy</t>
-        </is>
-      </c>
-      <c r="C79" s="36" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D79" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="36" t="inlineStr"/>
-      <c r="G79" s="34" t="inlineStr">
-        <is>
-          <t>FHIR 외</t>
-        </is>
-      </c>
-      <c r="H79" s="36" t="inlineStr">
-        <is>
-          <t>국내 DUR 중복 점검 규칙</t>
-        </is>
-      </c>
+      <c r="H79" s="15" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="16" t="inlineStr">
@@ -3792,7 +3781,7 @@
       </c>
       <c r="B80" s="19" t="inlineStr">
         <is>
-          <t>diseases</t>
+          <t>drug_details</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
@@ -3802,17 +3791,17 @@
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>CodeSystem</t>
+          <t>MedicationKnowledge</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>CodeSystem.concept</t>
+          <t>MedicationKnowledge</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>KCD 상병 코드 목록</t>
+          <t>효능효과 · 용법용량 · 주의사항</t>
         </is>
       </c>
       <c r="G80" s="16" t="inlineStr">
@@ -3820,7 +3809,11 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H80" s="15" t="inlineStr"/>
+      <c r="H80" s="15" t="inlineStr">
+        <is>
+          <t>RAG 검색 원문</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
@@ -3830,7 +3823,7 @@
       </c>
       <c r="B81" s="19" t="inlineStr">
         <is>
-          <t>checkup_items</t>
+          <t>dur_interaction · dur_interaction_exception</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
@@ -3840,17 +3833,17 @@
       </c>
       <c r="D81" s="14" t="inlineStr">
         <is>
-          <t>CodeSystem</t>
+          <t>ClinicalUseDefinition (R5)</t>
         </is>
       </c>
       <c r="E81" s="15" t="inlineStr">
         <is>
-          <t>CodeSystem.concept</t>
+          <t>ClinicalUseDefinition.interaction</t>
         </is>
       </c>
       <c r="F81" s="15" t="inlineStr">
         <is>
-          <t>건강검진 검사항목 코드 목록</t>
+          <t>type = interaction</t>
         </is>
       </c>
       <c r="G81" s="16" t="inlineStr">
@@ -3860,7 +3853,7 @@
       </c>
       <c r="H81" s="15" t="inlineStr">
         <is>
-          <t>보류</t>
+          <t>R4에는 전용 리소스 없음 — R5 참고</t>
         </is>
       </c>
     </row>
@@ -3872,7 +3865,7 @@
       </c>
       <c r="B82" s="19" t="inlineStr">
         <is>
-          <t>lifestyle_guides · lifestyle_guide_actions · lifestyle_medication_links</t>
+          <t>dur_elderly · dur_age_limit · dur_pregnancy</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
@@ -3882,15 +3875,19 @@
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>PlanDefinition</t>
+          <t>ClinicalUseDefinition (R5)</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>PlanDefinition.action</t>
-        </is>
-      </c>
-      <c r="F82" s="15" t="inlineStr"/>
+          <t>ClinicalUseDefinition.contraindication</t>
+        </is>
+      </c>
+      <c r="F82" s="15" t="inlineStr">
+        <is>
+          <t>type = contraindication, population = 나이 · 임부</t>
+        </is>
+      </c>
       <c r="G82" s="16" t="inlineStr">
         <is>
           <t>변환</t>
@@ -3898,7 +3895,7 @@
       </c>
       <c r="H82" s="15" t="inlineStr">
         <is>
-          <t>자체 생활습관 지식 베이스. 실천 항목 1개 = PlanDefinition.action 1개</t>
+          <t>R5 참고</t>
         </is>
       </c>
     </row>
@@ -3910,118 +3907,312 @@
       </c>
       <c r="B83" s="19" t="inlineStr">
         <is>
+          <t>dur_dose_limit</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>MedicationKnowledge</t>
+        </is>
+      </c>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>MedicationKnowledge.administrationGuidelines.dosage</t>
+        </is>
+      </c>
+      <c r="F83" s="15" t="inlineStr">
+        <is>
+          <t>1일 최대 투여량</t>
+        </is>
+      </c>
+      <c r="G83" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H83" s="15" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="34" t="inlineStr">
+        <is>
+          <t>마스터</t>
+        </is>
+      </c>
+      <c r="B84" s="40" t="inlineStr">
+        <is>
+          <t>dup_ingredient · dup_efficacy</t>
+        </is>
+      </c>
+      <c r="C84" s="36" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D84" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E84" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F84" s="36" t="inlineStr"/>
+      <c r="G84" s="34" t="inlineStr">
+        <is>
+          <t>FHIR 외</t>
+        </is>
+      </c>
+      <c r="H84" s="36" t="inlineStr">
+        <is>
+          <t>국내 DUR 중복 점검 규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>마스터</t>
+        </is>
+      </c>
+      <c r="B85" s="19" t="inlineStr">
+        <is>
+          <t>diseases</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D85" s="14" t="inlineStr">
+        <is>
+          <t>CodeSystem</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>CodeSystem.concept</t>
+        </is>
+      </c>
+      <c r="F85" s="15" t="inlineStr">
+        <is>
+          <t>KCD 상병 코드 목록</t>
+        </is>
+      </c>
+      <c r="G85" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H85" s="15" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>마스터</t>
+        </is>
+      </c>
+      <c r="B86" s="19" t="inlineStr">
+        <is>
+          <t>checkup_items</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>CodeSystem</t>
+        </is>
+      </c>
+      <c r="E86" s="15" t="inlineStr">
+        <is>
+          <t>CodeSystem.concept</t>
+        </is>
+      </c>
+      <c r="F86" s="15" t="inlineStr">
+        <is>
+          <t>건강검진 검사항목 코드 목록</t>
+        </is>
+      </c>
+      <c r="G86" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H86" s="15" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>마스터</t>
+        </is>
+      </c>
+      <c r="B87" s="19" t="inlineStr">
+        <is>
+          <t>lifestyle_guides · lifestyle_guide_actions · lifestyle_medication_links</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D87" s="14" t="inlineStr">
+        <is>
+          <t>PlanDefinition</t>
+        </is>
+      </c>
+      <c r="E87" s="15" t="inlineStr">
+        <is>
+          <t>PlanDefinition.action</t>
+        </is>
+      </c>
+      <c r="F87" s="15" t="inlineStr"/>
+      <c r="G87" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H87" s="15" t="inlineStr">
+        <is>
+          <t>자체 생활습관 지식 베이스. 실천 항목 1개 = PlanDefinition.action 1개</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>마스터</t>
+        </is>
+      </c>
+      <c r="B88" s="19" t="inlineStr">
+        <is>
           <t>lifestyle_guide_sources</t>
         </is>
       </c>
-      <c r="C83" s="15" t="inlineStr">
+      <c r="C88" s="15" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D83" s="14" t="inlineStr">
+      <c r="D88" s="14" t="inlineStr">
         <is>
           <t>DocumentReference / Citation (R5)</t>
         </is>
       </c>
-      <c r="E83" s="15" t="inlineStr">
+      <c r="E88" s="15" t="inlineStr">
         <is>
           <t>PlanDefinition.relatedArtifact</t>
         </is>
       </c>
-      <c r="F83" s="15" t="inlineStr">
+      <c r="F88" s="15" t="inlineStr">
         <is>
           <t>type = citation · display = 문서명 · url · citation = 기관 · 발행일</t>
         </is>
       </c>
-      <c r="G83" s="16" t="inlineStr">
+      <c r="G88" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H83" s="15" t="inlineStr">
+      <c r="H88" s="15" t="inlineStr">
         <is>
           <t>v1.2 · R4는 relatedArtifact로 출처 표시</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="22" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="22" t="inlineStr">
         <is>
           <t>마스터</t>
         </is>
       </c>
-      <c r="B84" s="37" t="inlineStr">
+      <c r="B89" s="37" t="inlineStr">
         <is>
           <t>lifestyle_medication_links</t>
         </is>
       </c>
-      <c r="C84" s="21" t="inlineStr">
+      <c r="C89" s="21" t="inlineStr">
         <is>
           <t>requires_clinician · goal_eligible</t>
         </is>
       </c>
-      <c r="D84" s="21" t="inlineStr">
+      <c r="D89" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E84" s="21" t="inlineStr">
+      <c r="E89" s="21" t="inlineStr">
         <is>
           <t>extension</t>
         </is>
       </c>
-      <c r="F84" s="21" t="inlineStr"/>
-      <c r="G84" s="22" t="inlineStr">
+      <c r="F89" s="21" t="inlineStr"/>
+      <c r="G89" s="22" t="inlineStr">
         <is>
           <t>확장</t>
         </is>
       </c>
-      <c r="H84" s="21" t="inlineStr">
+      <c r="H89" s="21" t="inlineStr">
         <is>
           <t>v1.2 · 서비스 표시 규칙</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="34" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="34" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B85" s="40" t="inlineStr">
+      <c r="B90" s="40" t="inlineStr">
         <is>
           <t>drug_guides</t>
         </is>
       </c>
-      <c r="C85" s="36" t="inlineStr">
+      <c r="C90" s="36" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D85" s="17" t="inlineStr">
+      <c r="D90" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E85" s="36" t="inlineStr">
+      <c r="E90" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F85" s="36" t="n"/>
-      <c r="G85" s="34" t="inlineStr">
+      <c r="F90" s="36" t="n"/>
+      <c r="G90" s="34" t="inlineStr">
         <is>
           <t>FHIR 외</t>
         </is>
       </c>
-      <c r="H85" s="36" t="inlineStr">
+      <c r="H90" s="36" t="inlineStr">
         <is>
           <t>미리 저장해 두는 AI 생성 약 안내문 (의료 기록 아님). guides와 같은 이유로 FHIR 대응 없음</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:H85"/>
+  <autoFilter ref="A5:H90"/>
   <dataValidations count="1">
     <dataValidation sqref="G6:G300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"일치,변환,확장,FHIR 외"</formula1>
@@ -4037,7 +4228,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E162"/>
+  <dimension ref="A1:E169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7167,6 +7358,139 @@
         </is>
       </c>
       <c r="E162" s="10" t="n"/>
+    </row>
+    <row r="163" hidden="1" outlineLevel="1">
+      <c r="A163" s="10" t="n"/>
+      <c r="B163" s="10" t="inlineStr">
+        <is>
+          <t>입력 / ocr_jobs.duplicates — 필드 추가</t>
+        </is>
+      </c>
+      <c r="C163" s="10" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="D163" s="10" t="inlineStr">
+        <is>
+          <t>duplicates jsonb · N · 이미 있는 처방전이라 새로 저장하지 않은 사진 [{fileIndex, prescriptionId}] (10/14 중복 처방전 처리)</t>
+        </is>
+      </c>
+      <c r="E163" s="10" t="n"/>
+    </row>
+    <row r="164" hidden="1" outlineLevel="1">
+      <c r="A164" s="10" t="n"/>
+      <c r="B164" s="10" t="inlineStr">
+        <is>
+          <t>입력 / prescriptions.content_key — 필드 추가</t>
+        </is>
+      </c>
+      <c r="C164" s="10" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="D164" s="10" t="inlineStr">
+        <is>
+          <t>content_key varchar(64) · N · 같은 처방전인지 가리는 해시 (병원, 교부일, 약 목록)</t>
+        </is>
+      </c>
+      <c r="E164" s="10" t="n"/>
+    </row>
+    <row r="165" hidden="1" outlineLevel="1">
+      <c r="A165" s="10" t="n"/>
+      <c r="B165" s="10" t="inlineStr">
+        <is>
+          <t>입력 / prescription_items.suggested_by — 필드 추가</t>
+        </is>
+      </c>
+      <c r="C165" s="10" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="D165" s="10" t="inlineStr">
+        <is>
+          <t>suggested_by varchar(20) · N · 후보가 추천에서 왔을 때 similar 또는 llm</t>
+        </is>
+      </c>
+      <c r="E165" s="10" t="n"/>
+    </row>
+    <row r="166" hidden="1" outlineLevel="1">
+      <c r="A166" s="10" t="n"/>
+      <c r="B166" s="10" t="inlineStr">
+        <is>
+          <t>분석 / analysis_warnings.detail — 필드 추가</t>
+        </is>
+      </c>
+      <c r="C166" s="10" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="D166" s="10" t="inlineStr">
+        <is>
+          <t>detail jsonb · N · 약이 3개 이상인 경고의 전체 항목 번호, 성분, 근거 구분</t>
+        </is>
+      </c>
+      <c r="E166" s="10" t="n"/>
+    </row>
+    <row r="167" hidden="1" outlineLevel="1">
+      <c r="A167" s="10" t="n"/>
+      <c r="B167" s="10" t="inlineStr">
+        <is>
+          <t>챗봇 / chat_sessions.safety_mode_until — 필드 추가 (이슈 #88)</t>
+        </is>
+      </c>
+      <c r="C167" s="10" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="D167" s="10" t="inlineStr">
+        <is>
+          <t>safety_mode_until timestamp · N · 자해 표현 뒤 안전 모드가 끝나는 시각</t>
+        </is>
+      </c>
+      <c r="E167" s="10" t="n"/>
+    </row>
+    <row r="168" hidden="1" outlineLevel="1">
+      <c r="A168" s="10" t="n"/>
+      <c r="B168" s="10" t="inlineStr">
+        <is>
+          <t>챗봇 / chat_messages.safety_card, status, model, prompt_tokens, completion_tokens, latency_ms — 필드 추가 (이슈 #88)</t>
+        </is>
+      </c>
+      <c r="C168" s="10" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="D168" s="10" t="inlineStr">
+        <is>
+          <t>6개 필드 (status는 Y, 기본값 'done'). 수인 10/12 확정</t>
+        </is>
+      </c>
+      <c r="E168" s="10" t="n"/>
+    </row>
+    <row r="169" hidden="1" outlineLevel="1">
+      <c r="A169" s="10" t="n"/>
+      <c r="B169" s="10" t="inlineStr">
+        <is>
+          <t>FHIR 대응 탭 — 위 필드 행 추가</t>
+        </is>
+      </c>
+      <c r="C169" s="10" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="D169" s="10" t="inlineStr">
+        <is>
+          <t>ocr_jobs.duplicates, prescriptions.content_key, prescription_items.suggested_by, analysis_warnings.detail, 챗봇 6개 필드 대응 행 추가</t>
+        </is>
+      </c>
+      <c r="E169" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -8481,7 +8805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8514,6 +8838,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -8983,64 +9308,60 @@
       <c r="N11" s="24" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>prescriptions</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>처방전 · 약봉투</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="15" t="n"/>
-      <c r="K12" s="15" t="inlineStr">
-        <is>
-          <t>OC-01 · OC-02 · O-1 · O-2</t>
-        </is>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
-        <is>
-          <t>기존</t>
-        </is>
-      </c>
-      <c r="M12" s="16" t="inlineStr">
-        <is>
-          <t>v0.1</t>
-        </is>
-      </c>
-      <c r="N12" s="15" t="inlineStr">
-        <is>
-          <t>사진 1장 = 1행. 업로드된 원본 이미지는 OCR 처리 후 즉시 폐기</t>
-        </is>
-      </c>
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>ocr_jobs</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>OCR 작업</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>duplicates</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>중복 사진</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="F12" s="25" t="n"/>
+      <c r="G12" s="24" t="n"/>
+      <c r="H12" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="n"/>
+      <c r="J12" s="24" t="inlineStr">
+        <is>
+          <t>이미 있는 처방전이라 새로 저장하지 않은 사진 [{fileIndex, prescriptionId}] (10/14 중복 처방전 처리). 없으면 null</t>
+        </is>
+      </c>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>OC-01 / O-1 / O-5</t>
+        </is>
+      </c>
+      <c r="L12" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M12" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N12" s="24" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
@@ -9055,12 +9376,12 @@
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>사용자 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -9070,14 +9391,10 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G13" s="15" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="n"/>
       <c r="H13" s="16" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9100,71 +9417,71 @@
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N13" s="15" t="n"/>
+      <c r="N13" s="15" t="inlineStr">
+        <is>
+          <t>사진 1장 = 1행. 업로드된 원본 이미지는 OCR 처리 후 즉시 폐기</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>prescriptions</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>처방전 · 약봉투</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>ocr_job_id</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>OCR 작업 ID</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>사용자 ID</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="F14" s="25" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
-        <is>
-          <t>ocr_jobs.id</t>
-        </is>
-      </c>
-      <c r="H14" s="25" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I14" s="24" t="n"/>
-      <c r="J14" s="24" t="inlineStr">
-        <is>
-          <t>어느 업로드 작업에서 나온 사진인지</t>
-        </is>
-      </c>
-      <c r="K14" s="24" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="n"/>
+      <c r="J14" s="15" t="n"/>
+      <c r="K14" s="15" t="inlineStr">
         <is>
           <t>OC-01 · OC-02 · O-1 · O-2</t>
         </is>
       </c>
-      <c r="L14" s="25" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M14" s="25" t="inlineStr">
-        <is>
-          <t>v1.2</t>
-        </is>
-      </c>
-      <c r="N14" s="24" t="n"/>
+      <c r="L14" s="16" t="inlineStr">
+        <is>
+          <t>기존</t>
+        </is>
+      </c>
+      <c r="M14" s="16" t="inlineStr">
+        <is>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="N14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="23" t="inlineStr">
@@ -9179,21 +9496,29 @@
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>file_index</t>
+          <t>ocr_job_id</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>사진 순번</t>
+          <t>OCR 작업 ID</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>smallint</t>
-        </is>
-      </c>
-      <c r="F15" s="25" t="n"/>
-      <c r="G15" s="24" t="n"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>ocr_jobs.id</t>
+        </is>
+      </c>
       <c r="H15" s="25" t="inlineStr">
         <is>
           <t>N</t>
@@ -9202,7 +9527,7 @@
       <c r="I15" s="24" t="n"/>
       <c r="J15" s="24" t="inlineStr">
         <is>
-          <t>작업 안에서 몇 번째 사진인지 (실패 사진 안내용)</t>
+          <t>어느 업로드 작업에서 나온 사진인지</t>
         </is>
       </c>
       <c r="K15" s="24" t="inlineStr">
@@ -9235,104 +9560,104 @@
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>doc_type</t>
+          <t>file_index</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>문서 종류</t>
+          <t>사진 순번</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="F16" s="25" t="n"/>
       <c r="G16" s="24" t="n"/>
       <c r="H16" s="25" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I16" s="24" t="n"/>
       <c r="J16" s="24" t="inlineStr">
         <is>
+          <t>작업 안에서 몇 번째 사진인지 (실패 사진 안내용)</t>
+        </is>
+      </c>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>OC-01 · OC-02 · O-1 · O-2</t>
+        </is>
+      </c>
+      <c r="L16" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M16" s="25" t="inlineStr">
+        <is>
+          <t>v1.2</t>
+        </is>
+      </c>
+      <c r="N16" s="24" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>prescriptions</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>처방전 · 약봉투</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>doc_type</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>문서 종류</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="F17" s="25" t="n"/>
+      <c r="G17" s="24" t="n"/>
+      <c r="H17" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="n"/>
+      <c r="J17" s="24" t="inlineStr">
+        <is>
           <t>prescription(처방전) / pill_bag(약봉투). 약봉투는 질병코드 없음 → RG-05-E1</t>
         </is>
       </c>
-      <c r="K16" s="24" t="inlineStr">
+      <c r="K17" s="24" t="inlineStr">
         <is>
           <t>OC-01 · OC-02 · O-1 · O-2</t>
         </is>
       </c>
-      <c r="L16" s="25" t="inlineStr">
+      <c r="L17" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M16" s="25" t="inlineStr">
+      <c r="M17" s="25" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N16" s="24" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>prescriptions</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>처방전 · 약봉투</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>issued_date</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>처방 교부일 · 조제일</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="15" t="n"/>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>처방 교부일 (약봉투는 조제일) — 약봉투에는 교부일이 없고, 조제일이 약을 받은 날</t>
-        </is>
-      </c>
-      <c r="K17" s="15" t="inlineStr">
-        <is>
-          <t>OC-01 · OC-02 · O-1 · O-2</t>
-        </is>
-      </c>
-      <c r="L17" s="16" t="inlineStr">
-        <is>
-          <t>수정</t>
-        </is>
-      </c>
-      <c r="M17" s="16" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N17" s="15" t="n"/>
+      <c r="N17" s="24" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
@@ -9347,17 +9672,17 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>hospital_name</t>
+          <t>issued_date</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>병원 이름</t>
+          <t>처방 교부일 · 조제일</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>varchar(200)</t>
+          <t>date</t>
         </is>
       </c>
       <c r="F18" s="16" t="n"/>
@@ -9368,7 +9693,11 @@
         </is>
       </c>
       <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>처방 교부일 (약봉투는 조제일) — 약봉투에는 교부일이 없고, 조제일이 약을 받은 날</t>
+        </is>
+      </c>
       <c r="K18" s="15" t="inlineStr">
         <is>
           <t>OC-01 · OC-02 · O-1 · O-2</t>
@@ -9376,179 +9705,175 @@
       </c>
       <c r="L18" s="16" t="inlineStr">
         <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="M18" s="16" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N18" s="15" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>prescriptions</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>처방전 · 약봉투</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>hospital_name</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>병원 이름</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="n"/>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="15" t="n"/>
+      <c r="K19" s="15" t="inlineStr">
+        <is>
+          <t>OC-01 · OC-02 · O-1 · O-2</t>
+        </is>
+      </c>
+      <c r="L19" s="16" t="inlineStr">
+        <is>
           <t>기존</t>
         </is>
       </c>
-      <c r="M18" s="16" t="inlineStr">
+      <c r="M19" s="16" t="inlineStr">
         <is>
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N18" s="15" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="N19" s="15" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>prescriptions</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>처방전 · 약봉투</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>ocr_raw_text</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>OCR 원문</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F19" s="22" t="n"/>
-      <c r="G19" s="21" t="n"/>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="F20" s="22" t="n"/>
+      <c r="G20" s="21" t="n"/>
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I19" s="21" t="n"/>
-      <c r="J19" s="21" t="inlineStr">
+      <c r="I20" s="21" t="n"/>
+      <c r="J20" s="21" t="inlineStr">
         <is>
           <t>OCR 원문 — 저장하지 않음 (10/15 결정, 칸은 남겨 두고 비워 둠) · 원본 이미지도 저장하지 않음</t>
         </is>
       </c>
-      <c r="K19" s="21" t="inlineStr">
+      <c r="K20" s="21" t="inlineStr">
         <is>
           <t>OC-01 · OC-02 · O-1 · O-2</t>
         </is>
       </c>
-      <c r="L19" s="22" t="inlineStr">
+      <c r="L20" s="22" t="inlineStr">
         <is>
           <t>수정</t>
         </is>
       </c>
-      <c r="M19" s="22" t="inlineStr">
+      <c r="M20" s="22" t="inlineStr">
         <is>
           <t>v1.3</t>
         </is>
       </c>
-      <c r="N19" s="21" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="N20" s="21" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>prescriptions</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>처방전 · 약봉투</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>ocr_confidence</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>OCR 신뢰도</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>decimal(5,4)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="F21" s="16" t="n"/>
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
-      <c r="K20" s="15" t="inlineStr">
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="15" t="n"/>
+      <c r="K21" s="15" t="inlineStr">
         <is>
           <t>OC-01 · OC-02 · O-1 · O-2</t>
         </is>
       </c>
-      <c r="L20" s="16" t="inlineStr">
+      <c r="L21" s="16" t="inlineStr">
         <is>
           <t>기존</t>
         </is>
       </c>
-      <c r="M20" s="16" t="inlineStr">
+      <c r="M21" s="16" t="inlineStr">
         <is>
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N20" s="15" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="23" t="inlineStr">
-        <is>
-          <t>prescriptions</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>처방전 · 약봉투</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="inlineStr">
-        <is>
-          <t>quality_flag</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>사진 품질 표시</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="F21" s="25" t="n"/>
-      <c r="G21" s="24" t="n"/>
-      <c r="H21" s="25" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I21" s="24" t="n"/>
-      <c r="J21" s="24" t="inlineStr">
-        <is>
-          <t>ok / low (OC-01-E1에서 "그래도 계속 진행" 시)</t>
-        </is>
-      </c>
-      <c r="K21" s="24" t="inlineStr">
-        <is>
-          <t>OC-01 · OC-02 · O-1 · O-2</t>
-        </is>
-      </c>
-      <c r="L21" s="25" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M21" s="25" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N21" s="24" t="n"/>
+      <c r="N21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="23" t="inlineStr">
@@ -9563,17 +9888,17 @@
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>notices</t>
+          <t>quality_flag</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>읽기 확인 표시</t>
+          <t>사진 품질 표시</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="F22" s="25" t="n"/>
@@ -9586,128 +9911,124 @@
       <c r="I22" s="24" t="n"/>
       <c r="J22" s="24" t="inlineStr">
         <is>
+          <t>ok / low (OC-01-E1에서 "그래도 계속 진행" 시)</t>
+        </is>
+      </c>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>OC-01 · OC-02 · O-1 · O-2</t>
+        </is>
+      </c>
+      <c r="L22" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M22" s="25" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="N22" s="24" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>prescriptions</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>처방전 · 약봉투</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>notices</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>읽기 확인 표시</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="F23" s="25" t="n"/>
+      <c r="G23" s="24" t="n"/>
+      <c r="H23" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="n"/>
+      <c r="J23" s="24" t="inlineStr">
+        <is>
           <t>사진을 읽을 때 사용자가 확인해야 할 점 문장 목록 (줄 수 불일치 · 칸 순서 추정 · 날짜 이상 등). 없으면 null</t>
         </is>
       </c>
-      <c r="K22" s="24" t="inlineStr">
+      <c r="K23" s="24" t="inlineStr">
         <is>
           <t>OC-01 · OC-02 · O-1 · O-2</t>
         </is>
       </c>
-      <c r="L22" s="25" t="inlineStr">
+      <c r="L23" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M22" s="25" t="inlineStr">
+      <c r="M23" s="25" t="inlineStr">
         <is>
           <t>v1.3</t>
         </is>
       </c>
-      <c r="N22" s="24" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>prescriptions</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>처방전 · 약봉투</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>생성 일시</t>
-        </is>
-      </c>
-      <c r="E23" s="15" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="n"/>
-      <c r="G23" s="15" t="n"/>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="n"/>
-      <c r="K23" s="15" t="inlineStr">
-        <is>
-          <t>OC-01 · OC-02 · O-1 · O-2</t>
-        </is>
-      </c>
-      <c r="L23" s="16" t="inlineStr">
-        <is>
-          <t>기존</t>
-        </is>
-      </c>
-      <c r="M23" s="16" t="inlineStr">
-        <is>
-          <t>v0.1</t>
-        </is>
-      </c>
-      <c r="N23" s="15" t="n"/>
+      <c r="N23" s="24" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="23" t="inlineStr">
         <is>
-          <t>prescription_diseases</t>
+          <t>prescriptions</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>처방전 질병코드</t>
+          <t>처방전 · 약봉투</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>content_key</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>같은 처방전 판별값</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F24" s="25" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>varchar(64)</t>
+        </is>
+      </c>
+      <c r="F24" s="25" t="n"/>
       <c r="G24" s="24" t="n"/>
       <c r="H24" s="25" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I24" s="24" t="n"/>
       <c r="J24" s="24" t="inlineStr">
         <is>
-          <t>코드 구현 맞춤 — Tortoise는 복합 PK를 지원하지 않아 id를 PK로 두고 원래 PK 두 칸은 unique로</t>
+          <t>같은 처방전인지 가리는 해시 (병원, 교부일, 약 목록). 인덱스</t>
         </is>
       </c>
       <c r="K24" s="24" t="inlineStr">
         <is>
-          <t>O-2 · R-4</t>
+          <t>OC-01 / O-1 / O-5</t>
         </is>
       </c>
       <c r="L24" s="25" t="inlineStr">
@@ -9717,74 +10038,66 @@
       </c>
       <c r="M24" s="25" t="inlineStr">
         <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N24" s="24" t="inlineStr">
-        <is>
-          <t>v1.0 신규 · 처방전 질병분류기호는 주상병 + 부상병 여러 개 · v1.3 id PK + (prescription_id, disease_id) UQ</t>
-        </is>
-      </c>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N24" s="24" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="23" t="inlineStr">
-        <is>
-          <t>prescription_diseases</t>
-        </is>
-      </c>
-      <c r="B25" s="24" t="inlineStr">
-        <is>
-          <t>처방전 질병코드</t>
-        </is>
-      </c>
-      <c r="C25" s="24" t="inlineStr">
-        <is>
-          <t>prescription_id</t>
-        </is>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
-        <is>
-          <t>처방전 ID</t>
-        </is>
-      </c>
-      <c r="E25" s="24" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F25" s="25" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G25" s="24" t="inlineStr">
-        <is>
-          <t>prescriptions.id</t>
-        </is>
-      </c>
-      <c r="H25" s="25" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I25" s="24" t="n"/>
-      <c r="J25" s="24" t="n"/>
-      <c r="K25" s="24" t="inlineStr">
-        <is>
-          <t>O-2 · R-4</t>
-        </is>
-      </c>
-      <c r="L25" s="25" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M25" s="25" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N25" s="24" t="n"/>
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>prescriptions</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>처방전 · 약봉투</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>생성 일시</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="15" t="n"/>
+      <c r="H25" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="J25" s="15" t="n"/>
+      <c r="K25" s="15" t="inlineStr">
+        <is>
+          <t>OC-01 · OC-02 · O-1 · O-2</t>
+        </is>
+      </c>
+      <c r="L25" s="16" t="inlineStr">
+        <is>
+          <t>기존</t>
+        </is>
+      </c>
+      <c r="M25" s="16" t="inlineStr">
+        <is>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="N25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="23" t="inlineStr">
@@ -9799,29 +10112,25 @@
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>disease_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>상병 코드</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
         <is>
-          <t>varchar(10)</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G26" s="24" t="inlineStr">
-        <is>
-          <t>diseases.code</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="n"/>
       <c r="H26" s="25" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9830,7 +10139,7 @@
       <c r="I26" s="24" t="n"/>
       <c r="J26" s="24" t="inlineStr">
         <is>
-          <t>값은 상병기호 (예: I10). (prescription_id, disease_id) UQ — 칸 이름은 Tortoise 규칙에 맞춤</t>
+          <t>코드 구현 맞춤 — Tortoise는 복합 PK를 지원하지 않아 id를 PK로 두고 원래 PK 두 칸은 unique로</t>
         </is>
       </c>
       <c r="K26" s="24" t="inlineStr">
@@ -9848,7 +10157,11 @@
           <t>v1.3</t>
         </is>
       </c>
-      <c r="N26" s="24" t="n"/>
+      <c r="N26" s="24" t="inlineStr">
+        <is>
+          <t>v1.0 신규 · 처방전 질병분류기호는 주상병 + 부상병 여러 개 · v1.3 id PK + (prescription_id, disease_id) UQ</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="23" t="inlineStr">
@@ -9863,352 +10176,356 @@
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
+          <t>prescription_id</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>처방전 ID</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F27" s="25" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>prescriptions.id</t>
+        </is>
+      </c>
+      <c r="H27" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="n"/>
+      <c r="J27" s="24" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>O-2 · R-4</t>
+        </is>
+      </c>
+      <c r="L27" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M27" s="25" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N27" s="24" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>prescription_diseases</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>처방전 질병코드</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>disease_id</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>상병 코드</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>varchar(10)</t>
+        </is>
+      </c>
+      <c r="F28" s="25" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>diseases.code</t>
+        </is>
+      </c>
+      <c r="H28" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="n"/>
+      <c r="J28" s="24" t="inlineStr">
+        <is>
+          <t>값은 상병기호 (예: I10). (prescription_id, disease_id) UQ — 칸 이름은 Tortoise 규칙에 맞춤</t>
+        </is>
+      </c>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>O-2 · R-4</t>
+        </is>
+      </c>
+      <c r="L28" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M28" s="25" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N28" s="24" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>prescription_diseases</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>처방전 질병코드</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
           <t>is_main</t>
         </is>
       </c>
-      <c r="D27" s="24" t="inlineStr">
+      <c r="D29" s="24" t="inlineStr">
         <is>
           <t>주상병 여부</t>
         </is>
       </c>
-      <c r="E27" s="24" t="inlineStr">
+      <c r="E29" s="24" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="F27" s="25" t="n"/>
-      <c r="G27" s="24" t="n"/>
-      <c r="H27" s="25" t="inlineStr">
+      <c r="F29" s="25" t="n"/>
+      <c r="G29" s="24" t="n"/>
+      <c r="H29" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I27" s="24" t="n"/>
-      <c r="J27" s="24" t="inlineStr">
+      <c r="I29" s="24" t="n"/>
+      <c r="J29" s="24" t="inlineStr">
         <is>
           <t>주상병 여부</t>
         </is>
       </c>
-      <c r="K27" s="24" t="inlineStr">
+      <c r="K29" s="24" t="inlineStr">
         <is>
           <t>O-2 · R-4</t>
         </is>
       </c>
-      <c r="L27" s="25" t="inlineStr">
+      <c r="L29" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M27" s="25" t="inlineStr">
+      <c r="M29" s="25" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N27" s="24" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="N29" s="24" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>prescription_items</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>처방 약품</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C30" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D30" s="15" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="G28" s="15" t="n"/>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I28" s="15" t="n"/>
-      <c r="J28" s="15" t="n"/>
-      <c r="K28" s="15" t="inlineStr">
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="15" t="n"/>
+      <c r="K30" s="15" t="inlineStr">
         <is>
           <t>OC-02 · O-2 · O-3</t>
         </is>
       </c>
-      <c r="L28" s="16" t="inlineStr">
+      <c r="L30" s="16" t="inlineStr">
         <is>
           <t>기존</t>
         </is>
       </c>
-      <c r="M28" s="16" t="inlineStr">
+      <c r="M30" s="16" t="inlineStr">
         <is>
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N28" s="15" t="inlineStr">
+      <c r="N30" s="15" t="inlineStr">
         <is>
           <t>needs_confirm · unmatched가 남아 있으면 분석 시작 불가 (REQ-033). 1일 총량 = dose_per_time * times_per_day. 약이 정해졌으면(auto · user_confirmed) edi_code · item_seq 중 하나는 있음</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>prescription_items</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>처방 약품</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>prescription_id</t>
         </is>
       </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="D31" s="15" t="inlineStr">
         <is>
           <t>처방전 ID</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F31" s="16" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="G29" s="15" t="inlineStr">
+      <c r="G31" s="15" t="inlineStr">
         <is>
           <t>prescriptions.id</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="H31" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I29" s="15" t="n"/>
-      <c r="J29" s="15" t="n"/>
-      <c r="K29" s="15" t="inlineStr">
+      <c r="I31" s="15" t="n"/>
+      <c r="J31" s="15" t="n"/>
+      <c r="K31" s="15" t="inlineStr">
         <is>
           <t>OC-02 · O-2 · O-3</t>
         </is>
       </c>
-      <c r="L29" s="16" t="inlineStr">
+      <c r="L31" s="16" t="inlineStr">
         <is>
           <t>기존</t>
         </is>
       </c>
-      <c r="M29" s="16" t="inlineStr">
+      <c r="M31" s="16" t="inlineStr">
         <is>
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N29" s="15" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="N31" s="15" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>prescription_items</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>처방 약품</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>edi_code</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>EDI 제품코드</t>
         </is>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>varchar(9)</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>drug_products.edi_code</t>
         </is>
       </c>
-      <c r="H30" s="22" t="inlineStr">
+      <c r="H32" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I30" s="21" t="n"/>
-      <c r="J30" s="21" t="inlineStr">
+      <c r="I32" s="21" t="n"/>
+      <c r="J32" s="21" t="inlineStr">
         <is>
           <t>매칭 실패 · 제외 · 급여목록에 없는 약이면 null</t>
         </is>
       </c>
-      <c r="K30" s="21" t="inlineStr">
+      <c r="K32" s="21" t="inlineStr">
         <is>
           <t>OC-02 · O-2 · O-3</t>
         </is>
       </c>
-      <c r="L30" s="22" t="inlineStr">
+      <c r="L32" s="22" t="inlineStr">
         <is>
           <t>수정</t>
         </is>
       </c>
-      <c r="M30" s="22" t="inlineStr">
+      <c r="M32" s="22" t="inlineStr">
         <is>
           <t>v1.3</t>
         </is>
       </c>
-      <c r="N30" s="21" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>prescription_items</t>
-        </is>
-      </c>
-      <c r="B31" s="21" t="inlineStr">
-        <is>
-          <t>처방 약품</t>
-        </is>
-      </c>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>item_seq</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>품목기준코드</t>
-        </is>
-      </c>
-      <c r="E31" s="21" t="inlineStr">
-        <is>
-          <t>varchar(9)</t>
-        </is>
-      </c>
-      <c r="F31" s="22" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
-        <is>
-          <t>drug_details.item_seq</t>
-        </is>
-      </c>
-      <c r="H31" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I31" s="21" t="n"/>
-      <c r="J31" s="21" t="inlineStr">
-        <is>
-          <t>급여목록에 없는 약(일반약 등)만 채움 — 있는 약은 edi_code로 약 정보까지 이어짐</t>
-        </is>
-      </c>
-      <c r="K31" s="21" t="inlineStr">
-        <is>
-          <t>OC-02 · O-2 · O-3</t>
-        </is>
-      </c>
-      <c r="L31" s="22" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M31" s="22" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N31" s="21" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>prescription_items</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>처방 약품</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>raw_name</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>인식된 약품명</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>varchar(300)</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="n"/>
-      <c r="G32" s="15" t="n"/>
-      <c r="H32" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I32" s="15" t="n"/>
-      <c r="J32" s="15" t="inlineStr">
-        <is>
-          <t>OCR이 읽은 원문 약품명</t>
-        </is>
-      </c>
-      <c r="K32" s="15" t="inlineStr">
-        <is>
-          <t>OC-02 · O-2 · O-3</t>
-        </is>
-      </c>
-      <c r="L32" s="16" t="inlineStr">
-        <is>
-          <t>기존</t>
-        </is>
-      </c>
-      <c r="M32" s="16" t="inlineStr">
-        <is>
-          <t>v0.1</t>
-        </is>
-      </c>
-      <c r="N32" s="15" t="n"/>
+      <c r="N32" s="21" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="20" t="inlineStr">
@@ -10223,28 +10540,40 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>match_score</t>
+          <t>item_seq</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
         <is>
-          <t>매칭 점수</t>
+          <t>품목기준코드</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
         <is>
-          <t>decimal(5,4)</t>
-        </is>
-      </c>
-      <c r="F33" s="22" t="n"/>
-      <c r="G33" s="21" t="n"/>
+          <t>varchar(9)</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
+        <is>
+          <t>drug_details.item_seq</t>
+        </is>
+      </c>
       <c r="H33" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
       <c r="I33" s="21" t="n"/>
-      <c r="J33" s="21" t="n"/>
+      <c r="J33" s="21" t="inlineStr">
+        <is>
+          <t>급여목록에 없는 약(일반약 등)만 채움 — 있는 약은 edi_code로 약 정보까지 이어짐</t>
+        </is>
+      </c>
       <c r="K33" s="21" t="inlineStr">
         <is>
           <t>OC-02 · O-2 · O-3</t>
@@ -10252,71 +10581,71 @@
       </c>
       <c r="L33" s="22" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="M33" s="22" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.3</t>
         </is>
       </c>
       <c r="N33" s="21" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>prescription_items</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>처방 약품</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
-        <is>
-          <t>match_status</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
-        <is>
-          <t>매칭 상태</t>
-        </is>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="F34" s="22" t="n"/>
-      <c r="G34" s="21" t="n"/>
-      <c r="H34" s="22" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>raw_name</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>인식된 약품명</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>varchar(300)</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="n"/>
+      <c r="G34" s="15" t="n"/>
+      <c r="H34" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I34" s="21" t="n"/>
-      <c r="J34" s="21" t="inlineStr">
-        <is>
-          <t>auto / needs_confirm / user_confirmed / unmatched / excluded(빼고 진행)</t>
-        </is>
-      </c>
-      <c r="K34" s="21" t="inlineStr">
+      <c r="I34" s="15" t="n"/>
+      <c r="J34" s="15" t="inlineStr">
+        <is>
+          <t>OCR이 읽은 원문 약품명</t>
+        </is>
+      </c>
+      <c r="K34" s="15" t="inlineStr">
         <is>
           <t>OC-02 · O-2 · O-3</t>
         </is>
       </c>
-      <c r="L34" s="22" t="inlineStr">
-        <is>
-          <t>수정</t>
-        </is>
-      </c>
-      <c r="M34" s="22" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N34" s="21" t="n"/>
+      <c r="L34" s="16" t="inlineStr">
+        <is>
+          <t>기존</t>
+        </is>
+      </c>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="N34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="20" t="inlineStr">
@@ -10331,17 +10660,17 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>dose_per_time</t>
+          <t>match_score</t>
         </is>
       </c>
       <c r="D35" s="21" t="inlineStr">
         <is>
-          <t>1회 투여량</t>
+          <t>매칭 점수</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
         <is>
-          <t>decimal(10,3)</t>
+          <t>decimal(5,4)</t>
         </is>
       </c>
       <c r="F35" s="22" t="n"/>
@@ -10383,28 +10712,32 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>times_per_day</t>
+          <t>match_status</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
         <is>
-          <t>1일 투여 횟수</t>
+          <t>매칭 상태</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="F36" s="22" t="n"/>
       <c r="G36" s="21" t="n"/>
       <c r="H36" s="22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I36" s="21" t="n"/>
-      <c r="J36" s="21" t="n"/>
+      <c r="J36" s="21" t="inlineStr">
+        <is>
+          <t>auto / needs_confirm / user_confirmed / unmatched / excluded(빼고 진행)</t>
+        </is>
+      </c>
       <c r="K36" s="21" t="inlineStr">
         <is>
           <t>OC-02 · O-2 · O-3</t>
@@ -10435,17 +10768,17 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>total_days</t>
+          <t>dose_per_time</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
         <is>
-          <t>총 투약일수</t>
+          <t>1회 투여량</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>decimal(10,3)</t>
         </is>
       </c>
       <c r="F37" s="22" t="n"/>
@@ -10487,17 +10820,17 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>times_per_day</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
         <is>
-          <t>복용 시점</t>
+          <t>1일 투여 횟수</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="F38" s="22" t="n"/>
@@ -10508,11 +10841,7 @@
         </is>
       </c>
       <c r="I38" s="21" t="n"/>
-      <c r="J38" s="21" t="inlineStr">
-        <is>
-          <t>아침 식후 등</t>
-        </is>
-      </c>
+      <c r="J38" s="21" t="n"/>
       <c r="K38" s="21" t="inlineStr">
         <is>
           <t>OC-02 · O-2 · O-3</t>
@@ -10543,17 +10872,17 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>guidance</t>
+          <t>total_days</t>
         </is>
       </c>
       <c r="D39" s="21" t="inlineStr">
         <is>
-          <t>약국 인쇄 복약 안내</t>
+          <t>총 투약일수</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="F39" s="22" t="n"/>
@@ -10564,194 +10893,178 @@
         </is>
       </c>
       <c r="I39" s="21" t="n"/>
-      <c r="J39" s="21" t="inlineStr">
+      <c r="J39" s="21" t="n"/>
+      <c r="K39" s="21" t="inlineStr">
+        <is>
+          <t>OC-02 · O-2 · O-3</t>
+        </is>
+      </c>
+      <c r="L39" s="22" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="M39" s="22" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="N39" s="21" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>prescription_items</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>처방 약품</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>복용 시점</t>
+        </is>
+      </c>
+      <c r="E40" s="21" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="F40" s="22" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I40" s="21" t="n"/>
+      <c r="J40" s="21" t="inlineStr">
+        <is>
+          <t>아침 식후 등</t>
+        </is>
+      </c>
+      <c r="K40" s="21" t="inlineStr">
+        <is>
+          <t>OC-02 · O-2 · O-3</t>
+        </is>
+      </c>
+      <c r="L40" s="22" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="M40" s="22" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="N40" s="21" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>prescription_items</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>처방 약품</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>guidance</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>약국 인쇄 복약 안내</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="F41" s="22" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I41" s="21" t="n"/>
+      <c r="J41" s="21" t="inlineStr">
         <is>
           <t>약봉투만 채움, 마스킹 후 저장. 없으면 null</t>
         </is>
       </c>
-      <c r="K39" s="21" t="inlineStr">
+      <c r="K41" s="21" t="inlineStr">
         <is>
           <t>OC-02 · O-2 · O-3</t>
         </is>
       </c>
-      <c r="L39" s="22" t="inlineStr">
+      <c r="L41" s="22" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M39" s="22" t="inlineStr">
+      <c r="M41" s="22" t="inlineStr">
         <is>
           <t>v1.3</t>
         </is>
       </c>
-      <c r="N39" s="21" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="23" t="inlineStr">
-        <is>
-          <t>prescription_item_candidates</t>
-        </is>
-      </c>
-      <c r="B40" s="24" t="inlineStr">
-        <is>
-          <t>약품 매칭 후보</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D40" s="24" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="E40" s="24" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F40" s="25" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G40" s="24" t="n"/>
-      <c r="H40" s="25" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I40" s="24" t="n"/>
-      <c r="J40" s="24" t="inlineStr">
-        <is>
-          <t>코드 구현 맞춤 — Tortoise는 복합 PK를 지원하지 않아 id를 PK로 두고 원래 PK 두 칸은 unique로</t>
-        </is>
-      </c>
-      <c r="K40" s="24" t="inlineStr">
-        <is>
-          <t>OC-02 · O-3</t>
-        </is>
-      </c>
-      <c r="L40" s="25" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M40" s="25" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N40" s="24" t="inlineStr">
-        <is>
-          <t>v1.0 신규 🟡 채연 확인 · OC-02 후보 목록. 매칭 정확도(1순위 적중률 · 5순위 내 포함률) 측정에 필요 · v1.3 id PK + (item_id, rank) UQ · v1.3 edi_code · item_seq 중 하나는 꼭 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="23" t="inlineStr">
-        <is>
-          <t>prescription_item_candidates</t>
-        </is>
-      </c>
-      <c r="B41" s="24" t="inlineStr">
-        <is>
-          <t>약품 매칭 후보</t>
-        </is>
-      </c>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>item_id</t>
-        </is>
-      </c>
-      <c r="D41" s="24" t="inlineStr">
-        <is>
-          <t>처방 약품 ID</t>
-        </is>
-      </c>
-      <c r="E41" s="24" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F41" s="25" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G41" s="24" t="inlineStr">
-        <is>
-          <t>prescription_items.id</t>
-        </is>
-      </c>
-      <c r="H41" s="25" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I41" s="24" t="n"/>
-      <c r="J41" s="24" t="n"/>
-      <c r="K41" s="24" t="inlineStr">
-        <is>
-          <t>OC-02 · O-3</t>
-        </is>
-      </c>
-      <c r="L41" s="25" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M41" s="25" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N41" s="24" t="n"/>
+      <c r="N41" s="21" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="23" t="inlineStr">
         <is>
-          <t>prescription_item_candidates</t>
+          <t>prescription_items</t>
         </is>
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>약품 매칭 후보</t>
+          <t>처방 약품</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>rank</t>
+          <t>suggested_by</t>
         </is>
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>순위</t>
+          <t>추천 출처</t>
         </is>
       </c>
       <c r="E42" s="24" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="F42" s="25" t="n"/>
       <c r="G42" s="24" t="n"/>
       <c r="H42" s="25" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I42" s="24" t="n"/>
       <c r="J42" s="24" t="inlineStr">
         <is>
-          <t>(item_id, rank) UQ</t>
+          <t>후보가 추천에서 왔을 때 similar(비슷한 이름) 또는 llm. 화면이 "추천"임을 알림</t>
         </is>
       </c>
       <c r="K42" s="24" t="inlineStr">
         <is>
-          <t>OC-02 · O-3</t>
+          <t>OC-02 / O-2</t>
         </is>
       </c>
       <c r="L42" s="25" t="inlineStr">
@@ -10761,7 +11074,7 @@
       </c>
       <c r="M42" s="25" t="inlineStr">
         <is>
-          <t>v1.3</t>
+          <t>v1.5</t>
         </is>
       </c>
       <c r="N42" s="24" t="n"/>
@@ -10779,38 +11092,34 @@
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>edi_code</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D43" s="24" t="inlineStr">
         <is>
-          <t>EDI 제품코드</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E43" s="24" t="inlineStr">
         <is>
-          <t>varchar(9)</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G43" s="24" t="inlineStr">
-        <is>
-          <t>drug_products.edi_code</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="n"/>
       <c r="H43" s="25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I43" s="24" t="n"/>
       <c r="J43" s="24" t="inlineStr">
         <is>
-          <t>급여목록에 있는 약 (없는 약은 item_seq) — 둘 중 하나는 꼭 있음</t>
+          <t>코드 구현 맞춤 — Tortoise는 복합 PK를 지원하지 않아 id를 PK로 두고 원래 PK 두 칸은 unique로</t>
         </is>
       </c>
       <c r="K43" s="24" t="inlineStr">
@@ -10828,7 +11137,11 @@
           <t>v1.3</t>
         </is>
       </c>
-      <c r="N43" s="24" t="n"/>
+      <c r="N43" s="24" t="inlineStr">
+        <is>
+          <t>v1.0 신규 🟡 채연 확인 · OC-02 후보 목록. 매칭 정확도(1순위 적중률 · 5순위 내 포함률) 측정에 필요 · v1.3 id PK + (item_id, rank) UQ · v1.3 edi_code · item_seq 중 하나는 꼭 있음</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="23" t="inlineStr">
@@ -10843,17 +11156,17 @@
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>item_seq</t>
+          <t>item_id</t>
         </is>
       </c>
       <c r="D44" s="24" t="inlineStr">
         <is>
-          <t>품목기준코드</t>
+          <t>처방 약품 ID</t>
         </is>
       </c>
       <c r="E44" s="24" t="inlineStr">
         <is>
-          <t>varchar(9)</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="F44" s="25" t="inlineStr">
@@ -10863,20 +11176,16 @@
       </c>
       <c r="G44" s="24" t="inlineStr">
         <is>
-          <t>drug_details.item_seq</t>
+          <t>prescription_items.id</t>
         </is>
       </c>
       <c r="H44" s="25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I44" s="24" t="n"/>
-      <c r="J44" s="24" t="inlineStr">
-        <is>
-          <t>급여목록에 없는 약 — edi_code가 없을 때 채움</t>
-        </is>
-      </c>
+      <c r="J44" s="24" t="n"/>
       <c r="K44" s="24" t="inlineStr">
         <is>
           <t>OC-02 · O-3</t>
@@ -10907,216 +11216,228 @@
       </c>
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>rank</t>
         </is>
       </c>
       <c r="D45" s="24" t="inlineStr">
         <is>
-          <t>매칭 점수</t>
+          <t>순위</t>
         </is>
       </c>
       <c r="E45" s="24" t="inlineStr">
         <is>
-          <t>decimal(5,4)</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="F45" s="25" t="n"/>
       <c r="G45" s="24" t="n"/>
       <c r="H45" s="25" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I45" s="24" t="n"/>
+      <c r="J45" s="24" t="inlineStr">
+        <is>
+          <t>(item_id, rank) UQ</t>
+        </is>
+      </c>
+      <c r="K45" s="24" t="inlineStr">
+        <is>
+          <t>OC-02 · O-3</t>
+        </is>
+      </c>
+      <c r="L45" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M45" s="25" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N45" s="24" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="23" t="inlineStr">
+        <is>
+          <t>prescription_item_candidates</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>약품 매칭 후보</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>edi_code</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>EDI 제품코드</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>varchar(9)</t>
+        </is>
+      </c>
+      <c r="F46" s="25" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G46" s="24" t="inlineStr">
+        <is>
+          <t>drug_products.edi_code</t>
+        </is>
+      </c>
+      <c r="H46" s="25" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I45" s="24" t="n"/>
-      <c r="J45" s="24" t="n"/>
-      <c r="K45" s="24" t="inlineStr">
+      <c r="I46" s="24" t="n"/>
+      <c r="J46" s="24" t="inlineStr">
+        <is>
+          <t>급여목록에 있는 약 (없는 약은 item_seq) — 둘 중 하나는 꼭 있음</t>
+        </is>
+      </c>
+      <c r="K46" s="24" t="inlineStr">
         <is>
           <t>OC-02 · O-3</t>
         </is>
       </c>
-      <c r="L45" s="25" t="inlineStr">
+      <c r="L46" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M45" s="25" t="inlineStr">
+      <c r="M46" s="25" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N46" s="24" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>prescription_item_candidates</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>약품 매칭 후보</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>item_seq</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>품목기준코드</t>
+        </is>
+      </c>
+      <c r="E47" s="24" t="inlineStr">
+        <is>
+          <t>varchar(9)</t>
+        </is>
+      </c>
+      <c r="F47" s="25" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G47" s="24" t="inlineStr">
+        <is>
+          <t>drug_details.item_seq</t>
+        </is>
+      </c>
+      <c r="H47" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I47" s="24" t="n"/>
+      <c r="J47" s="24" t="inlineStr">
+        <is>
+          <t>급여목록에 없는 약 — edi_code가 없을 때 채움</t>
+        </is>
+      </c>
+      <c r="K47" s="24" t="inlineStr">
+        <is>
+          <t>OC-02 · O-3</t>
+        </is>
+      </c>
+      <c r="L47" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M47" s="25" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N47" s="24" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="23" t="inlineStr">
+        <is>
+          <t>prescription_item_candidates</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>약품 매칭 후보</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>매칭 점수</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>decimal(5,4)</t>
+        </is>
+      </c>
+      <c r="F48" s="25" t="n"/>
+      <c r="G48" s="24" t="n"/>
+      <c r="H48" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I48" s="24" t="n"/>
+      <c r="J48" s="24" t="n"/>
+      <c r="K48" s="24" t="inlineStr">
+        <is>
+          <t>OC-02 · O-3</t>
+        </is>
+      </c>
+      <c r="L48" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M48" s="25" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N45" s="24" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="19" t="inlineStr">
-        <is>
-          <t>health_checkups</t>
-        </is>
-      </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>건강검진 (보류)</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D46" s="15" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="E46" s="15" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G46" s="15" t="n"/>
-      <c r="H46" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I46" s="15" t="n"/>
-      <c r="J46" s="15" t="n"/>
-      <c r="K46" s="15" t="inlineStr">
-        <is>
-          <t>REQ-015</t>
-        </is>
-      </c>
-      <c r="L46" s="16" t="inlineStr">
-        <is>
-          <t>기존</t>
-        </is>
-      </c>
-      <c r="M46" s="16" t="inlineStr">
-        <is>
-          <t>v0.1</t>
-        </is>
-      </c>
-      <c r="N46" s="15" t="inlineStr">
-        <is>
-          <t>보류 (REQ-015 · 멘토링 확인 후 결정)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="19" t="inlineStr">
-        <is>
-          <t>health_checkups</t>
-        </is>
-      </c>
-      <c r="B47" s="15" t="inlineStr">
-        <is>
-          <t>건강검진 (보류)</t>
-        </is>
-      </c>
-      <c r="C47" s="15" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="D47" s="15" t="inlineStr">
-        <is>
-          <t>사용자 ID</t>
-        </is>
-      </c>
-      <c r="E47" s="15" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F47" s="16" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G47" s="15" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
-      <c r="H47" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I47" s="15" t="n"/>
-      <c r="J47" s="15" t="n"/>
-      <c r="K47" s="15" t="inlineStr">
-        <is>
-          <t>REQ-015</t>
-        </is>
-      </c>
-      <c r="L47" s="16" t="inlineStr">
-        <is>
-          <t>기존</t>
-        </is>
-      </c>
-      <c r="M47" s="16" t="inlineStr">
-        <is>
-          <t>v0.1</t>
-        </is>
-      </c>
-      <c r="N47" s="15" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="19" t="inlineStr">
-        <is>
-          <t>health_checkups</t>
-        </is>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>건강검진 (보류)</t>
-        </is>
-      </c>
-      <c r="C48" s="15" t="inlineStr">
-        <is>
-          <t>checkup_date</t>
-        </is>
-      </c>
-      <c r="D48" s="15" t="inlineStr">
-        <is>
-          <t>검진일</t>
-        </is>
-      </c>
-      <c r="E48" s="15" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="F48" s="16" t="n"/>
-      <c r="G48" s="15" t="n"/>
-      <c r="H48" s="16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I48" s="15" t="n"/>
-      <c r="J48" s="15" t="n"/>
-      <c r="K48" s="15" t="inlineStr">
-        <is>
-          <t>REQ-015</t>
-        </is>
-      </c>
-      <c r="L48" s="16" t="inlineStr">
-        <is>
-          <t>기존</t>
-        </is>
-      </c>
-      <c r="M48" s="16" t="inlineStr">
-        <is>
-          <t>v0.1</t>
-        </is>
-      </c>
-      <c r="N48" s="15" t="n"/>
+      <c r="N48" s="24" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="19" t="inlineStr">
@@ -11131,24 +11452,28 @@
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>ocr_raw_text</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>OCR 원문</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F49" s="16" t="n"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F49" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G49" s="15" t="n"/>
       <c r="H49" s="16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I49" s="15" t="n"/>
@@ -11168,7 +11493,11 @@
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N49" s="15" t="n"/>
+      <c r="N49" s="15" t="inlineStr">
+        <is>
+          <t>보류 (REQ-015 · 멘토링 확인 후 결정)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="19" t="inlineStr">
@@ -11183,31 +11512,35 @@
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>사용자 ID</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="F50" s="16" t="n"/>
-      <c r="G50" s="15" t="n"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G50" s="15" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
       <c r="H50" s="16" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I50" s="15" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I50" s="15" t="n"/>
       <c r="J50" s="15" t="n"/>
       <c r="K50" s="15" t="inlineStr">
         <is>
@@ -11229,38 +11562,34 @@
     <row r="51">
       <c r="A51" s="19" t="inlineStr">
         <is>
-          <t>checkup_results</t>
+          <t>health_checkups</t>
         </is>
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>건강검진 결과 (보류)</t>
+          <t>건강검진 (보류)</t>
         </is>
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>checkup_date</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>검진일</t>
         </is>
       </c>
       <c r="E51" s="15" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F51" s="16" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F51" s="16" t="n"/>
       <c r="G51" s="15" t="n"/>
       <c r="H51" s="16" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I51" s="15" t="n"/>
@@ -11280,51 +11609,39 @@
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N51" s="15" t="inlineStr">
-        <is>
-          <t>보류 (REQ-015)</t>
-        </is>
-      </c>
+      <c r="N51" s="15" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="19" t="inlineStr">
         <is>
-          <t>checkup_results</t>
+          <t>health_checkups</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>건강검진 결과 (보류)</t>
+          <t>건강검진 (보류)</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>checkup_id</t>
+          <t>ocr_raw_text</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>건강검진 ID</t>
+          <t>OCR 원문</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F52" s="16" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G52" s="15" t="inlineStr">
-        <is>
-          <t>health_checkups.id</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="n"/>
+      <c r="G52" s="15" t="n"/>
       <c r="H52" s="16" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I52" s="15" t="n"/>
@@ -11347,171 +11664,347 @@
       <c r="N52" s="15" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="20" t="inlineStr">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>health_checkups</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>건강검진 (보류)</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>생성 일시</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F53" s="16" t="n"/>
+      <c r="G53" s="15" t="n"/>
+      <c r="H53" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I53" s="15" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="J53" s="15" t="n"/>
+      <c r="K53" s="15" t="inlineStr">
+        <is>
+          <t>REQ-015</t>
+        </is>
+      </c>
+      <c r="L53" s="16" t="inlineStr">
+        <is>
+          <t>기존</t>
+        </is>
+      </c>
+      <c r="M53" s="16" t="inlineStr">
+        <is>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="N53" s="15" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>checkup_results</t>
         </is>
       </c>
-      <c r="B53" s="21" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>건강검진 결과 (보류)</t>
         </is>
       </c>
-      <c r="C53" s="21" t="inlineStr">
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G54" s="15" t="n"/>
+      <c r="H54" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I54" s="15" t="n"/>
+      <c r="J54" s="15" t="n"/>
+      <c r="K54" s="15" t="inlineStr">
+        <is>
+          <t>REQ-015</t>
+        </is>
+      </c>
+      <c r="L54" s="16" t="inlineStr">
+        <is>
+          <t>기존</t>
+        </is>
+      </c>
+      <c r="M54" s="16" t="inlineStr">
+        <is>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="N54" s="15" t="inlineStr">
+        <is>
+          <t>보류 (REQ-015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>checkup_results</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>건강검진 결과 (보류)</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>checkup_id</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>건강검진 ID</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F55" s="16" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G55" s="15" t="inlineStr">
+        <is>
+          <t>health_checkups.id</t>
+        </is>
+      </c>
+      <c r="H55" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I55" s="15" t="n"/>
+      <c r="J55" s="15" t="n"/>
+      <c r="K55" s="15" t="inlineStr">
+        <is>
+          <t>REQ-015</t>
+        </is>
+      </c>
+      <c r="L55" s="16" t="inlineStr">
+        <is>
+          <t>기존</t>
+        </is>
+      </c>
+      <c r="M55" s="16" t="inlineStr">
+        <is>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="N55" s="15" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>checkup_results</t>
+        </is>
+      </c>
+      <c r="B56" s="21" t="inlineStr">
+        <is>
+          <t>건강검진 결과 (보류)</t>
+        </is>
+      </c>
+      <c r="C56" s="21" t="inlineStr">
         <is>
           <t>item_code</t>
         </is>
       </c>
-      <c r="D53" s="21" t="inlineStr">
+      <c r="D56" s="21" t="inlineStr">
         <is>
           <t>검사 항목 코드</t>
         </is>
       </c>
-      <c r="E53" s="21" t="inlineStr">
+      <c r="E56" s="21" t="inlineStr">
         <is>
           <t>varchar(8)</t>
         </is>
       </c>
-      <c r="F53" s="22" t="inlineStr">
+      <c r="F56" s="22" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="G53" s="21" t="inlineStr">
+      <c r="G56" s="21" t="inlineStr">
         <is>
           <t>checkup_items.code</t>
         </is>
       </c>
-      <c r="H53" s="22" t="inlineStr">
+      <c r="H56" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I53" s="21" t="n"/>
-      <c r="J53" s="21" t="n"/>
-      <c r="K53" s="21" t="inlineStr">
+      <c r="I56" s="21" t="n"/>
+      <c r="J56" s="21" t="n"/>
+      <c r="K56" s="21" t="inlineStr">
         <is>
           <t>REQ-015</t>
         </is>
       </c>
-      <c r="L53" s="22" t="inlineStr">
+      <c r="L56" s="22" t="inlineStr">
         <is>
           <t>수정</t>
         </is>
       </c>
-      <c r="M53" s="22" t="inlineStr">
+      <c r="M56" s="22" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N53" s="21" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="20" t="inlineStr">
+      <c r="N56" s="21" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="20" t="inlineStr">
         <is>
           <t>checkup_results</t>
         </is>
       </c>
-      <c r="B54" s="21" t="inlineStr">
+      <c r="B57" s="21" t="inlineStr">
         <is>
           <t>건강검진 결과 (보류)</t>
         </is>
       </c>
-      <c r="C54" s="21" t="inlineStr">
+      <c r="C57" s="21" t="inlineStr">
         <is>
           <t>value_num</t>
         </is>
       </c>
-      <c r="D54" s="21" t="inlineStr">
+      <c r="D57" s="21" t="inlineStr">
         <is>
           <t>결과 수치</t>
         </is>
       </c>
-      <c r="E54" s="21" t="inlineStr">
+      <c r="E57" s="21" t="inlineStr">
         <is>
           <t>decimal(12,3)</t>
         </is>
       </c>
-      <c r="F54" s="22" t="n"/>
-      <c r="G54" s="21" t="n"/>
-      <c r="H54" s="22" t="inlineStr">
+      <c r="F57" s="22" t="n"/>
+      <c r="G57" s="21" t="n"/>
+      <c r="H57" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I54" s="21" t="n"/>
-      <c r="J54" s="21" t="n"/>
-      <c r="K54" s="21" t="inlineStr">
+      <c r="I57" s="21" t="n"/>
+      <c r="J57" s="21" t="n"/>
+      <c r="K57" s="21" t="inlineStr">
         <is>
           <t>REQ-015</t>
         </is>
       </c>
-      <c r="L54" s="22" t="inlineStr">
+      <c r="L57" s="22" t="inlineStr">
         <is>
           <t>수정</t>
         </is>
       </c>
-      <c r="M54" s="22" t="inlineStr">
+      <c r="M57" s="22" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N54" s="21" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="20" t="inlineStr">
+      <c r="N57" s="21" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="inlineStr">
         <is>
           <t>checkup_results</t>
         </is>
       </c>
-      <c r="B55" s="21" t="inlineStr">
+      <c r="B58" s="21" t="inlineStr">
         <is>
           <t>건강검진 결과 (보류)</t>
         </is>
       </c>
-      <c r="C55" s="21" t="inlineStr">
+      <c r="C58" s="21" t="inlineStr">
         <is>
           <t>value_text</t>
         </is>
       </c>
-      <c r="D55" s="21" t="inlineStr">
+      <c r="D58" s="21" t="inlineStr">
         <is>
           <t>결과 판정</t>
         </is>
       </c>
-      <c r="E55" s="21" t="inlineStr">
+      <c r="E58" s="21" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="F55" s="22" t="n"/>
-      <c r="G55" s="21" t="n"/>
-      <c r="H55" s="22" t="inlineStr">
+      <c r="F58" s="22" t="n"/>
+      <c r="G58" s="21" t="n"/>
+      <c r="H58" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I55" s="21" t="n"/>
-      <c r="J55" s="21" t="n"/>
-      <c r="K55" s="21" t="inlineStr">
+      <c r="I58" s="21" t="n"/>
+      <c r="J58" s="21" t="n"/>
+      <c r="K58" s="21" t="inlineStr">
         <is>
           <t>REQ-015</t>
         </is>
       </c>
-      <c r="L55" s="22" t="inlineStr">
+      <c r="L58" s="22" t="inlineStr">
         <is>
           <t>수정</t>
         </is>
       </c>
-      <c r="M55" s="22" t="inlineStr">
+      <c r="M58" s="22" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N55" s="21" t="n"/>
+      <c r="N58" s="21" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N53"/>
+  <autoFilter ref="A4:N56"/>
   <dataValidations count="3">
     <dataValidation sqref="H5:H300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
@@ -11533,7 +12026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11566,6 +12059,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -13251,60 +13745,60 @@
       <c r="N32" s="24" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>guides</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>복약 · 생활습관 안내문</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="E33" s="15" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G33" s="15" t="inlineStr"/>
-      <c r="H33" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I33" s="15" t="inlineStr"/>
-      <c r="J33" s="15" t="inlineStr"/>
-      <c r="K33" s="15" t="inlineStr">
-        <is>
-          <t>RG-04 · RG-05 · R-4 · R-10</t>
-        </is>
-      </c>
-      <c r="L33" s="16" t="inlineStr">
-        <is>
-          <t>기존</t>
-        </is>
-      </c>
-      <c r="M33" s="16" t="inlineStr">
-        <is>
-          <t>v0.1</t>
-        </is>
-      </c>
-      <c r="N33" s="15" t="inlineStr"/>
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>analysis_warnings</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>안전성 경고</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>경고 세부</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="F33" s="25" t="n"/>
+      <c r="G33" s="24" t="n"/>
+      <c r="H33" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="n"/>
+      <c r="J33" s="24" t="inlineStr">
+        <is>
+          <t>약이 3개 이상인 경고의 전체 항목 번호, 성분, 근거 구분</t>
+        </is>
+      </c>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>RG-02 / R-4</t>
+        </is>
+      </c>
+      <c r="L33" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M33" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N33" s="24" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
@@ -13319,12 +13813,12 @@
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>analysis_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>분석 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
@@ -13334,14 +13828,10 @@
       </c>
       <c r="F34" s="16" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G34" s="15" t="inlineStr">
-        <is>
-          <t>analyses.id</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr"/>
       <c r="H34" s="16" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13367,172 +13857,176 @@
       <c r="N34" s="15" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>guides</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>복약 · 생활습관 안내문</t>
         </is>
       </c>
-      <c r="C35" s="21" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>analysis_id</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>분석 ID</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>analyses.id</t>
+        </is>
+      </c>
+      <c r="H35" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I35" s="15" t="inlineStr"/>
+      <c r="J35" s="15" t="inlineStr"/>
+      <c r="K35" s="15" t="inlineStr">
+        <is>
+          <t>RG-04 · RG-05 · R-4 · R-10</t>
+        </is>
+      </c>
+      <c r="L35" s="16" t="inlineStr">
+        <is>
+          <t>기존</t>
+        </is>
+      </c>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="N35" s="15" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>guides</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>복약 · 생활습관 안내문</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>section</t>
         </is>
       </c>
-      <c r="D35" s="21" t="inlineStr">
+      <c r="D36" s="21" t="inlineStr">
         <is>
           <t>안내 구분</t>
         </is>
       </c>
-      <c r="E35" s="21" t="inlineStr">
+      <c r="E36" s="21" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr"/>
-      <c r="G35" s="21" t="inlineStr"/>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr"/>
+      <c r="G36" s="21" t="inlineStr"/>
+      <c r="H36" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I35" s="21" t="inlineStr"/>
-      <c r="J35" s="21" t="inlineStr">
+      <c r="I36" s="21" t="inlineStr"/>
+      <c r="J36" s="21" t="inlineStr">
         <is>
           <t>medication / lifestyle</t>
         </is>
       </c>
-      <c r="K35" s="21" t="inlineStr">
+      <c r="K36" s="21" t="inlineStr">
         <is>
           <t>RG-04 · RG-05 · R-4 · R-10</t>
         </is>
       </c>
-      <c r="L35" s="22" t="inlineStr">
+      <c r="L36" s="22" t="inlineStr">
         <is>
           <t>수정</t>
         </is>
       </c>
-      <c r="M35" s="22" t="inlineStr">
+      <c r="M36" s="22" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N35" s="21" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="23" t="inlineStr">
+      <c r="N36" s="21" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>guides</t>
         </is>
       </c>
-      <c r="B36" s="24" t="inlineStr">
+      <c r="B37" s="24" t="inlineStr">
         <is>
           <t>복약 · 생활습관 안내문</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C37" s="24" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="D36" s="24" t="inlineStr">
+      <c r="D37" s="24" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="E37" s="24" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="F36" s="25" t="inlineStr"/>
-      <c r="G36" s="24" t="inlineStr"/>
-      <c r="H36" s="25" t="inlineStr">
+      <c r="F37" s="25" t="inlineStr"/>
+      <c r="G37" s="24" t="inlineStr"/>
+      <c r="H37" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I36" s="24" t="inlineStr"/>
-      <c r="J36" s="24" t="inlineStr">
+      <c r="I37" s="24" t="inlineStr"/>
+      <c r="J37" s="24" t="inlineStr">
         <is>
           <t>done / failed (부분 결과 RG-01-E1 → RG-04 · RG-05 "만들지 못했어요")</t>
         </is>
       </c>
-      <c r="K36" s="24" t="inlineStr">
+      <c r="K37" s="24" t="inlineStr">
         <is>
           <t>RG-04 · RG-05 · R-4 · R-10</t>
         </is>
       </c>
-      <c r="L36" s="25" t="inlineStr">
+      <c r="L37" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M36" s="25" t="inlineStr">
+      <c r="M37" s="25" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N36" s="24" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="20" t="inlineStr">
-        <is>
-          <t>guides</t>
-        </is>
-      </c>
-      <c r="B37" s="21" t="inlineStr">
-        <is>
-          <t>복약 · 생활습관 안내문</t>
-        </is>
-      </c>
-      <c r="C37" s="21" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="D37" s="21" t="inlineStr">
-        <is>
-          <t>안내 내용 (JSON)</t>
-        </is>
-      </c>
-      <c r="E37" s="21" t="inlineStr">
-        <is>
-          <t>jsonb</t>
-        </is>
-      </c>
-      <c r="F37" s="22" t="inlineStr"/>
-      <c r="G37" s="21" t="inlineStr"/>
-      <c r="H37" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I37" s="21" t="inlineStr"/>
-      <c r="J37" s="21" t="inlineStr">
-        <is>
-          <t>항목 고정 JSON (약별 purpose · howToTake · caution · source) — 결과 일관성 NFR-030</t>
-        </is>
-      </c>
-      <c r="K37" s="21" t="inlineStr">
-        <is>
-          <t>RG-04 · RG-05 · R-4 · R-10</t>
-        </is>
-      </c>
-      <c r="L37" s="22" t="inlineStr">
-        <is>
-          <t>수정</t>
-        </is>
-      </c>
-      <c r="M37" s="22" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N37" s="21" t="inlineStr"/>
+      <c r="N37" s="24" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
@@ -13547,17 +14041,17 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>prompt_ver</t>
+          <t>content</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
         <is>
-          <t>프롬프트 버전</t>
+          <t>안내 내용 (JSON)</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr"/>
@@ -13568,7 +14062,11 @@
         </is>
       </c>
       <c r="I38" s="21" t="inlineStr"/>
-      <c r="J38" s="21" t="inlineStr"/>
+      <c r="J38" s="21" t="inlineStr">
+        <is>
+          <t>항목 고정 JSON (약별 purpose · howToTake · caution · source) — 결과 일관성 NFR-030</t>
+        </is>
+      </c>
       <c r="K38" s="21" t="inlineStr">
         <is>
           <t>RG-04 · RG-05 · R-4 · R-10</t>
@@ -13599,17 +14097,17 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>model_name</t>
+          <t>prompt_ver</t>
         </is>
       </c>
       <c r="D39" s="21" t="inlineStr">
         <is>
-          <t>모델 이름</t>
+          <t>프롬프트 버전</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="F39" s="22" t="inlineStr"/>
@@ -13651,17 +14149,17 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>tts_url</t>
+          <t>model_name</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
         <is>
-          <t>음성 파일 주소</t>
+          <t>모델 이름</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
-          <t>varchar(500)</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr"/>
@@ -13672,126 +14170,122 @@
         </is>
       </c>
       <c r="I40" s="21" t="inlineStr"/>
-      <c r="J40" s="21" t="inlineStr">
+      <c r="J40" s="21" t="inlineStr"/>
+      <c r="K40" s="21" t="inlineStr">
+        <is>
+          <t>RG-04 · RG-05 · R-4 · R-10</t>
+        </is>
+      </c>
+      <c r="L40" s="22" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="M40" s="22" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="N40" s="21" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>guides</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>복약 · 생활습관 안내문</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>tts_url</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>음성 파일 주소</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="inlineStr">
+        <is>
+          <t>varchar(500)</t>
+        </is>
+      </c>
+      <c r="F41" s="22" t="inlineStr"/>
+      <c r="G41" s="21" t="inlineStr"/>
+      <c r="H41" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I41" s="21" t="inlineStr"/>
+      <c r="J41" s="21" t="inlineStr">
         <is>
           <t>선택 구현 (REQ-100)</t>
         </is>
       </c>
-      <c r="K40" s="21" t="inlineStr">
+      <c r="K41" s="21" t="inlineStr">
         <is>
           <t>RG-04 · RG-05 · R-4 · R-10</t>
         </is>
       </c>
-      <c r="L40" s="22" t="inlineStr">
+      <c r="L41" s="22" t="inlineStr">
         <is>
           <t>수정</t>
         </is>
       </c>
-      <c r="M40" s="22" t="inlineStr">
+      <c r="M41" s="22" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N40" s="21" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t>guides</t>
-        </is>
-      </c>
-      <c r="B41" s="15" t="inlineStr">
-        <is>
-          <t>복약 · 생활습관 안내문</t>
-        </is>
-      </c>
-      <c r="C41" s="15" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>생성 일시</t>
-        </is>
-      </c>
-      <c r="E41" s="15" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="F41" s="16" t="inlineStr"/>
-      <c r="G41" s="15" t="inlineStr"/>
-      <c r="H41" s="16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I41" s="15" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="J41" s="15" t="inlineStr"/>
-      <c r="K41" s="15" t="inlineStr">
-        <is>
-          <t>RG-04 · RG-05 · R-4 · R-10</t>
-        </is>
-      </c>
-      <c r="L41" s="16" t="inlineStr">
-        <is>
-          <t>기존</t>
-        </is>
-      </c>
-      <c r="M41" s="16" t="inlineStr">
-        <is>
-          <t>v0.1</t>
-        </is>
-      </c>
-      <c r="N41" s="15" t="inlineStr"/>
+      <c r="N41" s="21" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>feedbacks</t>
+          <t>guides</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>안내문 피드백</t>
+          <t>복약 · 생활습관 안내문</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>생성 일시</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr"/>
       <c r="G42" s="15" t="inlineStr"/>
       <c r="H42" s="16" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I42" s="15" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="J42" s="15" t="inlineStr"/>
       <c r="K42" s="15" t="inlineStr">
         <is>
-          <t>RG-04 · R-9</t>
+          <t>RG-04 · RG-05 · R-4 · R-10</t>
         </is>
       </c>
       <c r="L42" s="16" t="inlineStr">
@@ -13819,12 +14313,12 @@
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
-          <t>guide_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>안내문 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E43" s="15" t="inlineStr">
@@ -13834,14 +14328,10 @@
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G43" s="15" t="inlineStr">
-        <is>
-          <t>guides.id</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G43" s="15" t="inlineStr"/>
       <c r="H43" s="16" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13879,12 +14369,12 @@
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>guide_id</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>사용자 ID</t>
+          <t>안내문 ID</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
@@ -13899,7 +14389,7 @@
       </c>
       <c r="G44" s="15" t="inlineStr">
         <is>
-          <t>users.id</t>
+          <t>guides.id</t>
         </is>
       </c>
       <c r="H44" s="16" t="inlineStr">
@@ -13927,112 +14417,120 @@
       <c r="N44" s="15" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>feedbacks</t>
         </is>
       </c>
-      <c r="B45" s="21" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>안내문 피드백</t>
         </is>
       </c>
-      <c r="C45" s="21" t="inlineStr">
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>사용자 ID</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="H45" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I45" s="15" t="inlineStr"/>
+      <c r="J45" s="15" t="inlineStr"/>
+      <c r="K45" s="15" t="inlineStr">
+        <is>
+          <t>RG-04 · R-9</t>
+        </is>
+      </c>
+      <c r="L45" s="16" t="inlineStr">
+        <is>
+          <t>기존</t>
+        </is>
+      </c>
+      <c r="M45" s="16" t="inlineStr">
+        <is>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="N45" s="15" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>feedbacks</t>
+        </is>
+      </c>
+      <c r="B46" s="21" t="inlineStr">
+        <is>
+          <t>안내문 피드백</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="D45" s="21" t="inlineStr">
+      <c r="D46" s="21" t="inlineStr">
         <is>
           <t>평가</t>
         </is>
       </c>
-      <c r="E45" s="21" t="inlineStr">
+      <c r="E46" s="21" t="inlineStr">
         <is>
           <t>smallint</t>
         </is>
       </c>
-      <c r="F45" s="22" t="inlineStr"/>
-      <c r="G45" s="21" t="inlineStr"/>
-      <c r="H45" s="22" t="inlineStr">
+      <c r="F46" s="22" t="inlineStr"/>
+      <c r="G46" s="21" t="inlineStr"/>
+      <c r="H46" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I45" s="21" t="inlineStr"/>
-      <c r="J45" s="21" t="inlineStr">
+      <c r="I46" s="21" t="inlineStr"/>
+      <c r="J46" s="21" t="inlineStr">
         <is>
           <t>1 = 도움됐어요 / -1 = 도움 안 됐어요</t>
         </is>
       </c>
-      <c r="K45" s="21" t="inlineStr">
+      <c r="K46" s="21" t="inlineStr">
         <is>
           <t>RG-04 · R-9</t>
         </is>
       </c>
-      <c r="L45" s="22" t="inlineStr">
+      <c r="L46" s="22" t="inlineStr">
         <is>
           <t>수정</t>
         </is>
       </c>
-      <c r="M45" s="22" t="inlineStr">
+      <c r="M46" s="22" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N45" s="21" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="19" t="inlineStr">
-        <is>
-          <t>feedbacks</t>
-        </is>
-      </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>안내문 피드백</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="D46" s="15" t="inlineStr">
-        <is>
-          <t>의견</t>
-        </is>
-      </c>
-      <c r="E46" s="15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="inlineStr"/>
-      <c r="G46" s="15" t="inlineStr"/>
-      <c r="H46" s="16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I46" s="15" t="inlineStr"/>
-      <c r="J46" s="15" t="inlineStr"/>
-      <c r="K46" s="15" t="inlineStr">
-        <is>
-          <t>RG-04 · R-9</t>
-        </is>
-      </c>
-      <c r="L46" s="16" t="inlineStr">
-        <is>
-          <t>기존</t>
-        </is>
-      </c>
-      <c r="M46" s="16" t="inlineStr">
-        <is>
-          <t>v0.1</t>
-        </is>
-      </c>
-      <c r="N46" s="15" t="inlineStr"/>
+      <c r="N46" s="21" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="19" t="inlineStr">
@@ -14047,17 +14545,17 @@
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>의견</t>
         </is>
       </c>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F47" s="16" t="inlineStr"/>
@@ -14067,11 +14565,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I47" s="15" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+      <c r="I47" s="15" t="inlineStr"/>
       <c r="J47" s="15" t="inlineStr"/>
       <c r="K47" s="15" t="inlineStr">
         <is>
@@ -14093,66 +14587,58 @@
     <row r="48">
       <c r="A48" s="19" t="inlineStr">
         <is>
-          <t>drug_guides</t>
+          <t>feedbacks</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>약 안내문 (사전 저장)</t>
+          <t>안내문 피드백</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>edi_code</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>약 코드</t>
+          <t>생성 일시</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>varchar(9)</t>
-        </is>
-      </c>
-      <c r="F48" s="16" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G48" s="15" t="n"/>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F48" s="16" t="inlineStr"/>
+      <c r="G48" s="15" t="inlineStr"/>
       <c r="H48" s="16" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I48" s="15" t="n"/>
-      <c r="J48" s="15" t="inlineStr">
-        <is>
-          <t>약제급여목록 제품코드(EDI). 약 1개 = 1행. 급여목록에 없는 약은 행이 없음</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="J48" s="15" t="inlineStr"/>
       <c r="K48" s="15" t="inlineStr">
         <is>
-          <t>RG-04 · R-4 · 챗봇 출처</t>
+          <t>RG-04 · R-9</t>
         </is>
       </c>
       <c r="L48" s="16" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>기존</t>
         </is>
       </c>
       <c r="M48" s="16" t="inlineStr">
         <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N48" s="15" t="inlineStr">
-        <is>
-          <t>멘토링 4회차(10/13) · 10/14 팀 합의. 약 단위로 미리 만들어 두고 사람이 확인한 것만 분석에 씀. 약 1개 = 1행 (약효분류 표로 만든 안내문과 허가정보 문장이 같은 표에 들어감)</t>
-        </is>
-      </c>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="N48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="19" t="inlineStr">
@@ -14167,20 +14653,24 @@
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>edi_code</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>안내 내용 (JSON)</t>
+          <t>약 코드</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>jsonb</t>
-        </is>
-      </c>
-      <c r="F49" s="16" t="n"/>
+          <t>varchar(9)</t>
+        </is>
+      </c>
+      <c r="F49" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G49" s="15" t="n"/>
       <c r="H49" s="16" t="inlineStr">
         <is>
@@ -14190,7 +14680,7 @@
       <c r="I49" s="15" t="n"/>
       <c r="J49" s="15" t="inlineStr">
         <is>
-          <t>category · purpose · caution(문장을 줄바꿈으로 이은 문자열) · cautions(문장 배열) · source. 먹는 법은 처방마다 달라 여기 두지 않음</t>
+          <t>약제급여목록 제품코드(EDI). 약 1개 = 1행. 급여목록에 없는 약은 행이 없음</t>
         </is>
       </c>
       <c r="K49" s="15" t="inlineStr">
@@ -14208,7 +14698,11 @@
           <t>v1.3</t>
         </is>
       </c>
-      <c r="N49" s="15" t="n"/>
+      <c r="N49" s="15" t="inlineStr">
+        <is>
+          <t>멘토링 4회차(10/13) · 10/14 팀 합의. 약 단위로 미리 만들어 두고 사람이 확인한 것만 분석에 씀. 약 1개 = 1행 (약효분류 표로 만든 안내문과 허가정보 문장이 같은 표에 들어감)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="19" t="inlineStr">
@@ -14223,12 +14717,12 @@
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>evidence_ids</t>
+          <t>content</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>근거 목록</t>
+          <t>안내 내용 (JSON)</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
@@ -14240,13 +14734,13 @@
       <c r="G50" s="15" t="n"/>
       <c r="H50" s="16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I50" s="15" t="n"/>
       <c r="J50" s="15" t="inlineStr">
         <is>
-          <t>[{kind: hira_class | drug_details, key, label, field(문장 번호), use(purpose · caution1~3), text(원문 문장)}] — 챗봇이 출처를 붙일 때 그대로 씀</t>
+          <t>category · purpose · caution(문장을 줄바꿈으로 이은 문자열) · cautions(문장 배열) · source. 먹는 법은 처방마다 달라 여기 두지 않음</t>
         </is>
       </c>
       <c r="K50" s="15" t="inlineStr">
@@ -14279,17 +14773,17 @@
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>prompt_ver</t>
+          <t>evidence_ids</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>프롬프트 버전</t>
+          <t>근거 목록</t>
         </is>
       </c>
       <c r="E51" s="15" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="F51" s="16" t="n"/>
@@ -14302,7 +14796,7 @@
       <c r="I51" s="15" t="n"/>
       <c r="J51" s="15" t="inlineStr">
         <is>
-          <t>규칙 표로 만든 것은 rule-v1, AI 문장은 med-v8</t>
+          <t>[{kind: hira_class | drug_details, key, label, field(문장 번호), use(purpose · caution1~3), text(원문 문장)}] — 챗봇이 출처를 붙일 때 그대로 씀</t>
         </is>
       </c>
       <c r="K51" s="15" t="inlineStr">
@@ -14335,17 +14829,17 @@
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>model_name</t>
+          <t>prompt_ver</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>모델 이름</t>
+          <t>프롬프트 버전</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="F52" s="16" t="n"/>
@@ -14358,7 +14852,7 @@
       <c r="I52" s="15" t="n"/>
       <c r="J52" s="15" t="inlineStr">
         <is>
-          <t>AI 없이 규칙 표로 만든 안내문은 null. 값이 있으면 허가정보 문장(AI가 쓰고 규칙으로 걸러 냄)</t>
+          <t>규칙 표로 만든 것은 rule-v1, AI 문장은 med-v8</t>
         </is>
       </c>
       <c r="K52" s="15" t="inlineStr">
@@ -14391,34 +14885,30 @@
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
-          <t>review_status</t>
+          <t>model_name</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>확인 상태</t>
+          <t>모델 이름</t>
         </is>
       </c>
       <c r="E53" s="15" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="F53" s="16" t="n"/>
       <c r="G53" s="15" t="n"/>
       <c r="H53" s="16" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I53" s="15" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I53" s="15" t="n"/>
       <c r="J53" s="15" t="inlineStr">
         <is>
-          <t>draft / approved / rejected — 분석 때는 approved만 보여 줌 (멘토링 4회차 · 사람 확인 필수)</t>
+          <t>AI 없이 규칙 표로 만든 안내문은 null. 값이 있으면 허가정보 문장(AI가 쓰고 규칙으로 걸러 냄)</t>
         </is>
       </c>
       <c r="K53" s="15" t="inlineStr">
@@ -14451,28 +14941,36 @@
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>reviewed_by</t>
+          <t>review_status</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>확인한 사람</t>
+          <t>확인 상태</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="F54" s="16" t="n"/>
       <c r="G54" s="15" t="n"/>
       <c r="H54" s="16" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I54" s="15" t="n"/>
-      <c r="J54" s="15" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I54" s="15" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="J54" s="15" t="inlineStr">
+        <is>
+          <t>draft / approved / rejected — 분석 때는 approved만 보여 줌 (멘토링 4회차 · 사람 확인 필수)</t>
+        </is>
+      </c>
       <c r="K54" s="15" t="inlineStr">
         <is>
           <t>RG-04 · R-4 · 챗봇 출처</t>
@@ -14503,17 +15001,17 @@
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
-          <t>reviewed_at</t>
+          <t>reviewed_by</t>
         </is>
       </c>
       <c r="D55" s="15" t="inlineStr">
         <is>
-          <t>확인 일시</t>
+          <t>확인한 사람</t>
         </is>
       </c>
       <c r="E55" s="15" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="F55" s="16" t="n"/>
@@ -14555,12 +15053,12 @@
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>reviewed_at</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>확인 일시</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
@@ -14575,11 +15073,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I56" s="15" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+      <c r="I56" s="15" t="n"/>
       <c r="J56" s="15" t="n"/>
       <c r="K56" s="15" t="inlineStr">
         <is>
@@ -14611,12 +15105,12 @@
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D57" s="15" t="inlineStr">
         <is>
-          <t>수정 일시</t>
+          <t>생성 일시</t>
         </is>
       </c>
       <c r="E57" s="15" t="inlineStr">
@@ -14654,8 +15148,64 @@
       </c>
       <c r="N57" s="15" t="n"/>
     </row>
+    <row r="58">
+      <c r="A58" s="19" t="inlineStr">
+        <is>
+          <t>drug_guides</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>약 안내문 (사전 저장)</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>수정 일시</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F58" s="16" t="n"/>
+      <c r="G58" s="15" t="n"/>
+      <c r="H58" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I58" s="15" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="J58" s="15" t="n"/>
+      <c r="K58" s="15" t="inlineStr">
+        <is>
+          <t>RG-04 · R-4 · 챗봇 출처</t>
+        </is>
+      </c>
+      <c r="L58" s="16" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M58" s="16" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N58" s="15" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:N47"/>
+  <autoFilter ref="A4:N48"/>
   <dataValidations count="3">
     <dataValidation sqref="H5:H300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
@@ -14677,7 +15227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14710,6 +15260,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -15355,60 +15906,60 @@
       <c r="N14" s="24" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>chat_messages</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>대화 메시지</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G15" s="15" t="n"/>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="n"/>
-      <c r="K15" s="15" t="inlineStr">
-        <is>
-          <t>CB-01 · H-2 · H-3</t>
-        </is>
-      </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>기존</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="inlineStr">
-        <is>
-          <t>v0.1</t>
-        </is>
-      </c>
-      <c r="N15" s="15" t="n"/>
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>chat_sessions</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>대화</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>safety_mode_until</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>안전 모드 종료 시각</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="n"/>
+      <c r="G15" s="24" t="n"/>
+      <c r="H15" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="n"/>
+      <c r="J15" s="24" t="inlineStr">
+        <is>
+          <t>자해 표현 뒤 안전 모드가 끝나는 시각. null이면 안전 모드 아님 (이슈 #88)</t>
+        </is>
+      </c>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>CB-01~03 / H-1</t>
+        </is>
+      </c>
+      <c r="L15" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M15" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N15" s="24" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
@@ -15423,12 +15974,12 @@
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>session_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>대화 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
@@ -15438,14 +15989,10 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G16" s="15" t="inlineStr">
-        <is>
-          <t>chat_sessions.id</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="n"/>
       <c r="H16" s="16" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15483,32 +16030,36 @@
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>session_id</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>발화자</t>
+          <t>대화 ID</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>varchar(10)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="15" t="n"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>chat_sessions.id</t>
+        </is>
+      </c>
       <c r="H17" s="16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>user / assistant</t>
-        </is>
-      </c>
+      <c r="J17" s="15" t="n"/>
       <c r="K17" s="15" t="inlineStr">
         <is>
           <t>CB-01 · H-2 · H-3</t>
@@ -15539,17 +16090,17 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>role</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>메시지 내용</t>
+          <t>발화자</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>varchar(10)</t>
         </is>
       </c>
       <c r="F18" s="16" t="n"/>
@@ -15560,7 +16111,11 @@
         </is>
       </c>
       <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>user / assistant</t>
+        </is>
+      </c>
       <c r="K18" s="15" t="inlineStr">
         <is>
           <t>CB-01 · H-2 · H-3</t>
@@ -15579,60 +16134,56 @@
       <c r="N18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>chat_messages</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>대화 메시지</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>answer_type</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>답변 종류</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="F19" s="25" t="n"/>
-      <c r="G19" s="24" t="n"/>
-      <c r="H19" s="25" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>메시지 내용</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="n"/>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I19" s="24" t="n"/>
-      <c r="J19" s="24" t="inlineStr">
-        <is>
-          <t>normal / clarify(정보 확인) / partial(일부만 확인됐어요) / no_evidence(확인이 어렵습니다) / refer(의료진 상담 필요) / emergency(긴급 안내) / crisis(도움 연결) — error는 프론트 전용이라 저장 안 함 (API v1.3 H-3)</t>
-        </is>
-      </c>
-      <c r="K19" s="24" t="inlineStr">
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="15" t="n"/>
+      <c r="K19" s="15" t="inlineStr">
         <is>
           <t>CB-01 · H-2 · H-3</t>
         </is>
       </c>
-      <c r="L19" s="25" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M19" s="25" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N19" s="24" t="n"/>
+      <c r="L19" s="16" t="inlineStr">
+        <is>
+          <t>기존</t>
+        </is>
+      </c>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="N19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="23" t="inlineStr">
@@ -15647,17 +16198,17 @@
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>sources</t>
+          <t>answer_type</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>답변 출처</t>
+          <t>답변 종류</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="F20" s="25" t="n"/>
@@ -15670,7 +16221,7 @@
       <c r="I20" s="24" t="n"/>
       <c r="J20" s="24" t="inlineStr">
         <is>
-          <t>답변 근거 출처 — [{ title, basedOn }] 형식 (API v1.3 H-3)</t>
+          <t>normal / clarify(정보 확인) / partial(일부만 확인됐어요) / no_evidence(확인이 어렵습니다) / refer(의료진 상담 필요) / emergency(긴급 안내) / crisis(도움 연결) — error는 프론트 전용이라 저장 안 함 (API v1.3 H-3)</t>
         </is>
       </c>
       <c r="K20" s="24" t="inlineStr">
@@ -15703,17 +16254,17 @@
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>client_request_id</t>
+          <t>sources</t>
         </is>
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>요청 번호</t>
+          <t>답변 출처</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>varchar(64)</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="F21" s="25" t="n"/>
@@ -15726,12 +16277,12 @@
       <c r="I21" s="24" t="n"/>
       <c r="J21" s="24" t="inlineStr">
         <is>
-          <t>앱이 만든 요청 번호 — 다시 시도(CB-01-E6) 때 같은 질문을 두 번 저장하지 않음. (session_id, client_request_id) UQ</t>
+          <t>답변 근거 출처 — [{ title, basedOn }] 형식 (API v1.3 H-3)</t>
         </is>
       </c>
       <c r="K21" s="24" t="inlineStr">
         <is>
-          <t>CB-01 · H-2 · H-3 · H-7</t>
+          <t>CB-01 · H-2 · H-3</t>
         </is>
       </c>
       <c r="L21" s="25" t="inlineStr">
@@ -15759,17 +16310,17 @@
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>context_card</t>
+          <t>client_request_id</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>맥락 카드</t>
+          <t>요청 번호</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>varchar(64)</t>
         </is>
       </c>
       <c r="F22" s="25" t="n"/>
@@ -15782,84 +16333,480 @@
       <c r="I22" s="24" t="n"/>
       <c r="J22" s="24" t="inlineStr">
         <is>
+          <t>앱이 만든 요청 번호 — 다시 시도(CB-01-E6) 때 같은 질문을 두 번 저장하지 않음. (session_id, client_request_id) UQ</t>
+        </is>
+      </c>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 · H-2 · H-3 · H-7</t>
+        </is>
+      </c>
+      <c r="L22" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M22" s="25" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N22" s="24" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>chat_messages</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>대화 메시지</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>context_card</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>맥락 카드</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="F23" s="25" t="n"/>
+      <c r="G23" s="24" t="n"/>
+      <c r="H23" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="n"/>
+      <c r="J23" s="24" t="inlineStr">
+        <is>
           <t>1단계 하루 한 대화에서 붙인 분석 맥락 { analysisId, context } — 다시 들어왔을 때 카드를 그대로 그림 (H-7)</t>
         </is>
       </c>
-      <c r="K22" s="24" t="inlineStr">
+      <c r="K23" s="24" t="inlineStr">
         <is>
           <t>CB-01 · H-2 · H-3 · H-7</t>
         </is>
       </c>
-      <c r="L22" s="25" t="inlineStr">
+      <c r="L23" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M22" s="25" t="inlineStr">
+      <c r="M23" s="25" t="inlineStr">
         <is>
           <t>v1.3</t>
         </is>
       </c>
-      <c r="N22" s="24" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="N23" s="24" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>chat_messages</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>대화 메시지</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>safety_card</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>안전성 점검 카드</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="F24" s="25" t="n"/>
+      <c r="G24" s="24" t="n"/>
+      <c r="H24" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="n"/>
+      <c r="J24" s="24" t="inlineStr">
+        <is>
+          <t>안전성 점검 결과 카드 { analysisId, warningIds }. 카드가 붙는 답도 answer_type은 normal. 카드가 없으면 비어 있음 (이슈 #88)</t>
+        </is>
+      </c>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 / H-2 / H-3</t>
+        </is>
+      </c>
+      <c r="L24" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M24" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N24" s="24" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>chat_messages</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>대화 메시지</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>답변 상태</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="F25" s="25" t="n"/>
+      <c r="G25" s="24" t="n"/>
+      <c r="H25" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>'done'</t>
+        </is>
+      </c>
+      <c r="J25" s="24" t="inlineStr">
+        <is>
+          <t>generating 또는 done. 화면을 나갔다 와도 만드는 중인 답을 알 수 있게 함. 사용자 줄은 늘 done. 실패는 두지 않음: 서버가 실패하면 답을 저장하지 않고 앱이 E6을 보여 줌 (이슈 #88)</t>
+        </is>
+      </c>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 / H-2 / H-3</t>
+        </is>
+      </c>
+      <c r="L25" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M25" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N25" s="24" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>chat_messages</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>대화 메시지</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>모델 이름</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="F26" s="25" t="n"/>
+      <c r="G26" s="24" t="n"/>
+      <c r="H26" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="n"/>
+      <c r="J26" s="24" t="inlineStr">
+        <is>
+          <t>답을 만든 모델 이름 (예: gpt-4o-mini). 답변마다 비용과 시간을 재려고 둠. assistant 줄만 채움 (이슈 #88)</t>
+        </is>
+      </c>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 / H-2 / H-3</t>
+        </is>
+      </c>
+      <c r="L26" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M26" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N26" s="24" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>chat_messages</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>대화 메시지</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>prompt_tokens</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>입력 토큰 수</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F27" s="25" t="n"/>
+      <c r="G27" s="24" t="n"/>
+      <c r="H27" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="n"/>
+      <c r="J27" s="24" t="inlineStr">
+        <is>
+          <t>답 하나에 AI를 여러 번 부르면 합친 값. assistant 줄만 채움 (이슈 #88)</t>
+        </is>
+      </c>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 / H-2 / H-3</t>
+        </is>
+      </c>
+      <c r="L27" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M27" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N27" s="24" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>chat_messages</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>대화 메시지</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>completion_tokens</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>출력 토큰 수</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F28" s="25" t="n"/>
+      <c r="G28" s="24" t="n"/>
+      <c r="H28" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="n"/>
+      <c r="J28" s="24" t="inlineStr">
+        <is>
+          <t>출력 토큰 수 합친 값. assistant 줄만 채움 (이슈 #88)</t>
+        </is>
+      </c>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 / H-2 / H-3</t>
+        </is>
+      </c>
+      <c r="L28" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M28" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N28" s="24" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>chat_messages</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>대화 메시지</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>latency_ms</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>걸린 시간(ms)</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F29" s="25" t="n"/>
+      <c r="G29" s="24" t="n"/>
+      <c r="H29" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="n"/>
+      <c r="J29" s="24" t="inlineStr">
+        <is>
+          <t>질문을 받은 때부터 답을 저장할 때까지 걸린 시간, 밀리초. assistant 줄만 채움 (이슈 #88)</t>
+        </is>
+      </c>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 / H-2 / H-3</t>
+        </is>
+      </c>
+      <c r="L29" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M29" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N29" s="24" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>chat_messages</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>대화 메시지</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D30" s="15" t="inlineStr">
         <is>
           <t>생성 일시</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="F23" s="16" t="n"/>
-      <c r="G23" s="15" t="n"/>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="F30" s="16" t="n"/>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I23" s="15" t="inlineStr">
+      <c r="I30" s="15" t="inlineStr">
         <is>
           <t>now()</t>
         </is>
       </c>
-      <c r="J23" s="15" t="n"/>
-      <c r="K23" s="15" t="inlineStr">
+      <c r="J30" s="15" t="n"/>
+      <c r="K30" s="15" t="inlineStr">
         <is>
           <t>CB-01 · H-2 · H-3</t>
         </is>
       </c>
-      <c r="L23" s="16" t="inlineStr">
+      <c r="L30" s="16" t="inlineStr">
         <is>
           <t>기존</t>
         </is>
       </c>
-      <c r="M23" s="16" t="inlineStr">
+      <c r="M30" s="16" t="inlineStr">
         <is>
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N23" s="15" t="n"/>
+      <c r="N30" s="15" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N20"/>
+  <autoFilter ref="A4:N27"/>
   <dataValidations count="3">
     <dataValidation sqref="H5:H300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>

--- a/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 규칙" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변경 이력" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용자" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="입력" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분석" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="챗봇" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실천·보상" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="마스터" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FHIR 대응" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="작성 규칙" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변경 이력" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="요약" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="사용자" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="입력" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분석" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="챗봇" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="실천·보상" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="마스터" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="FHIR 대응" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'사용자'!$A$4:$N$21</definedName>
@@ -876,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -910,7 +910,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
@@ -4208,6 +4207,44 @@
       <c r="H90" s="36" t="inlineStr">
         <is>
           <t>미리 저장해 두는 AI 생성 약 안내문 (의료 기록 아님). guides와 같은 이유로 FHIR 대응 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B91" s="19" t="inlineStr">
+        <is>
+          <t>user_health_profiles</t>
+        </is>
+      </c>
+      <c r="C91" s="15" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D91" s="14" t="inlineStr">
+        <is>
+          <t>Observation / Condition / Appointment</t>
+        </is>
+      </c>
+      <c r="E91" s="15" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="F91" s="15" t="n"/>
+      <c r="G91" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H91" s="15" t="inlineStr">
+        <is>
+          <t>v1.5. 흡연, 음주, 키, 몸무게, 임신, 투석은 Observation, 질환은 Condition, 예정 검사는 Appointment로 옮길 수 있음. 코드(LOINC 등) 대응은 확인 전</t>
         </is>
       </c>
     </row>
@@ -4228,7 +4265,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E169"/>
+  <dimension ref="A1:E172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7491,6 +7528,64 @@
         </is>
       </c>
       <c r="E169" s="10" t="n"/>
+    </row>
+    <row r="170" hidden="1" outlineLevel="1">
+      <c r="A170" s="10" t="n"/>
+      <c r="B170" s="10" t="inlineStr">
+        <is>
+          <t>사용자 / user_health_profiles: 테이블 신규 (이슈 #101)</t>
+        </is>
+      </c>
+      <c r="C170" s="10" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="D170" s="10" t="inlineStr">
+        <is>
+          <t>필드 11개: user_id(PK, users와 1:1), smoking, drinking, diseases, pregnant, dialysis, height_cm, weight_kg, upcoming_exams, created_at, updated_at
+사유: 4회차 멘토링(건강 정보는 회원가입과 내 정보에서 받아 DB에), 10/14 회의 3번과 디코. 음주, 흡연 값은 국민건강영양조사 문항 기준 (10/19 수인, 채연 확인 필요)</t>
+        </is>
+      </c>
+      <c r="E170" s="10" t="n"/>
+    </row>
+    <row r="171" hidden="1" outlineLevel="1">
+      <c r="A171" s="10" t="n"/>
+      <c r="B171" s="10" t="inlineStr">
+        <is>
+          <t>FHIR 대응 탭: user_health_profiles 행 추가</t>
+        </is>
+      </c>
+      <c r="C171" s="10" t="inlineStr">
+        <is>
+          <t>90행</t>
+        </is>
+      </c>
+      <c r="D171" s="10" t="inlineStr">
+        <is>
+          <t>91행: user_health_profiles (테이블), 변환 (코드 대응은 확인 전)</t>
+        </is>
+      </c>
+      <c r="E171" s="10" t="n"/>
+    </row>
+    <row r="172" hidden="1" outlineLevel="1">
+      <c r="A172" s="10" t="n"/>
+      <c r="B172" s="10" t="inlineStr">
+        <is>
+          <t>분석 / analyses.health_snapshot: 필드 추가 (이슈 #101)</t>
+        </is>
+      </c>
+      <c r="C172" s="10" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="D172" s="10" t="inlineStr">
+        <is>
+          <t>health_snapshot jsonb, N, 분석 시점 건강 정보 스냅샷. 정보를 고쳐도 지난 결과는 그대로 (10/14 회의 3번 채연 안)</t>
+        </is>
+      </c>
+      <c r="E172" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -7773,7 +7868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8781,6 +8876,638 @@
           <t>인덱스: (user_id, consent_type) [unique]</t>
         </is>
       </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>user_health_profiles</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>건강 정보</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>사용자 ID</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F21" s="25" t="inlineStr">
+        <is>
+          <t>PK, FK</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="H21" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="n"/>
+      <c r="J21" s="24" t="inlineStr">
+        <is>
+          <t>users와 1:1. 가입 때 함께 만듦</t>
+        </is>
+      </c>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>CM-02, CM-05, CM-06, A-1, U-1, U-2, U-3, U-5</t>
+        </is>
+      </c>
+      <c r="L21" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M21" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N21" s="24" t="inlineStr">
+        <is>
+          <t>v1.5 신규. 민감정보(sensitive_health 동의 범위). 동의 철회(U-5), 탈퇴(U-3) 때 줄째 삭제 (탈퇴는 users 행을 남기므로 따로 지움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>user_health_profiles</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>건강 정보</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>smoking</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>흡연</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="F22" s="25" t="n"/>
+      <c r="G22" s="24" t="n"/>
+      <c r="H22" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="n"/>
+      <c r="J22" s="24" t="inlineStr">
+        <is>
+          <t>daily / sometimes / past / never / unknown. 국민건강영양조사 BS3_1에 "잘 모르겠어요"를 더함. 가입 때 필수 (10/19 수인, 채연 확인 필요)</t>
+        </is>
+      </c>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>CM-02, CM-05, CM-06, A-1, U-1, U-2, U-3, U-5</t>
+        </is>
+      </c>
+      <c r="L22" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M22" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N22" s="24" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>user_health_profiles</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>건강 정보</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>drinking</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>음주 빈도</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="F23" s="25" t="n"/>
+      <c r="G23" s="24" t="n"/>
+      <c r="H23" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="n"/>
+      <c r="J23" s="24" t="inlineStr">
+        <is>
+          <t>none / lt_monthly / monthly / 2_4_monthly / 2_3_weekly / 4plus_weekly / unknown. 국민건강영양조사 BD1_11(최근 1년 음주 빈도)에 "잘 모르겠어요"를 더함. 가입 때 필수 (10/19 수인, 채연 확인 필요)</t>
+        </is>
+      </c>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>CM-02, CM-05, CM-06, A-1, U-1, U-2, U-3, U-5</t>
+        </is>
+      </c>
+      <c r="L23" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M23" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N23" s="24" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>user_health_profiles</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>건강 정보</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>diseases</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>질환</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="F24" s="25" t="n"/>
+      <c r="G24" s="24" t="n"/>
+      <c r="H24" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J24" s="24" t="inlineStr">
+        <is>
+          <t>생활습관 질환 lifestyle_diseases.id 목록(HTN, DM2, DLP, CKD, IHD, STROKE, AF, COPD, OP, OA. 10/14 회의 3번 채연 안). 내 정보에서 선택. 분석은 처방전에 질병분류기호가 없을 때만 이 값으로 채움(출처 profile, 팩트표 kcd로 이음). 챗봇은 둘 다 씀 (10/19 수인 제안, 채연 확인 필요)</t>
+        </is>
+      </c>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>CM-02, CM-05, CM-06, A-1, U-1, U-2, U-3, U-5</t>
+        </is>
+      </c>
+      <c r="L24" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M24" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N24" s="24" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>user_health_profiles</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>건강 정보</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>pregnant</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>임신 여부</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>varchar(10)</t>
+        </is>
+      </c>
+      <c r="F25" s="25" t="n"/>
+      <c r="G25" s="24" t="n"/>
+      <c r="H25" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="n"/>
+      <c r="J25" s="24" t="inlineStr">
+        <is>
+          <t>yes / no. 여성만 내 정보에서 선택. 성별을 M으로 바꾸면 비움. 비어 있으면 임신 금기 점검을 건너뛰고 결과에 알림 (10/14 디코)</t>
+        </is>
+      </c>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>CM-02, CM-05, CM-06, A-1, U-1, U-2, U-3, U-5</t>
+        </is>
+      </c>
+      <c r="L25" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M25" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N25" s="24" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>user_health_profiles</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>건강 정보</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>dialysis</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>투석 여부</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>varchar(10)</t>
+        </is>
+      </c>
+      <c r="F26" s="25" t="n"/>
+      <c r="G26" s="24" t="n"/>
+      <c r="H26" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="n"/>
+      <c r="J26" s="24" t="inlineStr">
+        <is>
+          <t>yes / no / unknown. 팩트표 applies_when: dialysis (10/8 디코 채연 제안, 10/19 받기로 함)</t>
+        </is>
+      </c>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>CM-02, CM-05, CM-06, A-1, U-1, U-2, U-3, U-5</t>
+        </is>
+      </c>
+      <c r="L26" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M26" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N26" s="24" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>user_health_profiles</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>건강 정보</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>height_cm</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>키 (cm)</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>smallint</t>
+        </is>
+      </c>
+      <c r="F27" s="25" t="n"/>
+      <c r="G27" s="24" t="n"/>
+      <c r="H27" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="n"/>
+      <c r="J27" s="24" t="inlineStr">
+        <is>
+          <t>내 정보에서 선택 (10/14 디코)</t>
+        </is>
+      </c>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>CM-02, CM-05, CM-06, A-1, U-1, U-2, U-3, U-5</t>
+        </is>
+      </c>
+      <c r="L27" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M27" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N27" s="24" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>user_health_profiles</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>건강 정보</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>weight_kg</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>몸무게 (kg)</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>numeric(4,1)</t>
+        </is>
+      </c>
+      <c r="F28" s="25" t="n"/>
+      <c r="G28" s="24" t="n"/>
+      <c r="H28" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="n"/>
+      <c r="J28" s="24" t="inlineStr">
+        <is>
+          <t>내 정보에서 선택 (10/14 디코)</t>
+        </is>
+      </c>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>CM-02, CM-05, CM-06, A-1, U-1, U-2, U-3, U-5</t>
+        </is>
+      </c>
+      <c r="L28" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M28" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N28" s="24" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>user_health_profiles</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>건강 정보</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>upcoming_exams</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>예정 검사</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="F29" s="25" t="n"/>
+      <c r="G29" s="24" t="n"/>
+      <c r="H29" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J29" s="24" t="inlineStr">
+        <is>
+          <t>[{ name, date }]. name은 50자 이내, date는 YYYY-MM-DD. 내 정보에서 선택 (10/14 회의 3번)</t>
+        </is>
+      </c>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>CM-02, CM-05, CM-06, A-1, U-1, U-2, U-3, U-5</t>
+        </is>
+      </c>
+      <c r="L29" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M29" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N29" s="24" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>user_health_profiles</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>건강 정보</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>생성 일시</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F30" s="25" t="n"/>
+      <c r="G30" s="24" t="n"/>
+      <c r="H30" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="J30" s="24" t="n"/>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>CM-02, CM-05, CM-06, A-1, U-1, U-2, U-3, U-5</t>
+        </is>
+      </c>
+      <c r="L30" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M30" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N30" s="24" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>user_health_profiles</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>건강 정보</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>수정 일시</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F31" s="25" t="n"/>
+      <c r="G31" s="24" t="n"/>
+      <c r="H31" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="n"/>
+      <c r="J31" s="24" t="n"/>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>CM-02, CM-05, CM-06, A-1, U-1, U-2, U-3, U-5</t>
+        </is>
+      </c>
+      <c r="L31" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M31" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N31" s="24" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:N21"/>
@@ -8838,7 +9565,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -12026,7 +12752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12059,7 +12785,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -12593,56 +13318,60 @@
       <c r="N12" s="24" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>analyses</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>분석 작업</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>started_at</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>시작 일시</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr"/>
-      <c r="G13" s="15" t="inlineStr"/>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>health_snapshot</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>분석 시점 건강 정보</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="F13" s="25" t="n"/>
+      <c r="G13" s="24" t="n"/>
+      <c r="H13" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I13" s="15" t="inlineStr"/>
-      <c r="J13" s="15" t="inlineStr"/>
-      <c r="K13" s="15" t="inlineStr">
+      <c r="I13" s="24" t="n"/>
+      <c r="J13" s="24" t="inlineStr">
+        <is>
+          <t>분석 시점 건강 정보(user_health_profiles) 스냅샷. 정보를 고쳐도 지난 결과는 그대로 (10/14 회의 3번 채연 안, 이슈 #101)</t>
+        </is>
+      </c>
+      <c r="K13" s="24" t="inlineStr">
         <is>
           <t>RG-01 · RG-01-E1 · CM-04 · R-1~3 · R-7 · R-8</t>
         </is>
       </c>
-      <c r="L13" s="16" t="inlineStr">
-        <is>
-          <t>기존</t>
-        </is>
-      </c>
-      <c r="M13" s="16" t="inlineStr">
-        <is>
-          <t>v0.1</t>
-        </is>
-      </c>
-      <c r="N13" s="15" t="inlineStr"/>
+      <c r="L13" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M13" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N13" s="24" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
@@ -12657,12 +13386,12 @@
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>finished_at</t>
+          <t>started_at</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>종료 일시</t>
+          <t>시작 일시</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -12697,107 +13426,99 @@
       <c r="N14" s="15" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>analyses</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>분석 작업</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>생성 일시</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>finished_at</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>종료 일시</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="F15" s="25" t="inlineStr"/>
-      <c r="G15" s="24" t="inlineStr"/>
-      <c r="H15" s="25" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr"/>
+      <c r="G15" s="15" t="inlineStr"/>
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="J15" s="24" t="inlineStr"/>
-      <c r="K15" s="24" t="inlineStr">
+      <c r="I15" s="15" t="inlineStr"/>
+      <c r="J15" s="15" t="inlineStr"/>
+      <c r="K15" s="15" t="inlineStr">
         <is>
           <t>RG-01 · RG-01-E1 · CM-04 · R-1~3 · R-7 · R-8</t>
         </is>
       </c>
-      <c r="L15" s="25" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M15" s="25" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N15" s="24" t="inlineStr"/>
+      <c r="L15" s="16" t="inlineStr">
+        <is>
+          <t>기존</t>
+        </is>
+      </c>
+      <c r="M15" s="16" t="inlineStr">
+        <is>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="N15" s="15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="23" t="inlineStr">
         <is>
-          <t>analysis_prescriptions</t>
+          <t>analyses</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>분석-처방전 연결</t>
+          <t>분석 작업</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>analysis_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>분석 ID</t>
+          <t>생성 일시</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F16" s="25" t="inlineStr">
-        <is>
-          <t>PK · FK</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
-        <is>
-          <t>analyses.id</t>
-        </is>
-      </c>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="inlineStr"/>
+      <c r="G16" s="24" t="inlineStr"/>
       <c r="H16" s="25" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I16" s="24" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="J16" s="24" t="inlineStr"/>
       <c r="K16" s="24" t="inlineStr">
         <is>
-          <t>R-1</t>
+          <t>RG-01 · RG-01-E1 · CM-04 · R-1~3 · R-7 · R-8</t>
         </is>
       </c>
       <c r="L16" s="25" t="inlineStr">
@@ -12810,11 +13531,7 @@
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N16" s="24" t="inlineStr">
-        <is>
-          <t>v1.0 신규 · 여러 병원 처방전을 한 번에 점검 (최대 5장, REQ-013)</t>
-        </is>
-      </c>
+      <c r="N16" s="24" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="23" t="inlineStr">
@@ -12829,12 +13546,12 @@
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>prescription_id</t>
+          <t>analysis_id</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>처방전 ID</t>
+          <t>분석 ID</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -12849,7 +13566,7 @@
       </c>
       <c r="G17" s="24" t="inlineStr">
         <is>
-          <t>prescriptions.id</t>
+          <t>analyses.id</t>
         </is>
       </c>
       <c r="H17" s="25" t="inlineStr">
@@ -12874,27 +13591,31 @@
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N17" s="24" t="inlineStr"/>
+      <c r="N17" s="24" t="inlineStr">
+        <is>
+          <t>v1.0 신규 · 여러 병원 처방전을 한 번에 점검 (최대 5장, REQ-013)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="23" t="inlineStr">
         <is>
-          <t>analysis_diseases</t>
+          <t>analysis_prescriptions</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>분석 질환</t>
+          <t>분석-처방전 연결</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>analysis_id</t>
+          <t>prescription_id</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>분석 ID</t>
+          <t>처방전 ID</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -12909,7 +13630,7 @@
       </c>
       <c r="G18" s="24" t="inlineStr">
         <is>
-          <t>analyses.id</t>
+          <t>prescriptions.id</t>
         </is>
       </c>
       <c r="H18" s="25" t="inlineStr">
@@ -12921,7 +13642,7 @@
       <c r="J18" s="24" t="inlineStr"/>
       <c r="K18" s="24" t="inlineStr">
         <is>
-          <t>RG-05 · RG-05-E1 · R-6</t>
+          <t>R-1</t>
         </is>
       </c>
       <c r="L18" s="25" t="inlineStr">
@@ -12934,11 +13655,7 @@
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N18" s="24" t="inlineStr">
-        <is>
-          <t>v1.0 신규 · 생활습관 가이드 조회 기준</t>
-        </is>
-      </c>
+      <c r="N18" s="24" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
@@ -12953,17 +13670,17 @@
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>disease_code</t>
+          <t>analysis_id</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>상병 코드</t>
+          <t>분석 ID</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>varchar(10)</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="F19" s="25" t="inlineStr">
@@ -12973,7 +13690,7 @@
       </c>
       <c r="G19" s="24" t="inlineStr">
         <is>
-          <t>diseases.code</t>
+          <t>analyses.id</t>
         </is>
       </c>
       <c r="H19" s="25" t="inlineStr">
@@ -12998,7 +13715,11 @@
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N19" s="24" t="inlineStr"/>
+      <c r="N19" s="24" t="inlineStr">
+        <is>
+          <t>v1.0 신규 · 생활습관 가이드 조회 기준</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="23" t="inlineStr">
@@ -13013,108 +13734,108 @@
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
+          <t>disease_code</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>상병 코드</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>varchar(10)</t>
+        </is>
+      </c>
+      <c r="F20" s="25" t="inlineStr">
+        <is>
+          <t>PK · FK</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>diseases.code</t>
+        </is>
+      </c>
+      <c r="H20" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr"/>
+      <c r="J20" s="24" t="inlineStr"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>RG-05 · RG-05-E1 · R-6</t>
+        </is>
+      </c>
+      <c r="L20" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M20" s="25" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="N20" s="24" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>analysis_diseases</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>분석 질환</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
           <t>origin</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="D21" s="24" t="inlineStr">
         <is>
           <t>출처 구분</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E21" s="24" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="F20" s="25" t="inlineStr"/>
-      <c r="G20" s="24" t="inlineStr"/>
-      <c r="H20" s="25" t="inlineStr">
+      <c r="F21" s="25" t="inlineStr"/>
+      <c r="G21" s="24" t="inlineStr"/>
+      <c r="H21" s="25" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I20" s="24" t="inlineStr"/>
-      <c r="J20" s="24" t="inlineStr">
+      <c r="I21" s="24" t="inlineStr"/>
+      <c r="J21" s="24" t="inlineStr">
         <is>
           <t>prescription(처방전 코드) / user(RG-05-E1에서 직접 선택)</t>
         </is>
       </c>
-      <c r="K20" s="24" t="inlineStr">
+      <c r="K21" s="24" t="inlineStr">
         <is>
           <t>RG-05 · RG-05-E1 · R-6</t>
         </is>
       </c>
-      <c r="L20" s="25" t="inlineStr">
+      <c r="L21" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M20" s="25" t="inlineStr">
+      <c r="M21" s="25" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N20" s="24" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>analysis_warnings</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>안전성 경고</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G21" s="15" t="inlineStr"/>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I21" s="15" t="inlineStr"/>
-      <c r="J21" s="15" t="inlineStr"/>
-      <c r="K21" s="15" t="inlineStr">
-        <is>
-          <t>RG-02 · RG-02-E1 · RG-03 · R-4 · R-5</t>
-        </is>
-      </c>
-      <c r="L21" s="16" t="inlineStr">
-        <is>
-          <t>기존</t>
-        </is>
-      </c>
-      <c r="M21" s="16" t="inlineStr">
-        <is>
-          <t>v0.1</t>
-        </is>
-      </c>
-      <c r="N21" s="15" t="inlineStr">
-        <is>
-          <t>DB 조회로 결정적으로 산출. 0건이면 RG-02-E1</t>
-        </is>
-      </c>
+      <c r="N21" s="24" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
@@ -13129,12 +13850,12 @@
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>analysis_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>분석 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
@@ -13144,14 +13865,10 @@
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G22" s="15" t="inlineStr">
-        <is>
-          <t>analyses.id</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr"/>
       <c r="H22" s="16" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13174,63 +13891,71 @@
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N22" s="15" t="inlineStr"/>
+      <c r="N22" s="15" t="inlineStr">
+        <is>
+          <t>DB 조회로 결정적으로 산출. 0건이면 RG-02-E1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>analysis_warnings</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>안전성 경고</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>warning_type</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr">
-        <is>
-          <t>경고 종류</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
-        <is>
-          <t>varchar(30)</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="inlineStr"/>
-      <c r="G23" s="21" t="inlineStr"/>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>analysis_id</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>분석 ID</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>analyses.id</t>
+        </is>
+      </c>
+      <c r="H23" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I23" s="21" t="inlineStr"/>
-      <c r="J23" s="21" t="inlineStr">
-        <is>
-          <t>interaction / duplicate_ingredient / duplicate_efficacy / elderly / age / pregnancy / dose_exceed / polypharmacy(v1.0 🟡)</t>
-        </is>
-      </c>
-      <c r="K23" s="21" t="inlineStr">
+      <c r="I23" s="15" t="inlineStr"/>
+      <c r="J23" s="15" t="inlineStr"/>
+      <c r="K23" s="15" t="inlineStr">
         <is>
           <t>RG-02 · RG-02-E1 · RG-03 · R-4 · R-5</t>
         </is>
       </c>
-      <c r="L23" s="22" t="inlineStr">
-        <is>
-          <t>수정</t>
-        </is>
-      </c>
-      <c r="M23" s="22" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N23" s="21" t="inlineStr"/>
+      <c r="L23" s="16" t="inlineStr">
+        <is>
+          <t>기존</t>
+        </is>
+      </c>
+      <c r="M23" s="16" t="inlineStr">
+        <is>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="N23" s="15" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
@@ -13245,17 +13970,17 @@
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>warning_type</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
         <is>
-          <t>경고 등급</t>
+          <t>경고 종류</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
         <is>
-          <t>varchar(10)</t>
+          <t>varchar(30)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr"/>
@@ -13268,89 +13993,81 @@
       <c r="I24" s="21" t="inlineStr"/>
       <c r="J24" s="21" t="inlineStr">
         <is>
+          <t>interaction / duplicate_ingredient / duplicate_efficacy / elderly / age / pregnancy / dose_exceed / polypharmacy(v1.0 🟡)</t>
+        </is>
+      </c>
+      <c r="K24" s="21" t="inlineStr">
+        <is>
+          <t>RG-02 · RG-02-E1 · RG-03 · R-4 · R-5</t>
+        </is>
+      </c>
+      <c r="L24" s="22" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="M24" s="22" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="N24" s="21" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>analysis_warnings</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>안전성 경고</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>경고 등급</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>varchar(10)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr"/>
+      <c r="G25" s="21" t="inlineStr"/>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr"/>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
           <t>danger / caution / info</t>
         </is>
       </c>
-      <c r="K24" s="21" t="inlineStr">
+      <c r="K25" s="21" t="inlineStr">
         <is>
           <t>RG-02 · RG-02-E1 · RG-03 · R-4 · R-5</t>
         </is>
       </c>
-      <c r="L24" s="22" t="inlineStr">
+      <c r="L25" s="22" t="inlineStr">
         <is>
           <t>수정</t>
         </is>
       </c>
-      <c r="M24" s="22" t="inlineStr">
+      <c r="M25" s="22" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N24" s="21" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="23" t="inlineStr">
-        <is>
-          <t>analysis_warnings</t>
-        </is>
-      </c>
-      <c r="B25" s="24" t="inlineStr">
-        <is>
-          <t>안전성 경고</t>
-        </is>
-      </c>
-      <c r="C25" s="24" t="inlineStr">
-        <is>
-          <t>item_id_a</t>
-        </is>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
-        <is>
-          <t>대상 약 항목 ID</t>
-        </is>
-      </c>
-      <c r="E25" s="24" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F25" s="25" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G25" s="24" t="inlineStr">
-        <is>
-          <t>prescription_items.id</t>
-        </is>
-      </c>
-      <c r="H25" s="25" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I25" s="24" t="inlineStr"/>
-      <c r="J25" s="24" t="inlineStr">
-        <is>
-          <t>약 이름 대신 항목 참조 (처방 병원 표시용)</t>
-        </is>
-      </c>
-      <c r="K25" s="24" t="inlineStr">
-        <is>
-          <t>RG-02 · RG-02-E1 · RG-03 · R-4 · R-5</t>
-        </is>
-      </c>
-      <c r="L25" s="25" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M25" s="25" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N25" s="24" t="inlineStr"/>
+      <c r="N25" s="21" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="23" t="inlineStr">
@@ -13365,12 +14082,12 @@
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>item_id_b</t>
+          <t>item_id_a</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>상대 약 항목 ID</t>
+          <t>대상 약 항목 ID</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
@@ -13396,245 +14113,257 @@
       <c r="I26" s="24" t="inlineStr"/>
       <c r="J26" s="24" t="inlineStr">
         <is>
+          <t>약 이름 대신 항목 참조 (처방 병원 표시용)</t>
+        </is>
+      </c>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>RG-02 · RG-02-E1 · RG-03 · R-4 · R-5</t>
+        </is>
+      </c>
+      <c r="L26" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M26" s="25" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="N26" s="24" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>analysis_warnings</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>안전성 경고</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>item_id_b</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>상대 약 항목 ID</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F27" s="25" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>prescription_items.id</t>
+        </is>
+      </c>
+      <c r="H27" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr"/>
+      <c r="J27" s="24" t="inlineStr">
+        <is>
           <t>상대 약 (병용금기 · 중복)</t>
         </is>
       </c>
-      <c r="K26" s="24" t="inlineStr">
+      <c r="K27" s="24" t="inlineStr">
         <is>
           <t>RG-02 · RG-02-E1 · RG-03 · R-4 · R-5</t>
         </is>
       </c>
-      <c r="L26" s="25" t="inlineStr">
+      <c r="L27" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M26" s="25" t="inlineStr">
+      <c r="M27" s="25" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N26" s="24" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="N27" s="24" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>analysis_warnings</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>안전성 경고</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>사유</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr"/>
-      <c r="G27" s="21" t="inlineStr"/>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr"/>
+      <c r="G28" s="21" t="inlineStr"/>
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I27" s="21" t="inlineStr"/>
-      <c r="J27" s="21" t="inlineStr">
+      <c r="I28" s="21" t="inlineStr"/>
+      <c r="J28" s="21" t="inlineStr">
         <is>
           <t>DUR 금기 사유 원문</t>
         </is>
       </c>
-      <c r="K27" s="21" t="inlineStr">
+      <c r="K28" s="21" t="inlineStr">
         <is>
           <t>RG-02 · RG-02-E1 · RG-03 · R-4 · R-5</t>
         </is>
       </c>
-      <c r="L27" s="22" t="inlineStr">
+      <c r="L28" s="22" t="inlineStr">
         <is>
           <t>수정</t>
         </is>
       </c>
-      <c r="M27" s="22" t="inlineStr">
+      <c r="M28" s="22" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N27" s="21" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="N28" s="21" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>analysis_warnings</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>안전성 경고</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>summary</t>
         </is>
       </c>
-      <c r="D28" s="24" t="inlineStr">
+      <c r="D29" s="24" t="inlineStr">
         <is>
           <t>화면 표시 문장</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E29" s="24" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F28" s="25" t="inlineStr"/>
-      <c r="G28" s="24" t="inlineStr"/>
-      <c r="H28" s="25" t="inlineStr">
+      <c r="F29" s="25" t="inlineStr"/>
+      <c r="G29" s="24" t="inlineStr"/>
+      <c r="H29" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I28" s="24" t="inlineStr"/>
-      <c r="J28" s="24" t="inlineStr">
+      <c r="I29" s="24" t="inlineStr"/>
+      <c r="J29" s="24" t="inlineStr">
         <is>
           <t>화면 표시 문장 (템플릿, AI 생성 아님 · NFR-032)</t>
         </is>
       </c>
-      <c r="K28" s="24" t="inlineStr">
+      <c r="K29" s="24" t="inlineStr">
         <is>
           <t>RG-02 · RG-02-E1 · RG-03 · R-4 · R-5</t>
         </is>
       </c>
-      <c r="L28" s="25" t="inlineStr">
+      <c r="L29" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M28" s="25" t="inlineStr">
+      <c r="M29" s="25" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N28" s="24" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="N29" s="24" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>analysis_warnings</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>안전성 경고</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>고시명</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr"/>
-      <c r="G29" s="21" t="inlineStr"/>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr"/>
+      <c r="G30" s="21" t="inlineStr"/>
+      <c r="H30" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I29" s="21" t="inlineStr"/>
-      <c r="J29" s="21" t="inlineStr">
+      <c r="I30" s="21" t="inlineStr"/>
+      <c r="J30" s="21" t="inlineStr">
         <is>
           <t>식약처 고시명</t>
         </is>
       </c>
-      <c r="K29" s="21" t="inlineStr">
+      <c r="K30" s="21" t="inlineStr">
         <is>
           <t>RG-02 · RG-02-E1 · RG-03 · R-4 · R-5</t>
         </is>
       </c>
-      <c r="L29" s="22" t="inlineStr">
+      <c r="L30" s="22" t="inlineStr">
         <is>
           <t>수정</t>
         </is>
       </c>
-      <c r="M29" s="22" t="inlineStr">
+      <c r="M30" s="22" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N29" s="21" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="23" t="inlineStr">
-        <is>
-          <t>analysis_warnings</t>
-        </is>
-      </c>
-      <c r="B30" s="24" t="inlineStr">
-        <is>
-          <t>안전성 경고</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>notice_date</t>
-        </is>
-      </c>
-      <c r="D30" s="24" t="inlineStr">
-        <is>
-          <t>고시일</t>
-        </is>
-      </c>
-      <c r="E30" s="24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="F30" s="25" t="inlineStr"/>
-      <c r="G30" s="24" t="inlineStr"/>
-      <c r="H30" s="25" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I30" s="24" t="inlineStr"/>
-      <c r="J30" s="24" t="inlineStr"/>
-      <c r="K30" s="24" t="inlineStr">
-        <is>
-          <t>RG-02 · RG-02-E1 · RG-03 · R-4 · R-5</t>
-        </is>
-      </c>
-      <c r="L30" s="25" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M30" s="25" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N30" s="24" t="inlineStr"/>
+      <c r="N30" s="21" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
@@ -13649,17 +14378,17 @@
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>daily_total</t>
+          <t>notice_date</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>1일 총 복용량</t>
+          <t>고시일</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
         <is>
-          <t>decimal(12,3)</t>
+          <t>date</t>
         </is>
       </c>
       <c r="F31" s="25" t="inlineStr"/>
@@ -13670,11 +14399,7 @@
         </is>
       </c>
       <c r="I31" s="24" t="inlineStr"/>
-      <c r="J31" s="24" t="inlineStr">
-        <is>
-          <t>1일 최대용량 초과일 때만</t>
-        </is>
-      </c>
+      <c r="J31" s="24" t="inlineStr"/>
       <c r="K31" s="24" t="inlineStr">
         <is>
           <t>RG-02 · RG-02-E1 · RG-03 · R-4 · R-5</t>
@@ -13705,12 +14430,12 @@
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>max_daily</t>
+          <t>daily_total</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>1일 최대 기준량</t>
+          <t>1일 총 복용량</t>
         </is>
       </c>
       <c r="E32" s="24" t="inlineStr">
@@ -13726,7 +14451,11 @@
         </is>
       </c>
       <c r="I32" s="24" t="inlineStr"/>
-      <c r="J32" s="24" t="inlineStr"/>
+      <c r="J32" s="24" t="inlineStr">
+        <is>
+          <t>1일 최대용량 초과일 때만</t>
+        </is>
+      </c>
       <c r="K32" s="24" t="inlineStr">
         <is>
           <t>RG-02 · RG-02-E1 · RG-03 · R-4 · R-5</t>
@@ -13757,104 +14486,100 @@
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
+          <t>max_daily</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>1일 최대 기준량</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>decimal(12,3)</t>
+        </is>
+      </c>
+      <c r="F33" s="25" t="inlineStr"/>
+      <c r="G33" s="24" t="inlineStr"/>
+      <c r="H33" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr"/>
+      <c r="J33" s="24" t="inlineStr"/>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>RG-02 · RG-02-E1 · RG-03 · R-4 · R-5</t>
+        </is>
+      </c>
+      <c r="L33" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M33" s="25" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="N33" s="24" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>analysis_warnings</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>안전성 경고</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
           <t>detail</t>
         </is>
       </c>
-      <c r="D33" s="24" t="inlineStr">
+      <c r="D34" s="24" t="inlineStr">
         <is>
           <t>경고 세부</t>
         </is>
       </c>
-      <c r="E33" s="24" t="inlineStr">
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>jsonb</t>
         </is>
       </c>
-      <c r="F33" s="25" t="n"/>
-      <c r="G33" s="24" t="n"/>
-      <c r="H33" s="25" t="inlineStr">
+      <c r="F34" s="25" t="n"/>
+      <c r="G34" s="24" t="n"/>
+      <c r="H34" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I33" s="24" t="n"/>
-      <c r="J33" s="24" t="inlineStr">
+      <c r="I34" s="24" t="n"/>
+      <c r="J34" s="24" t="inlineStr">
         <is>
           <t>약이 3개 이상인 경고의 전체 항목 번호, 성분, 근거 구분</t>
         </is>
       </c>
-      <c r="K33" s="24" t="inlineStr">
+      <c r="K34" s="24" t="inlineStr">
         <is>
           <t>RG-02 / R-4</t>
         </is>
       </c>
-      <c r="L33" s="25" t="inlineStr">
+      <c r="L34" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M33" s="25" t="inlineStr">
+      <c r="M34" s="25" t="inlineStr">
         <is>
           <t>v1.5</t>
         </is>
       </c>
-      <c r="N33" s="24" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>guides</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>복약 · 생활습관 안내문</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="E34" s="15" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G34" s="15" t="inlineStr"/>
-      <c r="H34" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I34" s="15" t="inlineStr"/>
-      <c r="J34" s="15" t="inlineStr"/>
-      <c r="K34" s="15" t="inlineStr">
-        <is>
-          <t>RG-04 · RG-05 · R-4 · R-10</t>
-        </is>
-      </c>
-      <c r="L34" s="16" t="inlineStr">
-        <is>
-          <t>기존</t>
-        </is>
-      </c>
-      <c r="M34" s="16" t="inlineStr">
-        <is>
-          <t>v0.1</t>
-        </is>
-      </c>
-      <c r="N34" s="15" t="inlineStr"/>
+      <c r="N34" s="24" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
@@ -13869,12 +14594,12 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>analysis_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>분석 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E35" s="15" t="inlineStr">
@@ -13884,14 +14609,10 @@
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G35" s="15" t="inlineStr">
-        <is>
-          <t>analyses.id</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr"/>
       <c r="H35" s="16" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13917,172 +14638,176 @@
       <c r="N35" s="15" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>guides</t>
         </is>
       </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>복약 · 생활습관 안내문</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>analysis_id</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>분석 ID</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>analyses.id</t>
+        </is>
+      </c>
+      <c r="H36" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I36" s="15" t="inlineStr"/>
+      <c r="J36" s="15" t="inlineStr"/>
+      <c r="K36" s="15" t="inlineStr">
+        <is>
+          <t>RG-04 · RG-05 · R-4 · R-10</t>
+        </is>
+      </c>
+      <c r="L36" s="16" t="inlineStr">
+        <is>
+          <t>기존</t>
+        </is>
+      </c>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="N36" s="15" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>guides</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>복약 · 생활습관 안내문</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
         <is>
           <t>section</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr">
         <is>
           <t>안내 구분</t>
         </is>
       </c>
-      <c r="E36" s="21" t="inlineStr">
+      <c r="E37" s="21" t="inlineStr">
         <is>
           <t>varchar(30)</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr"/>
-      <c r="G36" s="21" t="inlineStr"/>
-      <c r="H36" s="22" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr"/>
+      <c r="G37" s="21" t="inlineStr"/>
+      <c r="H37" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I36" s="21" t="inlineStr"/>
-      <c r="J36" s="21" t="inlineStr">
+      <c r="I37" s="21" t="inlineStr"/>
+      <c r="J37" s="21" t="inlineStr">
         <is>
           <t>medication / lifestyle</t>
         </is>
       </c>
-      <c r="K36" s="21" t="inlineStr">
+      <c r="K37" s="21" t="inlineStr">
         <is>
           <t>RG-04 · RG-05 · R-4 · R-10</t>
         </is>
       </c>
-      <c r="L36" s="22" t="inlineStr">
+      <c r="L37" s="22" t="inlineStr">
         <is>
           <t>수정</t>
         </is>
       </c>
-      <c r="M36" s="22" t="inlineStr">
+      <c r="M37" s="22" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N36" s="21" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="23" t="inlineStr">
+      <c r="N37" s="21" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="inlineStr">
         <is>
           <t>guides</t>
         </is>
       </c>
-      <c r="B37" s="24" t="inlineStr">
+      <c r="B38" s="24" t="inlineStr">
         <is>
           <t>복약 · 생활습관 안내문</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C38" s="24" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="D37" s="24" t="inlineStr">
+      <c r="D38" s="24" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="E37" s="24" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="F37" s="25" t="inlineStr"/>
-      <c r="G37" s="24" t="inlineStr"/>
-      <c r="H37" s="25" t="inlineStr">
+      <c r="F38" s="25" t="inlineStr"/>
+      <c r="G38" s="24" t="inlineStr"/>
+      <c r="H38" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I37" s="24" t="inlineStr"/>
-      <c r="J37" s="24" t="inlineStr">
+      <c r="I38" s="24" t="inlineStr"/>
+      <c r="J38" s="24" t="inlineStr">
         <is>
           <t>done / failed (부분 결과 RG-01-E1 → RG-04 · RG-05 "만들지 못했어요")</t>
         </is>
       </c>
-      <c r="K37" s="24" t="inlineStr">
+      <c r="K38" s="24" t="inlineStr">
         <is>
           <t>RG-04 · RG-05 · R-4 · R-10</t>
         </is>
       </c>
-      <c r="L37" s="25" t="inlineStr">
+      <c r="L38" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M37" s="25" t="inlineStr">
+      <c r="M38" s="25" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N37" s="24" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>guides</t>
-        </is>
-      </c>
-      <c r="B38" s="21" t="inlineStr">
-        <is>
-          <t>복약 · 생활습관 안내문</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>안내 내용 (JSON)</t>
-        </is>
-      </c>
-      <c r="E38" s="21" t="inlineStr">
-        <is>
-          <t>jsonb</t>
-        </is>
-      </c>
-      <c r="F38" s="22" t="inlineStr"/>
-      <c r="G38" s="21" t="inlineStr"/>
-      <c r="H38" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I38" s="21" t="inlineStr"/>
-      <c r="J38" s="21" t="inlineStr">
-        <is>
-          <t>항목 고정 JSON (약별 purpose · howToTake · caution · source) — 결과 일관성 NFR-030</t>
-        </is>
-      </c>
-      <c r="K38" s="21" t="inlineStr">
-        <is>
-          <t>RG-04 · RG-05 · R-4 · R-10</t>
-        </is>
-      </c>
-      <c r="L38" s="22" t="inlineStr">
-        <is>
-          <t>수정</t>
-        </is>
-      </c>
-      <c r="M38" s="22" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N38" s="21" t="inlineStr"/>
+      <c r="N38" s="24" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="20" t="inlineStr">
@@ -14097,17 +14822,17 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>prompt_ver</t>
+          <t>content</t>
         </is>
       </c>
       <c r="D39" s="21" t="inlineStr">
         <is>
-          <t>프롬프트 버전</t>
+          <t>안내 내용 (JSON)</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="F39" s="22" t="inlineStr"/>
@@ -14118,7 +14843,11 @@
         </is>
       </c>
       <c r="I39" s="21" t="inlineStr"/>
-      <c r="J39" s="21" t="inlineStr"/>
+      <c r="J39" s="21" t="inlineStr">
+        <is>
+          <t>항목 고정 JSON (약별 purpose · howToTake · caution · source) — 결과 일관성 NFR-030</t>
+        </is>
+      </c>
       <c r="K39" s="21" t="inlineStr">
         <is>
           <t>RG-04 · RG-05 · R-4 · R-10</t>
@@ -14149,17 +14878,17 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>model_name</t>
+          <t>prompt_ver</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
         <is>
-          <t>모델 이름</t>
+          <t>프롬프트 버전</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr"/>
@@ -14201,17 +14930,17 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>tts_url</t>
+          <t>model_name</t>
         </is>
       </c>
       <c r="D41" s="21" t="inlineStr">
         <is>
-          <t>음성 파일 주소</t>
+          <t>모델 이름</t>
         </is>
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
-          <t>varchar(500)</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="F41" s="22" t="inlineStr"/>
@@ -14222,126 +14951,122 @@
         </is>
       </c>
       <c r="I41" s="21" t="inlineStr"/>
-      <c r="J41" s="21" t="inlineStr">
+      <c r="J41" s="21" t="inlineStr"/>
+      <c r="K41" s="21" t="inlineStr">
+        <is>
+          <t>RG-04 · RG-05 · R-4 · R-10</t>
+        </is>
+      </c>
+      <c r="L41" s="22" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="M41" s="22" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="N41" s="21" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>guides</t>
+        </is>
+      </c>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>복약 · 생활습관 안내문</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>tts_url</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>음성 파일 주소</t>
+        </is>
+      </c>
+      <c r="E42" s="21" t="inlineStr">
+        <is>
+          <t>varchar(500)</t>
+        </is>
+      </c>
+      <c r="F42" s="22" t="inlineStr"/>
+      <c r="G42" s="21" t="inlineStr"/>
+      <c r="H42" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I42" s="21" t="inlineStr"/>
+      <c r="J42" s="21" t="inlineStr">
         <is>
           <t>선택 구현 (REQ-100)</t>
         </is>
       </c>
-      <c r="K41" s="21" t="inlineStr">
+      <c r="K42" s="21" t="inlineStr">
         <is>
           <t>RG-04 · RG-05 · R-4 · R-10</t>
         </is>
       </c>
-      <c r="L41" s="22" t="inlineStr">
+      <c r="L42" s="22" t="inlineStr">
         <is>
           <t>수정</t>
         </is>
       </c>
-      <c r="M41" s="22" t="inlineStr">
+      <c r="M42" s="22" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N41" s="21" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="19" t="inlineStr">
-        <is>
-          <t>guides</t>
-        </is>
-      </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>복약 · 생활습관 안내문</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="D42" s="15" t="inlineStr">
-        <is>
-          <t>생성 일시</t>
-        </is>
-      </c>
-      <c r="E42" s="15" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="inlineStr"/>
-      <c r="G42" s="15" t="inlineStr"/>
-      <c r="H42" s="16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I42" s="15" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="J42" s="15" t="inlineStr"/>
-      <c r="K42" s="15" t="inlineStr">
-        <is>
-          <t>RG-04 · RG-05 · R-4 · R-10</t>
-        </is>
-      </c>
-      <c r="L42" s="16" t="inlineStr">
-        <is>
-          <t>기존</t>
-        </is>
-      </c>
-      <c r="M42" s="16" t="inlineStr">
-        <is>
-          <t>v0.1</t>
-        </is>
-      </c>
-      <c r="N42" s="15" t="inlineStr"/>
+      <c r="N42" s="21" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>feedbacks</t>
+          <t>guides</t>
         </is>
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>안내문 피드백</t>
+          <t>복약 · 생활습관 안내문</t>
         </is>
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>생성 일시</t>
         </is>
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F43" s="16" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr"/>
       <c r="G43" s="15" t="inlineStr"/>
       <c r="H43" s="16" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I43" s="15" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="J43" s="15" t="inlineStr"/>
       <c r="K43" s="15" t="inlineStr">
         <is>
-          <t>RG-04 · R-9</t>
+          <t>RG-04 · RG-05 · R-4 · R-10</t>
         </is>
       </c>
       <c r="L43" s="16" t="inlineStr">
@@ -14369,12 +15094,12 @@
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>guide_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>안내문 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
@@ -14384,14 +15109,10 @@
       </c>
       <c r="F44" s="16" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G44" s="15" t="inlineStr">
-        <is>
-          <t>guides.id</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G44" s="15" t="inlineStr"/>
       <c r="H44" s="16" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14429,12 +15150,12 @@
       </c>
       <c r="C45" s="15" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>guide_id</t>
         </is>
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>사용자 ID</t>
+          <t>안내문 ID</t>
         </is>
       </c>
       <c r="E45" s="15" t="inlineStr">
@@ -14449,7 +15170,7 @@
       </c>
       <c r="G45" s="15" t="inlineStr">
         <is>
-          <t>users.id</t>
+          <t>guides.id</t>
         </is>
       </c>
       <c r="H45" s="16" t="inlineStr">
@@ -14477,112 +15198,120 @@
       <c r="N45" s="15" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>feedbacks</t>
         </is>
       </c>
-      <c r="B46" s="21" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>안내문 피드백</t>
         </is>
       </c>
-      <c r="C46" s="21" t="inlineStr">
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>사용자 ID</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G46" s="15" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="H46" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I46" s="15" t="inlineStr"/>
+      <c r="J46" s="15" t="inlineStr"/>
+      <c r="K46" s="15" t="inlineStr">
+        <is>
+          <t>RG-04 · R-9</t>
+        </is>
+      </c>
+      <c r="L46" s="16" t="inlineStr">
+        <is>
+          <t>기존</t>
+        </is>
+      </c>
+      <c r="M46" s="16" t="inlineStr">
+        <is>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="N46" s="15" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>feedbacks</t>
+        </is>
+      </c>
+      <c r="B47" s="21" t="inlineStr">
+        <is>
+          <t>안내문 피드백</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="D46" s="21" t="inlineStr">
+      <c r="D47" s="21" t="inlineStr">
         <is>
           <t>평가</t>
         </is>
       </c>
-      <c r="E46" s="21" t="inlineStr">
+      <c r="E47" s="21" t="inlineStr">
         <is>
           <t>smallint</t>
         </is>
       </c>
-      <c r="F46" s="22" t="inlineStr"/>
-      <c r="G46" s="21" t="inlineStr"/>
-      <c r="H46" s="22" t="inlineStr">
+      <c r="F47" s="22" t="inlineStr"/>
+      <c r="G47" s="21" t="inlineStr"/>
+      <c r="H47" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I46" s="21" t="inlineStr"/>
-      <c r="J46" s="21" t="inlineStr">
+      <c r="I47" s="21" t="inlineStr"/>
+      <c r="J47" s="21" t="inlineStr">
         <is>
           <t>1 = 도움됐어요 / -1 = 도움 안 됐어요</t>
         </is>
       </c>
-      <c r="K46" s="21" t="inlineStr">
+      <c r="K47" s="21" t="inlineStr">
         <is>
           <t>RG-04 · R-9</t>
         </is>
       </c>
-      <c r="L46" s="22" t="inlineStr">
+      <c r="L47" s="22" t="inlineStr">
         <is>
           <t>수정</t>
         </is>
       </c>
-      <c r="M46" s="22" t="inlineStr">
+      <c r="M47" s="22" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N46" s="21" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="19" t="inlineStr">
-        <is>
-          <t>feedbacks</t>
-        </is>
-      </c>
-      <c r="B47" s="15" t="inlineStr">
-        <is>
-          <t>안내문 피드백</t>
-        </is>
-      </c>
-      <c r="C47" s="15" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="D47" s="15" t="inlineStr">
-        <is>
-          <t>의견</t>
-        </is>
-      </c>
-      <c r="E47" s="15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F47" s="16" t="inlineStr"/>
-      <c r="G47" s="15" t="inlineStr"/>
-      <c r="H47" s="16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I47" s="15" t="inlineStr"/>
-      <c r="J47" s="15" t="inlineStr"/>
-      <c r="K47" s="15" t="inlineStr">
-        <is>
-          <t>RG-04 · R-9</t>
-        </is>
-      </c>
-      <c r="L47" s="16" t="inlineStr">
-        <is>
-          <t>기존</t>
-        </is>
-      </c>
-      <c r="M47" s="16" t="inlineStr">
-        <is>
-          <t>v0.1</t>
-        </is>
-      </c>
-      <c r="N47" s="15" t="inlineStr"/>
+      <c r="N47" s="21" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="19" t="inlineStr">
@@ -14597,17 +15326,17 @@
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>의견</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F48" s="16" t="inlineStr"/>
@@ -14617,11 +15346,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I48" s="15" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+      <c r="I48" s="15" t="inlineStr"/>
       <c r="J48" s="15" t="inlineStr"/>
       <c r="K48" s="15" t="inlineStr">
         <is>
@@ -14643,66 +15368,58 @@
     <row r="49">
       <c r="A49" s="19" t="inlineStr">
         <is>
-          <t>drug_guides</t>
+          <t>feedbacks</t>
         </is>
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>약 안내문 (사전 저장)</t>
+          <t>안내문 피드백</t>
         </is>
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>edi_code</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>약 코드</t>
+          <t>생성 일시</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>varchar(9)</t>
-        </is>
-      </c>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G49" s="15" t="n"/>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F49" s="16" t="inlineStr"/>
+      <c r="G49" s="15" t="inlineStr"/>
       <c r="H49" s="16" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I49" s="15" t="n"/>
-      <c r="J49" s="15" t="inlineStr">
-        <is>
-          <t>약제급여목록 제품코드(EDI). 약 1개 = 1행. 급여목록에 없는 약은 행이 없음</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="J49" s="15" t="inlineStr"/>
       <c r="K49" s="15" t="inlineStr">
         <is>
-          <t>RG-04 · R-4 · 챗봇 출처</t>
+          <t>RG-04 · R-9</t>
         </is>
       </c>
       <c r="L49" s="16" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>기존</t>
         </is>
       </c>
       <c r="M49" s="16" t="inlineStr">
         <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N49" s="15" t="inlineStr">
-        <is>
-          <t>멘토링 4회차(10/13) · 10/14 팀 합의. 약 단위로 미리 만들어 두고 사람이 확인한 것만 분석에 씀. 약 1개 = 1행 (약효분류 표로 만든 안내문과 허가정보 문장이 같은 표에 들어감)</t>
-        </is>
-      </c>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="N49" s="15" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="19" t="inlineStr">
@@ -14717,20 +15434,24 @@
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>edi_code</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>안내 내용 (JSON)</t>
+          <t>약 코드</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>jsonb</t>
-        </is>
-      </c>
-      <c r="F50" s="16" t="n"/>
+          <t>varchar(9)</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G50" s="15" t="n"/>
       <c r="H50" s="16" t="inlineStr">
         <is>
@@ -14740,7 +15461,7 @@
       <c r="I50" s="15" t="n"/>
       <c r="J50" s="15" t="inlineStr">
         <is>
-          <t>category · purpose · caution(문장을 줄바꿈으로 이은 문자열) · cautions(문장 배열) · source. 먹는 법은 처방마다 달라 여기 두지 않음</t>
+          <t>약제급여목록 제품코드(EDI). 약 1개 = 1행. 급여목록에 없는 약은 행이 없음</t>
         </is>
       </c>
       <c r="K50" s="15" t="inlineStr">
@@ -14758,7 +15479,11 @@
           <t>v1.3</t>
         </is>
       </c>
-      <c r="N50" s="15" t="n"/>
+      <c r="N50" s="15" t="inlineStr">
+        <is>
+          <t>멘토링 4회차(10/13) · 10/14 팀 합의. 약 단위로 미리 만들어 두고 사람이 확인한 것만 분석에 씀. 약 1개 = 1행 (약효분류 표로 만든 안내문과 허가정보 문장이 같은 표에 들어감)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="19" t="inlineStr">
@@ -14773,12 +15498,12 @@
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>evidence_ids</t>
+          <t>content</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>근거 목록</t>
+          <t>안내 내용 (JSON)</t>
         </is>
       </c>
       <c r="E51" s="15" t="inlineStr">
@@ -14790,13 +15515,13 @@
       <c r="G51" s="15" t="n"/>
       <c r="H51" s="16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I51" s="15" t="n"/>
       <c r="J51" s="15" t="inlineStr">
         <is>
-          <t>[{kind: hira_class | drug_details, key, label, field(문장 번호), use(purpose · caution1~3), text(원문 문장)}] — 챗봇이 출처를 붙일 때 그대로 씀</t>
+          <t>category · purpose · caution(문장을 줄바꿈으로 이은 문자열) · cautions(문장 배열) · source. 먹는 법은 처방마다 달라 여기 두지 않음</t>
         </is>
       </c>
       <c r="K51" s="15" t="inlineStr">
@@ -14829,17 +15554,17 @@
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>prompt_ver</t>
+          <t>evidence_ids</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>프롬프트 버전</t>
+          <t>근거 목록</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="F52" s="16" t="n"/>
@@ -14852,7 +15577,7 @@
       <c r="I52" s="15" t="n"/>
       <c r="J52" s="15" t="inlineStr">
         <is>
-          <t>규칙 표로 만든 것은 rule-v1, AI 문장은 med-v8</t>
+          <t>[{kind: hira_class | drug_details, key, label, field(문장 번호), use(purpose · caution1~3), text(원문 문장)}] — 챗봇이 출처를 붙일 때 그대로 씀</t>
         </is>
       </c>
       <c r="K52" s="15" t="inlineStr">
@@ -14885,17 +15610,17 @@
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
-          <t>model_name</t>
+          <t>prompt_ver</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>모델 이름</t>
+          <t>프롬프트 버전</t>
         </is>
       </c>
       <c r="E53" s="15" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="F53" s="16" t="n"/>
@@ -14908,7 +15633,7 @@
       <c r="I53" s="15" t="n"/>
       <c r="J53" s="15" t="inlineStr">
         <is>
-          <t>AI 없이 규칙 표로 만든 안내문은 null. 값이 있으면 허가정보 문장(AI가 쓰고 규칙으로 걸러 냄)</t>
+          <t>규칙 표로 만든 것은 rule-v1, AI 문장은 med-v8</t>
         </is>
       </c>
       <c r="K53" s="15" t="inlineStr">
@@ -14941,34 +15666,30 @@
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>review_status</t>
+          <t>model_name</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>확인 상태</t>
+          <t>모델 이름</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="F54" s="16" t="n"/>
       <c r="G54" s="15" t="n"/>
       <c r="H54" s="16" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I54" s="15" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I54" s="15" t="n"/>
       <c r="J54" s="15" t="inlineStr">
         <is>
-          <t>draft / approved / rejected — 분석 때는 approved만 보여 줌 (멘토링 4회차 · 사람 확인 필수)</t>
+          <t>AI 없이 규칙 표로 만든 안내문은 null. 값이 있으면 허가정보 문장(AI가 쓰고 규칙으로 걸러 냄)</t>
         </is>
       </c>
       <c r="K54" s="15" t="inlineStr">
@@ -15001,28 +15722,36 @@
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
-          <t>reviewed_by</t>
+          <t>review_status</t>
         </is>
       </c>
       <c r="D55" s="15" t="inlineStr">
         <is>
-          <t>확인한 사람</t>
+          <t>확인 상태</t>
         </is>
       </c>
       <c r="E55" s="15" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="F55" s="16" t="n"/>
       <c r="G55" s="15" t="n"/>
       <c r="H55" s="16" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I55" s="15" t="n"/>
-      <c r="J55" s="15" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="J55" s="15" t="inlineStr">
+        <is>
+          <t>draft / approved / rejected — 분석 때는 approved만 보여 줌 (멘토링 4회차 · 사람 확인 필수)</t>
+        </is>
+      </c>
       <c r="K55" s="15" t="inlineStr">
         <is>
           <t>RG-04 · R-4 · 챗봇 출처</t>
@@ -15053,17 +15782,17 @@
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>reviewed_at</t>
+          <t>reviewed_by</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>확인 일시</t>
+          <t>확인한 사람</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="F56" s="16" t="n"/>
@@ -15105,12 +15834,12 @@
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>reviewed_at</t>
         </is>
       </c>
       <c r="D57" s="15" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>확인 일시</t>
         </is>
       </c>
       <c r="E57" s="15" t="inlineStr">
@@ -15125,11 +15854,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I57" s="15" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+      <c r="I57" s="15" t="n"/>
       <c r="J57" s="15" t="n"/>
       <c r="K57" s="15" t="inlineStr">
         <is>
@@ -15161,12 +15886,12 @@
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>수정 일시</t>
+          <t>생성 일시</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
@@ -15203,6 +15928,62 @@
         </is>
       </c>
       <c r="N58" s="15" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>drug_guides</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>약 안내문 (사전 저장)</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="D59" s="15" t="inlineStr">
+        <is>
+          <t>수정 일시</t>
+        </is>
+      </c>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F59" s="16" t="n"/>
+      <c r="G59" s="15" t="n"/>
+      <c r="H59" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I59" s="15" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="J59" s="15" t="n"/>
+      <c r="K59" s="15" t="inlineStr">
+        <is>
+          <t>RG-04 · R-4 · 챗봇 출처</t>
+        </is>
+      </c>
+      <c r="L59" s="16" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M59" s="16" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N59" s="15" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:N48"/>
@@ -15260,7 +16041,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>

--- a/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
@@ -9090,14 +9090,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I24" s="24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="I24" s="24" t="n"/>
       <c r="J24" s="24" t="inlineStr">
         <is>
-          <t>생활습관 질환 lifestyle_diseases.id 목록(HTN, DM2, DLP, CKD, IHD, STROKE, AF, COPD, OP, OA. 10/14 회의 3번 채연 안). 내 정보에서 선택. 분석은 처방전에 질병분류기호가 없을 때만 이 값으로 채움(출처 profile, 팩트표 kcd로 이음). 챗봇은 둘 다 씀 (10/19 수인 제안, 채연 확인 필요)</t>
+          <t>빈 목록은 앱이 넣음(DB 기본값 없음). 생활습관 질환 lifestyle_diseases.id 목록(HTN, DM2, DLP, CKD, IHD, STROKE, AF, COPD, OP, OA. 10/14 회의 3번 채연 안). 내 정보에서 선택. 분석은 처방전에 질병분류기호가 없을 때만 이 값으로 채움(출처 profile, 팩트표 kcd로 이음). 챗봇은 둘 다 씀 (10/19 수인 제안, 채연 확인 필요)</t>
         </is>
       </c>
       <c r="K24" s="24" t="inlineStr">
@@ -9374,14 +9370,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I29" s="24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="I29" s="24" t="n"/>
       <c r="J29" s="24" t="inlineStr">
         <is>
-          <t>[{ name, date }]. name은 50자 이내, date는 YYYY-MM-DD. 내 정보에서 선택 (10/14 회의 3번)</t>
+          <t>빈 목록은 앱이 넣음(DB 기본값 없음). [{ name, date }]. name은 50자 이내, date는 YYYY-MM-DD. 내 정보에서 선택 (10/14 회의 3번)</t>
         </is>
       </c>
       <c r="K29" s="24" t="inlineStr">

--- a/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
@@ -910,6 +910,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
@@ -7633,6 +7634,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -7901,6 +7903,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -9149,7 +9152,7 @@
       <c r="I25" s="24" t="n"/>
       <c r="J25" s="24" t="inlineStr">
         <is>
-          <t>yes / no. 여성만 내 정보에서 선택. 성별을 M으로 바꾸면 비움. 비어 있으면 임신 금기 점검을 건너뛰고 결과에 알림 (10/14 디코)</t>
+          <t>yes / no. 여성만 내 정보에서 선택. 성별을 M으로 바꾸면 비움. 임부금기 점검에 쓸지는 정하지 않음 (#101)</t>
         </is>
       </c>
       <c r="K25" s="24" t="inlineStr">
@@ -9557,6 +9560,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -12777,6 +12781,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -16033,6 +16038,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -17633,6 +17639,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -19761,6 +19768,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>

--- a/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
@@ -19,9 +19,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FHIR 대응" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'사용자'!$A$4:$N$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'사용자'!$A$4:$N$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'입력'!$A$4:$N$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'분석'!$A$4:$N$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'분석'!$A$4:$N$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'챗봇'!$A$4:$N$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'실천·보상'!$A$4:$N$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'마스터'!$A$4:$N$106</definedName>
@@ -910,7 +910,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
@@ -4228,7 +4227,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E169"/>
+  <dimension ref="A1:E171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7492,6 +7491,51 @@
       </c>
       <c r="E169" s="10" t="n"/>
     </row>
+    <row r="170" hidden="1" outlineLevel="1">
+      <c r="A170" s="10" t="n"/>
+      <c r="B170" s="10" t="inlineStr">
+        <is>
+          <t>분석 / feedbacks — 유일 조건 추가, rating 필수</t>
+        </is>
+      </c>
+      <c r="C170" s="10" t="inlineStr">
+        <is>
+          <t>rating N(없어도 됨), 유일 조건 없음</t>
+        </is>
+      </c>
+      <c r="D170" s="10" t="inlineStr">
+        <is>
+          <t>rating Y(필수), unique (guide_id, user_id)
+사유: R-9를 서버에 구현하면서 한 사람이 안내문 하나에 하나만 남기고 다시 보내면 덮어쓰도록 함 (10/19, 마이그레이션 9번)</t>
+        </is>
+      </c>
+      <c r="E170" s="10" t="n"/>
+    </row>
+    <row r="171" hidden="1" outlineLevel="1">
+      <c r="A171" s="10" t="n"/>
+      <c r="B171" s="10" t="inlineStr">
+        <is>
+          <t>마스터 / evidence_chunks — 테이블 신규</t>
+        </is>
+      </c>
+      <c r="C171" s="10" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="D171" s="10" t="inlineStr">
+        <is>
+          <t>필드 18개: id, chunk_id, kind, drug_code, disease_code, section, group_key, seq, source_order, heading, content, search_text, embed_text, drug_name, source_ids, embedding, embedding_model, created_at
+사유: 챗봇 근거 검색(RAG)에 쓰는 약 허가문서 문장과 팩트표 조각. 벡터는 pgvector, 글자 조각 검색은 pg_trgm (10/19, 마이그레이션 10번)</t>
+        </is>
+      </c>
+      <c r="E171" s="10" t="n"/>
+    </row>
+    <row r="172" hidden="1" outlineLevel="1"/>
+    <row r="173" hidden="1" outlineLevel="1"/>
+    <row r="174" hidden="1" outlineLevel="1"/>
+    <row r="175"/>
+    <row r="176"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A2:E2"/>
@@ -8783,7 +8827,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N21"/>
+  <autoFilter ref="A4:N36"/>
   <dataValidations count="3">
     <dataValidation sqref="H5:H300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
@@ -8838,7 +8882,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -12059,7 +12102,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -14506,13 +14548,13 @@
       <c r="G46" s="21" t="inlineStr"/>
       <c r="H46" s="22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I46" s="21" t="inlineStr"/>
       <c r="J46" s="21" t="inlineStr">
         <is>
-          <t>1 = 도움됐어요 / -1 = 도움 안 됐어요</t>
+          <t>1 = 도움됐어요 / -1 = 도움 안 됐어요 · (guide_id, user_id) 유일, 다시 보내면 덮어씀</t>
         </is>
       </c>
       <c r="K46" s="21" t="inlineStr">
@@ -14527,7 +14569,7 @@
       </c>
       <c r="M46" s="22" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.5 초안</t>
         </is>
       </c>
       <c r="N46" s="21" t="inlineStr"/>
@@ -15205,7 +15247,7 @@
       <c r="N58" s="15" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N48"/>
+  <autoFilter ref="A4:N59"/>
   <dataValidations count="3">
     <dataValidation sqref="H5:H300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
@@ -15260,7 +15302,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -18956,7 +18997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N106"/>
+  <dimension ref="A1:N124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -24804,6 +24845,1034 @@
       </c>
       <c r="N106" s="24" t="n"/>
     </row>
+    <row r="107">
+      <c r="A107" s="23" t="inlineStr">
+        <is>
+          <t>evidence_chunks</t>
+        </is>
+      </c>
+      <c r="B107" s="24" t="inlineStr">
+        <is>
+          <t>근거 조각</t>
+        </is>
+      </c>
+      <c r="C107" s="24" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D107" s="24" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E107" s="24" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F107" s="25" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G107" s="24" t="n"/>
+      <c r="H107" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I107" s="24" t="n"/>
+      <c r="J107" s="24" t="n"/>
+      <c r="K107" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 · 챗봇 근거 검색</t>
+        </is>
+      </c>
+      <c r="L107" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M107" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N107" s="24" t="inlineStr">
+        <is>
+          <t>RAG 근거 검색용 조각 표. 챗봇 서버와 같이 읽음. 마이그레이션 10번(vector, pg_trgm 확장 포함). 적재는 scripts/rag/load_evidence_chunks.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="23" t="inlineStr">
+        <is>
+          <t>evidence_chunks</t>
+        </is>
+      </c>
+      <c r="B108" s="24" t="inlineStr">
+        <is>
+          <t>근거 조각</t>
+        </is>
+      </c>
+      <c r="C108" s="24" t="inlineStr">
+        <is>
+          <t>chunk_id</t>
+        </is>
+      </c>
+      <c r="D108" s="24" t="inlineStr">
+        <is>
+          <t>출처 번호</t>
+        </is>
+      </c>
+      <c r="E108" s="24" t="inlineStr">
+        <is>
+          <t>varchar(150)</t>
+        </is>
+      </c>
+      <c r="F108" s="25" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
+      <c r="G108" s="24" t="n"/>
+      <c r="H108" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I108" s="24" t="n"/>
+      <c r="J108" s="24" t="inlineStr">
+        <is>
+          <t>약 허가문서는 D:&lt;약코드&gt;:S12, 팩트표는 F:..., 교차 규칙은 X:... 챗봇이 돌려받는 sentenceId</t>
+        </is>
+      </c>
+      <c r="K108" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 · 챗봇 근거 검색</t>
+        </is>
+      </c>
+      <c r="L108" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M108" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N108" s="24" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="23" t="inlineStr">
+        <is>
+          <t>evidence_chunks</t>
+        </is>
+      </c>
+      <c r="B109" s="24" t="inlineStr">
+        <is>
+          <t>근거 조각</t>
+        </is>
+      </c>
+      <c r="C109" s="24" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="D109" s="24" t="inlineStr">
+        <is>
+          <t>종류</t>
+        </is>
+      </c>
+      <c r="E109" s="24" t="inlineStr">
+        <is>
+          <t>varchar(10)</t>
+        </is>
+      </c>
+      <c r="F109" s="25" t="n"/>
+      <c r="G109" s="24" t="n"/>
+      <c r="H109" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I109" s="24" t="n"/>
+      <c r="J109" s="24" t="inlineStr">
+        <is>
+          <t>drug(약 허가문서 문장) / fact(생활습관 팩트표) / cross(질환이 겹칠 때 규칙)</t>
+        </is>
+      </c>
+      <c r="K109" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 · 챗봇 근거 검색</t>
+        </is>
+      </c>
+      <c r="L109" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M109" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N109" s="24" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="23" t="inlineStr">
+        <is>
+          <t>evidence_chunks</t>
+        </is>
+      </c>
+      <c r="B110" s="24" t="inlineStr">
+        <is>
+          <t>근거 조각</t>
+        </is>
+      </c>
+      <c r="C110" s="24" t="inlineStr">
+        <is>
+          <t>drug_code</t>
+        </is>
+      </c>
+      <c r="D110" s="24" t="inlineStr">
+        <is>
+          <t>약 코드</t>
+        </is>
+      </c>
+      <c r="E110" s="24" t="inlineStr">
+        <is>
+          <t>varchar(9)</t>
+        </is>
+      </c>
+      <c r="F110" s="25" t="n"/>
+      <c r="G110" s="24" t="inlineStr">
+        <is>
+          <t>drug_products.edi_code</t>
+        </is>
+      </c>
+      <c r="H110" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I110" s="24" t="n"/>
+      <c r="J110" s="24" t="inlineStr">
+        <is>
+          <t>kind = drug일 때. 인덱스</t>
+        </is>
+      </c>
+      <c r="K110" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 · 챗봇 근거 검색</t>
+        </is>
+      </c>
+      <c r="L110" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M110" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N110" s="24" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="23" t="inlineStr">
+        <is>
+          <t>evidence_chunks</t>
+        </is>
+      </c>
+      <c r="B111" s="24" t="inlineStr">
+        <is>
+          <t>근거 조각</t>
+        </is>
+      </c>
+      <c r="C111" s="24" t="inlineStr">
+        <is>
+          <t>disease_code</t>
+        </is>
+      </c>
+      <c r="D111" s="24" t="inlineStr">
+        <is>
+          <t>질환 코드</t>
+        </is>
+      </c>
+      <c r="E111" s="24" t="inlineStr">
+        <is>
+          <t>varchar(10)</t>
+        </is>
+      </c>
+      <c r="F111" s="25" t="n"/>
+      <c r="G111" s="24" t="n"/>
+      <c r="H111" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I111" s="24" t="n"/>
+      <c r="J111" s="24" t="inlineStr">
+        <is>
+          <t>팩트표 질환 id (예: HTN). kind = fact일 때. 인덱스</t>
+        </is>
+      </c>
+      <c r="K111" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 · 챗봇 근거 검색</t>
+        </is>
+      </c>
+      <c r="L111" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M111" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N111" s="24" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="23" t="inlineStr">
+        <is>
+          <t>evidence_chunks</t>
+        </is>
+      </c>
+      <c r="B112" s="24" t="inlineStr">
+        <is>
+          <t>근거 조각</t>
+        </is>
+      </c>
+      <c r="C112" s="24" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="D112" s="24" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="E112" s="24" t="inlineStr">
+        <is>
+          <t>char(1)</t>
+        </is>
+      </c>
+      <c r="F112" s="25" t="n"/>
+      <c r="G112" s="24" t="n"/>
+      <c r="H112" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I112" s="24" t="n"/>
+      <c r="J112" s="24" t="inlineStr">
+        <is>
+          <t>E 효능효과 / S 주의사항 / P 용법용량</t>
+        </is>
+      </c>
+      <c r="K112" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 · 챗봇 근거 검색</t>
+        </is>
+      </c>
+      <c r="L112" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M112" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N112" s="24" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="23" t="inlineStr">
+        <is>
+          <t>evidence_chunks</t>
+        </is>
+      </c>
+      <c r="B113" s="24" t="inlineStr">
+        <is>
+          <t>근거 조각</t>
+        </is>
+      </c>
+      <c r="C113" s="24" t="inlineStr">
+        <is>
+          <t>group_key</t>
+        </is>
+      </c>
+      <c r="D113" s="24" t="inlineStr">
+        <is>
+          <t>소항목 묶음 키</t>
+        </is>
+      </c>
+      <c r="E113" s="24" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="F113" s="25" t="n"/>
+      <c r="G113" s="24" t="n"/>
+      <c r="H113" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I113" s="24" t="n"/>
+      <c r="J113" s="24" t="inlineStr">
+        <is>
+          <t>고른 조각의 같은 소항목 문장을 함께 보냄(최대 8개). 인덱스</t>
+        </is>
+      </c>
+      <c r="K113" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 · 챗봇 근거 검색</t>
+        </is>
+      </c>
+      <c r="L113" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M113" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N113" s="24" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="23" t="inlineStr">
+        <is>
+          <t>evidence_chunks</t>
+        </is>
+      </c>
+      <c r="B114" s="24" t="inlineStr">
+        <is>
+          <t>근거 조각</t>
+        </is>
+      </c>
+      <c r="C114" s="24" t="inlineStr">
+        <is>
+          <t>seq</t>
+        </is>
+      </c>
+      <c r="D114" s="24" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="E114" s="24" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F114" s="25" t="n"/>
+      <c r="G114" s="24" t="n"/>
+      <c r="H114" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I114" s="24" t="n"/>
+      <c r="J114" s="24" t="inlineStr">
+        <is>
+          <t>같은 약, 같은 구분 안에서의 순서</t>
+        </is>
+      </c>
+      <c r="K114" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 · 챗봇 근거 검색</t>
+        </is>
+      </c>
+      <c r="L114" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M114" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N114" s="24" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="23" t="inlineStr">
+        <is>
+          <t>evidence_chunks</t>
+        </is>
+      </c>
+      <c r="B115" s="24" t="inlineStr">
+        <is>
+          <t>근거 조각</t>
+        </is>
+      </c>
+      <c r="C115" s="24" t="inlineStr">
+        <is>
+          <t>source_order</t>
+        </is>
+      </c>
+      <c r="D115" s="24" t="inlineStr">
+        <is>
+          <t>시험 조각 순서</t>
+        </is>
+      </c>
+      <c r="E115" s="24" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F115" s="25" t="n"/>
+      <c r="G115" s="24" t="n"/>
+      <c r="H115" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I115" s="24" t="n"/>
+      <c r="J115" s="24" t="inlineStr">
+        <is>
+          <t>시험에서 쓴 조각 순서. 후보 목록 순서를 같게 하려고 보존</t>
+        </is>
+      </c>
+      <c r="K115" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 · 챗봇 근거 검색</t>
+        </is>
+      </c>
+      <c r="L115" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M115" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N115" s="24" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="23" t="inlineStr">
+        <is>
+          <t>evidence_chunks</t>
+        </is>
+      </c>
+      <c r="B116" s="24" t="inlineStr">
+        <is>
+          <t>근거 조각</t>
+        </is>
+      </c>
+      <c r="C116" s="24" t="inlineStr">
+        <is>
+          <t>heading</t>
+        </is>
+      </c>
+      <c r="D116" s="24" t="inlineStr">
+        <is>
+          <t>제목 경로</t>
+        </is>
+      </c>
+      <c r="E116" s="24" t="inlineStr">
+        <is>
+          <t>varchar(300)</t>
+        </is>
+      </c>
+      <c r="F116" s="25" t="n"/>
+      <c r="G116" s="24" t="n"/>
+      <c r="H116" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I116" s="24" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="J116" s="24" t="inlineStr">
+        <is>
+          <t>큰제목 &gt; 소항목</t>
+        </is>
+      </c>
+      <c r="K116" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 · 챗봇 근거 검색</t>
+        </is>
+      </c>
+      <c r="L116" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M116" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N116" s="24" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="23" t="inlineStr">
+        <is>
+          <t>evidence_chunks</t>
+        </is>
+      </c>
+      <c r="B117" s="24" t="inlineStr">
+        <is>
+          <t>근거 조각</t>
+        </is>
+      </c>
+      <c r="C117" s="24" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="D117" s="24" t="inlineStr">
+        <is>
+          <t>근거 글</t>
+        </is>
+      </c>
+      <c r="E117" s="24" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F117" s="25" t="n"/>
+      <c r="G117" s="24" t="n"/>
+      <c r="H117" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I117" s="24" t="n"/>
+      <c r="J117" s="24" t="inlineStr">
+        <is>
+          <t>근거 글 원문</t>
+        </is>
+      </c>
+      <c r="K117" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 · 챗봇 근거 검색</t>
+        </is>
+      </c>
+      <c r="L117" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M117" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N117" s="24" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="23" t="inlineStr">
+        <is>
+          <t>evidence_chunks</t>
+        </is>
+      </c>
+      <c r="B118" s="24" t="inlineStr">
+        <is>
+          <t>근거 조각</t>
+        </is>
+      </c>
+      <c r="C118" s="24" t="inlineStr">
+        <is>
+          <t>search_text</t>
+        </is>
+      </c>
+      <c r="D118" s="24" t="inlineStr">
+        <is>
+          <t>글자 조각 검색용 글</t>
+        </is>
+      </c>
+      <c r="E118" s="24" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F118" s="25" t="n"/>
+      <c r="G118" s="24" t="n"/>
+      <c r="H118" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I118" s="24" t="n"/>
+      <c r="J118" s="24" t="inlineStr">
+        <is>
+          <t>heading + content. pg_trgm word_similarity로 비교</t>
+        </is>
+      </c>
+      <c r="K118" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 · 챗봇 근거 검색</t>
+        </is>
+      </c>
+      <c r="L118" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M118" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N118" s="24" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="23" t="inlineStr">
+        <is>
+          <t>evidence_chunks</t>
+        </is>
+      </c>
+      <c r="B119" s="24" t="inlineStr">
+        <is>
+          <t>근거 조각</t>
+        </is>
+      </c>
+      <c r="C119" s="24" t="inlineStr">
+        <is>
+          <t>embed_text</t>
+        </is>
+      </c>
+      <c r="D119" s="24" t="inlineStr">
+        <is>
+          <t>임베딩에 넣은 글</t>
+        </is>
+      </c>
+      <c r="E119" s="24" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F119" s="25" t="n"/>
+      <c r="G119" s="24" t="n"/>
+      <c r="H119" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I119" s="24" t="n"/>
+      <c r="J119" s="24" t="inlineStr">
+        <is>
+          <t>약 이름 + 구분 + 경로 + 본문</t>
+        </is>
+      </c>
+      <c r="K119" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 · 챗봇 근거 검색</t>
+        </is>
+      </c>
+      <c r="L119" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M119" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N119" s="24" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="23" t="inlineStr">
+        <is>
+          <t>evidence_chunks</t>
+        </is>
+      </c>
+      <c r="B120" s="24" t="inlineStr">
+        <is>
+          <t>근거 조각</t>
+        </is>
+      </c>
+      <c r="C120" s="24" t="inlineStr">
+        <is>
+          <t>drug_name</t>
+        </is>
+      </c>
+      <c r="D120" s="24" t="inlineStr">
+        <is>
+          <t>약 이름</t>
+        </is>
+      </c>
+      <c r="E120" s="24" t="inlineStr">
+        <is>
+          <t>varchar(300)</t>
+        </is>
+      </c>
+      <c r="F120" s="25" t="n"/>
+      <c r="G120" s="24" t="n"/>
+      <c r="H120" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I120" s="24" t="n"/>
+      <c r="J120" s="24" t="inlineStr">
+        <is>
+          <t>근거 머리말과 질문 프롬프트에 쓰는 이름</t>
+        </is>
+      </c>
+      <c r="K120" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 · 챗봇 근거 검색</t>
+        </is>
+      </c>
+      <c r="L120" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M120" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N120" s="24" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="23" t="inlineStr">
+        <is>
+          <t>evidence_chunks</t>
+        </is>
+      </c>
+      <c r="B121" s="24" t="inlineStr">
+        <is>
+          <t>근거 조각</t>
+        </is>
+      </c>
+      <c r="C121" s="24" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+      <c r="D121" s="24" t="inlineStr">
+        <is>
+          <t>합친 문장 번호</t>
+        </is>
+      </c>
+      <c r="E121" s="24" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="F121" s="25" t="n"/>
+      <c r="G121" s="24" t="n"/>
+      <c r="H121" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I121" s="24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J121" s="24" t="inlineStr">
+        <is>
+          <t>이 조각이 합친 허가정보 문장 번호들</t>
+        </is>
+      </c>
+      <c r="K121" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 · 챗봇 근거 검색</t>
+        </is>
+      </c>
+      <c r="L121" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M121" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N121" s="24" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="23" t="inlineStr">
+        <is>
+          <t>evidence_chunks</t>
+        </is>
+      </c>
+      <c r="B122" s="24" t="inlineStr">
+        <is>
+          <t>근거 조각</t>
+        </is>
+      </c>
+      <c r="C122" s="24" t="inlineStr">
+        <is>
+          <t>embedding</t>
+        </is>
+      </c>
+      <c r="D122" s="24" t="inlineStr">
+        <is>
+          <t>벡터</t>
+        </is>
+      </c>
+      <c r="E122" s="24" t="inlineStr">
+        <is>
+          <t>vector(1536)</t>
+        </is>
+      </c>
+      <c r="F122" s="25" t="n"/>
+      <c r="G122" s="24" t="n"/>
+      <c r="H122" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I122" s="24" t="n"/>
+      <c r="J122" s="24" t="inlineStr">
+        <is>
+          <t>pgvector. text-embedding-3-small. 벡터 인덱스는 걸지 않음(범위를 좁힌 안이 평균 수백 개)</t>
+        </is>
+      </c>
+      <c r="K122" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 · 챗봇 근거 검색</t>
+        </is>
+      </c>
+      <c r="L122" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M122" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N122" s="24" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="23" t="inlineStr">
+        <is>
+          <t>evidence_chunks</t>
+        </is>
+      </c>
+      <c r="B123" s="24" t="inlineStr">
+        <is>
+          <t>근거 조각</t>
+        </is>
+      </c>
+      <c r="C123" s="24" t="inlineStr">
+        <is>
+          <t>embedding_model</t>
+        </is>
+      </c>
+      <c r="D123" s="24" t="inlineStr">
+        <is>
+          <t>벡터 모델</t>
+        </is>
+      </c>
+      <c r="E123" s="24" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="F123" s="25" t="n"/>
+      <c r="G123" s="24" t="n"/>
+      <c r="H123" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I123" s="24" t="n"/>
+      <c r="J123" s="24" t="inlineStr">
+        <is>
+          <t>벡터를 만든 모델. 바꾸면 새로 만들어야 함</t>
+        </is>
+      </c>
+      <c r="K123" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 · 챗봇 근거 검색</t>
+        </is>
+      </c>
+      <c r="L123" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M123" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N123" s="24" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="23" t="inlineStr">
+        <is>
+          <t>evidence_chunks</t>
+        </is>
+      </c>
+      <c r="B124" s="24" t="inlineStr">
+        <is>
+          <t>근거 조각</t>
+        </is>
+      </c>
+      <c r="C124" s="24" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D124" s="24" t="inlineStr">
+        <is>
+          <t>생성 일시</t>
+        </is>
+      </c>
+      <c r="E124" s="24" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F124" s="25" t="n"/>
+      <c r="G124" s="24" t="n"/>
+      <c r="H124" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I124" s="24" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="J124" s="24" t="n"/>
+      <c r="K124" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 · 챗봇 근거 검색</t>
+        </is>
+      </c>
+      <c r="L124" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M124" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N124" s="24" t="n"/>
+    </row>
   </sheetData>
   <autoFilter ref="A4:N106"/>
   <dataValidations count="3">

--- a/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
@@ -7544,7 +7544,7 @@
       <c r="D170" s="10" t="inlineStr">
         <is>
           <t>필드 11개: user_id(PK, users와 1:1), smoking, drinking, diseases, pregnant, dialysis, height_cm, weight_kg, upcoming_exams, created_at, updated_at
-사유: 4회차 멘토링(건강 정보는 회원가입과 내 정보에서 받아 DB에), 10/14 회의 3번과 디코. 음주, 흡연 값은 국민건강영양조사 문항 기준 (10/19 수인, 채연 확인 필요)</t>
+사유: 4회차 멘토링(건강 정보는 회원가입과 내 정보에서 받아 DB에), 10/14 회의 3번과 디코. 음주, 흡연 값은 국민건강영양조사 문항 기준 (10/19 수인)</t>
         </is>
       </c>
       <c r="E170" s="10" t="n"/>
@@ -9021,7 +9021,7 @@
       <c r="I22" s="24" t="n"/>
       <c r="J22" s="24" t="inlineStr">
         <is>
-          <t>daily / sometimes / past / never / unknown. 국민건강영양조사 BS3_1에 "잘 모르겠어요"를 더함. 가입 때 필수 (10/19 수인, 채연 확인 필요)</t>
+          <t>daily / sometimes / past / never / unknown. 국민건강영양조사 BS3_1에 "잘 모르겠어요"를 더함. 가입 때 필수 (10/19 수인)</t>
         </is>
       </c>
       <c r="K22" s="24" t="inlineStr">
@@ -9077,7 +9077,7 @@
       <c r="I23" s="24" t="n"/>
       <c r="J23" s="24" t="inlineStr">
         <is>
-          <t>none / lt_monthly / monthly / 2_4_monthly / 2_3_weekly / 4plus_weekly / unknown. 국민건강영양조사 BD1_11(최근 1년 음주 빈도)에 "잘 모르겠어요"를 더함. 가입 때 필수 (10/19 수인, 채연 확인 필요)</t>
+          <t>none / lt_monthly / monthly / 2_4_monthly / 2_3_weekly / 4plus_weekly / unknown. 국민건강영양조사 BD1_11(최근 1년 음주 빈도)에 "잘 모르겠어요"를 더함. 가입 때 필수 (10/19 수인)</t>
         </is>
       </c>
       <c r="K23" s="24" t="inlineStr">
@@ -9133,7 +9133,7 @@
       <c r="I24" s="24" t="n"/>
       <c r="J24" s="24" t="inlineStr">
         <is>
-          <t>빈 목록은 앱이 넣음(DB 기본값 없음). 생활습관 질환 lifestyle_diseases.id 목록(HTN, DM2, DLP, CKD, IHD, STROKE, AF, COPD, OP, OA. 10/14 회의 3번 채연 안). 내 정보에서 선택. 분석은 처방전에 질병분류기호가 없을 때만 이 값으로 채움(출처 profile, 팩트표 kcd로 이음). 챗봇은 둘 다 씀 (10/19 수인 제안, 채연 확인 필요)</t>
+          <t>빈 목록은 앱이 넣음(DB 기본값 없음). 생활습관 질환 lifestyle_diseases.id 목록(HTN, DM2, DLP, CKD, IHD, STROKE, AF, COPD, OP, OA. 10/14 회의 3번 채연 안). 내 정보에서 선택. 분석은 처방전 질환과 이 값을 합쳐 씀: 질환 기준으로 중복을 빼고(팩트표는 한 질환에 코드가 여러 개라 코드가 달라도 같은 질환이면 하나), 팩트표의 대표 질병분류기호(예: HTN은 I10)로 바꿔 넣고, 출처는 profile(analysis_diseases.origin에 profile 추가), RG-05-E1을 미리 채워 사용자가 빼거나 더함. 챗봇은 둘 다 고정 정보로 씀 (10/19 채연 제안으로 확인됨, 구현은 #105 다음 PR에서 수인, 리뷰 채연)</t>
         </is>
       </c>
       <c r="K24" s="24" t="inlineStr">

--- a/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
@@ -4265,7 +4265,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E174"/>
+  <dimension ref="A1:E175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7626,6 +7626,26 @@
         </is>
       </c>
       <c r="E174" s="10" t="n"/>
+    </row>
+    <row r="175" outlineLevel="1">
+      <c r="A175" s="10" t="n"/>
+      <c r="B175" s="10" t="inlineStr">
+        <is>
+          <t>분석 / analysis_diseases.origin: 값 추가 (이슈 #101)</t>
+        </is>
+      </c>
+      <c r="C175" s="10" t="inlineStr">
+        <is>
+          <t>prescription / user</t>
+        </is>
+      </c>
+      <c r="D175" s="10" t="inlineStr">
+        <is>
+          <t>prescription / profile / user
+사유: 분석 질환은 처방전 질환과 내 정보 질환을 합쳐 씀. 처방전에 같은 질환이 있으면 코드가 달라도 내 정보 질환은 넣지 않음 (10/19 합의, 10/20 수인, 마이그레이션 12번)</t>
+        </is>
+      </c>
+      <c r="E175" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -13849,7 +13869,7 @@
       <c r="I21" s="24" t="inlineStr"/>
       <c r="J21" s="24" t="inlineStr">
         <is>
-          <t>prescription(처방전 코드) / user(RG-05-E1에서 직접 선택)</t>
+          <t>prescription(처방전 코드) / profile(내 정보 질환, 대표 질병분류기호로 바꿔 넣음. 처방전에 같은 질환이 있으면 넣지 않음, 10/19 합의, #101) / user(RG-05-E1에서 직접 선택)</t>
         </is>
       </c>
       <c r="K21" s="24" t="inlineStr">

--- a/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
@@ -4265,7 +4265,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E175"/>
+  <dimension ref="A1:E179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7646,6 +7646,84 @@
         </is>
       </c>
       <c r="E175" s="10" t="n"/>
+    </row>
+    <row r="176" outlineLevel="1">
+      <c r="A176" s="10" t="n"/>
+      <c r="B176" s="10" t="inlineStr">
+        <is>
+          <t>챗봇 / chat_messages.reply_to_id: 필드 추가 (이슈 #100)</t>
+        </is>
+      </c>
+      <c r="C176" s="10" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="D176" s="10" t="inlineStr">
+        <is>
+          <t>reply_to_id bigint, FK chat_messages.id, N, 답 줄이 어느 질문의 답인지 질문 줄 번호
+사유: 다시 시도 때 답 줄을 찾고, 맨 아래에 생긴 답에 질문을 인용함 (수인 10/22)</t>
+        </is>
+      </c>
+      <c r="E176" s="10" t="n"/>
+    </row>
+    <row r="177" outlineLevel="1">
+      <c r="A177" s="10" t="n"/>
+      <c r="B177" s="10" t="inlineStr">
+        <is>
+          <t>챗봇 / chat_messages.safety: 필드 추가 (이슈 #100)</t>
+        </is>
+      </c>
+      <c r="C177" s="10" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="D177" s="10" t="inlineStr">
+        <is>
+          <t>safety jsonb, N, 서버가 감지한 긴급, 자해 결과 { types, overdose, rule }
+사유: 다시 들어왔을 때 카드를 그대로 그림. 원문은 담지 않음 (수인 10/22)</t>
+        </is>
+      </c>
+      <c r="E177" s="10" t="n"/>
+    </row>
+    <row r="178" outlineLevel="1">
+      <c r="A178" s="10" t="n"/>
+      <c r="B178" s="10" t="inlineStr">
+        <is>
+          <t>챗봇 / chat_messages.status: 설명 변경 (이슈 #100)</t>
+        </is>
+      </c>
+      <c r="C178" s="10" t="inlineStr">
+        <is>
+          <t>generating 또는 done. 화면을 나갔다 와도 만드는 중인 답을 알 수 있게 함. 사용자 줄은 늘 done. 실패는 두지 않음: 서버가 실패하면 답을 저장하지 않고 앱이 E6을 보여 줌 (이슈 #88)</t>
+        </is>
+      </c>
+      <c r="D178" s="10" t="inlineStr">
+        <is>
+          <t>generating / done. 화면을 나갔다 와도 만드는 중인 답을 알 수 있게 (이슈 #88). 사용자 줄은 늘 done. 실패(failed)는 두지 않음: 서버가 실패하면 만드는 중이던 줄을 지우고 앱이 E6을 보여 줌. 30초를 넘긴 줄은 다시 시도 때 지움 (수인 10/12 확정, 줄을 지우는 것은 10/22 #100)</t>
+        </is>
+      </c>
+      <c r="E178" s="10" t="n"/>
+    </row>
+    <row r="179" outlineLevel="1">
+      <c r="A179" s="10" t="n"/>
+      <c r="B179" s="10" t="inlineStr">
+        <is>
+          <t>챗봇 / chat_sessions.analysis_id: 설명 변경 (이슈 #100)</t>
+        </is>
+      </c>
+      <c r="C179" s="10" t="inlineStr">
+        <is>
+          <t>null이면 일반 질문 모드 (분석 전)</t>
+        </is>
+      </c>
+      <c r="D179" s="10" t="inlineStr">
+        <is>
+          <t>null이면 일반 질문 모드 (분석 전). 분석을 지우면(R-8) 비움(set null). 대화까지 지울지는 채연과 정함 (이슈 #100, 수인 10/22)</t>
+        </is>
+      </c>
+      <c r="E179" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -16060,7 +16138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16329,7 +16407,7 @@
       <c r="I7" s="21" t="n"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t>null이면 일반 질문 모드 (분석 전)</t>
+          <t>null이면 일반 질문 모드 (분석 전). 분석을 지우면(R-8) 비움(set null). 대화까지 지울지는 채연과 정함 (이슈 #100, 수인 10/22)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
@@ -16344,7 +16422,7 @@
       </c>
       <c r="M7" s="22" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.5</t>
         </is>
       </c>
       <c r="N7" s="21" t="n"/>
@@ -17198,21 +17276,29 @@
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>context_card</t>
+          <t>reply_to_id</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>맥락 카드</t>
+          <t>답한 질문 ID</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>jsonb</t>
-        </is>
-      </c>
-      <c r="F23" s="25" t="n"/>
-      <c r="G23" s="24" t="n"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F23" s="25" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>chat_messages.id</t>
+        </is>
+      </c>
       <c r="H23" s="25" t="inlineStr">
         <is>
           <t>N</t>
@@ -17221,12 +17307,12 @@
       <c r="I23" s="24" t="n"/>
       <c r="J23" s="24" t="inlineStr">
         <is>
-          <t>1단계 하루 한 대화에서 붙인 분석 맥락 { analysisId, context } — 다시 들어왔을 때 카드를 그대로 그림 (H-7)</t>
+          <t>답 줄이 어느 질문의 답인지 질문 줄 번호. 답 줄만 채움. 다시 시도 때 답 줄을 찾고, 맨 아래에 생긴 답에 질문을 인용함 (이슈 #100, 수인 10/22)</t>
         </is>
       </c>
       <c r="K23" s="24" t="inlineStr">
         <is>
-          <t>CB-01 · H-2 · H-3 · H-7</t>
+          <t>CB-01 / H-2 / H-3</t>
         </is>
       </c>
       <c r="L23" s="25" t="inlineStr">
@@ -17236,7 +17322,7 @@
       </c>
       <c r="M23" s="25" t="inlineStr">
         <is>
-          <t>v1.3</t>
+          <t>v1.5</t>
         </is>
       </c>
       <c r="N23" s="24" t="n"/>
@@ -17254,12 +17340,12 @@
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>safety_card</t>
+          <t>context_card</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>안전성 점검 카드</t>
+          <t>맥락 카드</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -17277,12 +17363,12 @@
       <c r="I24" s="24" t="n"/>
       <c r="J24" s="24" t="inlineStr">
         <is>
-          <t>안전성 점검 결과 카드 { analysisId, warningIds }. 카드가 붙는 답도 answer_type은 normal. 카드가 없으면 비어 있음 (이슈 #88)</t>
+          <t>1단계 하루 한 대화에서 붙인 분석 맥락 { analysisId, context } — 다시 들어왔을 때 카드를 그대로 그림 (H-7)</t>
         </is>
       </c>
       <c r="K24" s="24" t="inlineStr">
         <is>
-          <t>CB-01 / H-2 / H-3</t>
+          <t>CB-01 · H-2 · H-3 · H-7</t>
         </is>
       </c>
       <c r="L24" s="25" t="inlineStr">
@@ -17292,7 +17378,7 @@
       </c>
       <c r="M24" s="25" t="inlineStr">
         <is>
-          <t>v1.5</t>
+          <t>v1.3</t>
         </is>
       </c>
       <c r="N24" s="24" t="n"/>
@@ -17310,34 +17396,30 @@
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>safety_card</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>답변 상태</t>
+          <t>안전성 점검 카드</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="F25" s="25" t="n"/>
       <c r="G25" s="24" t="n"/>
       <c r="H25" s="25" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I25" s="24" t="inlineStr">
-        <is>
-          <t>'done'</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="n"/>
       <c r="J25" s="24" t="inlineStr">
         <is>
-          <t>generating 또는 done. 화면을 나갔다 와도 만드는 중인 답을 알 수 있게 함. 사용자 줄은 늘 done. 실패는 두지 않음: 서버가 실패하면 답을 저장하지 않고 앱이 E6을 보여 줌 (이슈 #88)</t>
+          <t>안전성 점검 결과 카드 { analysisId, warningIds }. 카드가 붙는 답도 answer_type은 normal. 카드가 없으면 비어 있음 (이슈 #88)</t>
         </is>
       </c>
       <c r="K25" s="24" t="inlineStr">
@@ -17370,17 +17452,17 @@
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>safety</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>모델 이름</t>
+          <t>긴급, 자해 감지 결과</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="F26" s="25" t="n"/>
@@ -17393,7 +17475,7 @@
       <c r="I26" s="24" t="n"/>
       <c r="J26" s="24" t="inlineStr">
         <is>
-          <t>답을 만든 모델 이름 (예: gpt-4o-mini). 답변마다 비용과 시간을 재려고 둠. assistant 줄만 채움 (이슈 #88)</t>
+          <t>서버가 감지한 긴급, 자해 결과 { types, overdose, rule }. answer_type이 emergency, crisis인 답에만. 원문은 담지 않음 (이슈 #100, 수인 10/22)</t>
         </is>
       </c>
       <c r="K26" s="24" t="inlineStr">
@@ -17426,30 +17508,34 @@
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>prompt_tokens</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>입력 토큰 수</t>
+          <t>답변 상태</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="F27" s="25" t="n"/>
       <c r="G27" s="24" t="n"/>
       <c r="H27" s="25" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I27" s="24" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>'done'</t>
+        </is>
+      </c>
       <c r="J27" s="24" t="inlineStr">
         <is>
-          <t>답 하나에 AI를 여러 번 부르면 합친 값. assistant 줄만 채움 (이슈 #88)</t>
+          <t>generating / done. 화면을 나갔다 와도 만드는 중인 답을 알 수 있게 (이슈 #88). 사용자 줄은 늘 done. 실패(failed)는 두지 않음: 서버가 실패하면 만드는 중이던 줄을 지우고 앱이 E6을 보여 줌. 30초를 넘긴 줄은 다시 시도 때 지움 (수인 10/12 확정, 줄을 지우는 것은 10/22 #100)</t>
         </is>
       </c>
       <c r="K27" s="24" t="inlineStr">
@@ -17482,17 +17568,17 @@
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>completion_tokens</t>
+          <t>model</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>출력 토큰 수</t>
+          <t>모델 이름</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="F28" s="25" t="n"/>
@@ -17505,7 +17591,7 @@
       <c r="I28" s="24" t="n"/>
       <c r="J28" s="24" t="inlineStr">
         <is>
-          <t>출력 토큰 수 합친 값. assistant 줄만 채움 (이슈 #88)</t>
+          <t>답을 만든 모델 이름 (예: gpt-4o-mini). 답변마다 비용과 시간을 재려고 둠. assistant 줄만 채움 (이슈 #88)</t>
         </is>
       </c>
       <c r="K28" s="24" t="inlineStr">
@@ -17538,12 +17624,12 @@
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>latency_ms</t>
+          <t>prompt_tokens</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>걸린 시간(ms)</t>
+          <t>입력 토큰 수</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -17561,81 +17647,193 @@
       <c r="I29" s="24" t="n"/>
       <c r="J29" s="24" t="inlineStr">
         <is>
+          <t>답 하나에 AI를 여러 번 부르면 합친 값. assistant 줄만 채움 (이슈 #88)</t>
+        </is>
+      </c>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 / H-2 / H-3</t>
+        </is>
+      </c>
+      <c r="L29" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M29" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N29" s="24" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>chat_messages</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>대화 메시지</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>completion_tokens</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>출력 토큰 수</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F30" s="25" t="n"/>
+      <c r="G30" s="24" t="n"/>
+      <c r="H30" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="n"/>
+      <c r="J30" s="24" t="inlineStr">
+        <is>
+          <t>출력 토큰 수 합친 값. assistant 줄만 채움 (이슈 #88)</t>
+        </is>
+      </c>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 / H-2 / H-3</t>
+        </is>
+      </c>
+      <c r="L30" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M30" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N30" s="24" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>chat_messages</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>대화 메시지</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>latency_ms</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>걸린 시간(ms)</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F31" s="25" t="n"/>
+      <c r="G31" s="24" t="n"/>
+      <c r="H31" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="n"/>
+      <c r="J31" s="24" t="inlineStr">
+        <is>
           <t>질문을 받은 때부터 답을 저장할 때까지 걸린 시간, 밀리초. assistant 줄만 채움 (이슈 #88)</t>
         </is>
       </c>
-      <c r="K29" s="24" t="inlineStr">
+      <c r="K31" s="24" t="inlineStr">
         <is>
           <t>CB-01 / H-2 / H-3</t>
         </is>
       </c>
-      <c r="L29" s="25" t="inlineStr">
+      <c r="L31" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M29" s="25" t="inlineStr">
+      <c r="M31" s="25" t="inlineStr">
         <is>
           <t>v1.5</t>
         </is>
       </c>
-      <c r="N29" s="24" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="N31" s="24" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>chat_messages</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>대화 메시지</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="D30" s="15" t="inlineStr">
+      <c r="D32" s="15" t="inlineStr">
         <is>
           <t>생성 일시</t>
         </is>
       </c>
-      <c r="E30" s="15" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="F30" s="16" t="n"/>
-      <c r="G30" s="15" t="n"/>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="15" t="n"/>
+      <c r="H32" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I30" s="15" t="inlineStr">
+      <c r="I32" s="15" t="inlineStr">
         <is>
           <t>now()</t>
         </is>
       </c>
-      <c r="J30" s="15" t="n"/>
-      <c r="K30" s="15" t="inlineStr">
+      <c r="J32" s="15" t="n"/>
+      <c r="K32" s="15" t="inlineStr">
         <is>
           <t>CB-01 · H-2 · H-3</t>
         </is>
       </c>
-      <c r="L30" s="16" t="inlineStr">
+      <c r="L32" s="16" t="inlineStr">
         <is>
           <t>기존</t>
         </is>
       </c>
-      <c r="M30" s="16" t="inlineStr">
+      <c r="M32" s="16" t="inlineStr">
         <is>
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N30" s="15" t="n"/>
+      <c r="N32" s="15" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:N27"/>

--- a/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
@@ -4265,7 +4265,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E179"/>
+  <dimension ref="A1:E180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7724,6 +7724,26 @@
         </is>
       </c>
       <c r="E179" s="10" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="10" t="n"/>
+      <c r="B180" s="10" t="inlineStr">
+        <is>
+          <t>챗봇 / chat_sessions.analysis_id: 설명 변경 (이슈 #100)</t>
+        </is>
+      </c>
+      <c r="C180" s="10" t="inlineStr">
+        <is>
+          <t>null이면 일반 질문 모드 (분석 전). 분석을 지우면(R-8) 비움(set null). 대화까지 지울지는 채연과 정함 (이슈 #100, 수인 10/22)</t>
+        </is>
+      </c>
+      <c r="D180" s="10" t="inlineStr">
+        <is>
+          <t>null이면 일반 질문 모드 (분석 전). 분석을 지우면(R-8) 이 대화는 R-8 코드가 지움(그 분석의 맥락 카드가 붙은 대화도). FK는 set null (이슈 #100, #119 리뷰 10/23)
+사유: 분석을 지우면 연결된 챗봇 대화도 지움(명세서 R-8). 1단계는 하루 한 대화라 카드로 붙은 대화까지 지움 (채연 리뷰, 수인 10/23)</t>
+        </is>
+      </c>
+      <c r="E180" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -16407,7 +16427,7 @@
       <c r="I7" s="21" t="n"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t>null이면 일반 질문 모드 (분석 전). 분석을 지우면(R-8) 비움(set null). 대화까지 지울지는 채연과 정함 (이슈 #100, 수인 10/22)</t>
+          <t>null이면 일반 질문 모드 (분석 전). 분석을 지우면(R-8) 이 대화는 R-8 코드가 지움(그 분석의 맥락 카드가 붙은 대화도). FK는 set null (이슈 #100, #119 리뷰 10/23)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">

--- a/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
@@ -17439,7 +17439,7 @@
       <c r="I25" s="24" t="n"/>
       <c r="J25" s="24" t="inlineStr">
         <is>
-          <t>안전성 점검 결과 카드 { analysisId, warningIds }. 카드가 붙는 답도 answer_type은 normal. 카드가 없으면 비어 있음 (이슈 #88)</t>
+          <t>안전성 점검 결과 카드 { analysisId, warningIds }. 카드가 붙는 답도 answer_type은 normal, 상담 갈래(next_visit, soon)면 refer (#134, 10/28). 카드가 없으면 비어 있음 (이슈 #88)</t>
         </is>
       </c>
       <c r="K25" s="24" t="inlineStr">

--- a/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
@@ -8675,7 +8675,7 @@
       <c r="I14" s="21" t="inlineStr"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t>탈퇴 시 개인정보 파기 후 시각만 남김 (CM-07)</t>
+          <t>탈퇴 시 개인정보 파기 후 시각을 남김 (CM-07). 개인정보 칸은 자리 값(login_id withdrawn-{id}, birth_year 0, sex M)으로 덮어씀 (#136)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">

--- a/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
@@ -4265,7 +4265,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E180"/>
+  <dimension ref="A1:E182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7744,6 +7744,46 @@
         </is>
       </c>
       <c r="E180" s="10" t="n"/>
+    </row>
+    <row r="181" outlineLevel="1">
+      <c r="A181" s="10" t="n"/>
+      <c r="B181" s="10" t="inlineStr">
+        <is>
+          <t>챗봇 / chat_messages.route_kind: 필드 추가 (#140)</t>
+        </is>
+      </c>
+      <c r="C181" s="10" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="D181" s="10" t="inlineStr">
+        <is>
+          <t>route_kind varchar(20), N, 답 줄만. 답을 만든 갈래(Route.kind). out_of_scope면 다음 질문의 대화 기억에서 뺌
+사유: 범위 밖으로 걸러진 질문과 답이 다음 답의 노이즈가 됨(5회차 멘토링 시연, #99). 마이그레이션 17번</t>
+        </is>
+      </c>
+      <c r="E181" s="10" t="n"/>
+    </row>
+    <row r="182" outlineLevel="1">
+      <c r="A182" s="10" t="n"/>
+      <c r="B182" s="10" t="inlineStr">
+        <is>
+          <t>챗봇 / chat_messages.safety_card: 설명 변경 (#134, #140)</t>
+        </is>
+      </c>
+      <c r="C182" s="10" t="inlineStr">
+        <is>
+          <t>카드가 붙는 답도 answer_type은 normal</t>
+        </is>
+      </c>
+      <c r="D182" s="10" t="inlineStr">
+        <is>
+          <t>카드가 붙는 답도 answer_type은 normal, 상담 갈래(next_visit, soon)면 refer
+사유: 상담 갈래에서 카드가 붙은 답은 refer로 저장(#134). 칸 설명은 마이그레이션 17번에서 맞춤</t>
+        </is>
+      </c>
+      <c r="E182" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -16158,7 +16198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17528,12 +17568,12 @@
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>route_kind</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>답변 상태</t>
+          <t>답을 만든 갈래</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
@@ -17545,17 +17585,13 @@
       <c r="G27" s="24" t="n"/>
       <c r="H27" s="25" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I27" s="24" t="inlineStr">
-        <is>
-          <t>'done'</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="n"/>
       <c r="J27" s="24" t="inlineStr">
         <is>
-          <t>generating / done. 화면을 나갔다 와도 만드는 중인 답을 알 수 있게 (이슈 #88). 사용자 줄은 늘 done. 실패(failed)는 두지 않음: 서버가 실패하면 만드는 중이던 줄을 지우고 앱이 E6을 보여 줌. 30초를 넘긴 줄은 다시 시도 때 지움 (수인 10/12 확정, 줄을 지우는 것은 10/22 #100)</t>
+          <t>답 줄만. 답을 만든 갈래(Route.kind: emergency, crisis, medication, lifestyle, refer, clarify, out_of_scope). out_of_scope면 다음 질문의 대화 기억에서 뺌. H-2 응답에는 내보내지 않음 (#140, 수인 10/28)</t>
         </is>
       </c>
       <c r="K27" s="24" t="inlineStr">
@@ -17588,30 +17624,34 @@
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>모델 이름</t>
+          <t>답변 상태</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="F28" s="25" t="n"/>
       <c r="G28" s="24" t="n"/>
       <c r="H28" s="25" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I28" s="24" t="n"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>'done'</t>
+        </is>
+      </c>
       <c r="J28" s="24" t="inlineStr">
         <is>
-          <t>답을 만든 모델 이름 (예: gpt-4o-mini). 답변마다 비용과 시간을 재려고 둠. assistant 줄만 채움 (이슈 #88)</t>
+          <t>generating / done. 화면을 나갔다 와도 만드는 중인 답을 알 수 있게 (이슈 #88). 사용자 줄은 늘 done. 실패(failed)는 두지 않음: 서버가 실패하면 만드는 중이던 줄을 지우고 앱이 E6을 보여 줌. 30초를 넘긴 줄은 다시 시도 때 지움 (수인 10/12 확정, 줄을 지우는 것은 10/22 #100)</t>
         </is>
       </c>
       <c r="K28" s="24" t="inlineStr">
@@ -17644,17 +17684,17 @@
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>prompt_tokens</t>
+          <t>model</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>입력 토큰 수</t>
+          <t>모델 이름</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="F29" s="25" t="n"/>
@@ -17667,7 +17707,7 @@
       <c r="I29" s="24" t="n"/>
       <c r="J29" s="24" t="inlineStr">
         <is>
-          <t>답 하나에 AI를 여러 번 부르면 합친 값. assistant 줄만 채움 (이슈 #88)</t>
+          <t>답을 만든 모델 이름 (예: gpt-4o-mini). 답변마다 비용과 시간을 재려고 둠. assistant 줄만 채움 (이슈 #88)</t>
         </is>
       </c>
       <c r="K29" s="24" t="inlineStr">
@@ -17700,12 +17740,12 @@
       </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
-          <t>completion_tokens</t>
+          <t>prompt_tokens</t>
         </is>
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>출력 토큰 수</t>
+          <t>입력 토큰 수</t>
         </is>
       </c>
       <c r="E30" s="24" t="inlineStr">
@@ -17723,7 +17763,7 @@
       <c r="I30" s="24" t="n"/>
       <c r="J30" s="24" t="inlineStr">
         <is>
-          <t>출력 토큰 수 합친 값. assistant 줄만 채움 (이슈 #88)</t>
+          <t>답 하나에 AI를 여러 번 부르면 합친 값. assistant 줄만 채움 (이슈 #88)</t>
         </is>
       </c>
       <c r="K30" s="24" t="inlineStr">
@@ -17756,12 +17796,12 @@
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>latency_ms</t>
+          <t>completion_tokens</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>걸린 시간(ms)</t>
+          <t>출력 토큰 수</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
@@ -17779,81 +17819,137 @@
       <c r="I31" s="24" t="n"/>
       <c r="J31" s="24" t="inlineStr">
         <is>
+          <t>출력 토큰 수 합친 값. assistant 줄만 채움 (이슈 #88)</t>
+        </is>
+      </c>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>CB-01 / H-2 / H-3</t>
+        </is>
+      </c>
+      <c r="L31" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M31" s="25" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="N31" s="24" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>chat_messages</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>대화 메시지</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>latency_ms</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>걸린 시간(ms)</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F32" s="25" t="n"/>
+      <c r="G32" s="24" t="n"/>
+      <c r="H32" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="n"/>
+      <c r="J32" s="24" t="inlineStr">
+        <is>
           <t>질문을 받은 때부터 답을 저장할 때까지 걸린 시간, 밀리초. assistant 줄만 채움 (이슈 #88)</t>
         </is>
       </c>
-      <c r="K31" s="24" t="inlineStr">
+      <c r="K32" s="24" t="inlineStr">
         <is>
           <t>CB-01 / H-2 / H-3</t>
         </is>
       </c>
-      <c r="L31" s="25" t="inlineStr">
+      <c r="L32" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M31" s="25" t="inlineStr">
+      <c r="M32" s="25" t="inlineStr">
         <is>
           <t>v1.5</t>
         </is>
       </c>
-      <c r="N31" s="24" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="N32" s="24" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>chat_messages</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>대화 메시지</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="D33" s="15" t="inlineStr">
         <is>
           <t>생성 일시</t>
         </is>
       </c>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="E33" s="15" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="F32" s="16" t="n"/>
-      <c r="G32" s="15" t="n"/>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="F33" s="16" t="n"/>
+      <c r="G33" s="15" t="n"/>
+      <c r="H33" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I32" s="15" t="inlineStr">
+      <c r="I33" s="15" t="inlineStr">
         <is>
           <t>now()</t>
         </is>
       </c>
-      <c r="J32" s="15" t="n"/>
-      <c r="K32" s="15" t="inlineStr">
+      <c r="J33" s="15" t="n"/>
+      <c r="K33" s="15" t="inlineStr">
         <is>
           <t>CB-01 · H-2 · H-3</t>
         </is>
       </c>
-      <c r="L32" s="16" t="inlineStr">
+      <c r="L33" s="16" t="inlineStr">
         <is>
           <t>기존</t>
         </is>
       </c>
-      <c r="M32" s="16" t="inlineStr">
+      <c r="M33" s="16" t="inlineStr">
         <is>
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N32" s="15" t="n"/>
+      <c r="N33" s="15" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:N27"/>

--- a/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'입력'!$A$4:$N$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'분석'!$A$4:$N$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'챗봇'!$A$4:$N$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'실천·보상'!$A$4:$N$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'실천·보상'!$A$4:$N$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'마스터'!$A$4:$N$106</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'FHIR 대응'!$A$5:$H$90</definedName>
   </definedNames>
@@ -4265,7 +4265,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E182"/>
+  <dimension ref="A1:E185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7784,6 +7784,66 @@
         </is>
       </c>
       <c r="E182" s="10" t="n"/>
+    </row>
+    <row r="183" outlineLevel="1">
+      <c r="A183" s="10" t="n"/>
+      <c r="B183" s="10" t="inlineStr">
+        <is>
+          <t>실천·보상 / recommendations: 필드 바꿈 (10/30, 마이그레이션 18번)</t>
+        </is>
+      </c>
+      <c r="C183" s="10" t="inlineStr">
+        <is>
+          <t>guide_id, medication_link_id, action_id (FK, 팩트 표를 가리킴). reason_label, goal_type, rank는 N</t>
+        </is>
+      </c>
+      <c r="D183" s="10" t="inlineStr">
+        <is>
+          <t>guide_id, medication_link_id, action_id를 빼고 challenge_key varchar(20) Y, desc varchar(200) N, caution_label varchar(20) N, fact_refs jsonb Y, created_at timestamp N 추가. unique (analysis_id, challenge_key). reason_label, goal_type, rank는 Y, analysis_id는 ON DELETE CASCADE
+사유: 팩트표가 코드의 JSON 파일이라 가리킬 표가 없음. 9/23에 정한 세 가지 챌린지를 팩트표 근거가 있을 때만 추천 (10/30 수인)</t>
+        </is>
+      </c>
+      <c r="E183" s="10" t="n"/>
+    </row>
+    <row r="184" outlineLevel="1">
+      <c r="A184" s="10" t="n"/>
+      <c r="B184" s="10" t="inlineStr">
+        <is>
+          <t>실천·보상 / habit_goals.end_date: 설명 변경</t>
+        </is>
+      </c>
+      <c r="C184" s="10" t="inlineStr">
+        <is>
+          <t>주 단위 (REQ-116 재선택 흐름 🟡)</t>
+        </is>
+      </c>
+      <c r="D184" s="10" t="inlineStr">
+        <is>
+          <t>끝낸 날 (뺀 목표, 동의 철회). 주 단위 다시 고르기 REQ-116은 뒤로
+사유: 다시 고르면 같은 목표는 유지하고 뺀 것만 끝냄 (#43 목표 교체, 10/30 수인)</t>
+        </is>
+      </c>
+      <c r="E184" s="10" t="n"/>
+    </row>
+    <row r="185" outlineLevel="1">
+      <c r="A185" s="10" t="n"/>
+      <c r="B185" s="10" t="inlineStr">
+        <is>
+          <t>실천·보상 / habit_records.value: 설명 변경</t>
+        </is>
+      </c>
+      <c r="C185" s="10" t="inlineStr">
+        <is>
+          <t>수량형 누적값</t>
+        </is>
+      </c>
+      <c r="D185" s="10" t="inlineStr">
+        <is>
+          <t>수량형 그날 총량 (P-4에서 앱이 총량을 보내 다시 보내도 두 번 더해지지 않음)
+사유: 저장 실패 뒤 같은 요청을 다시 보내도 값이 두 번 더해지지 않게 (REQ-115, 10/30 수인)</t>
+        </is>
+      </c>
+      <c r="E185" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -17974,7 +18034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18110,14 +18170,14 @@
           <t>PK</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr"/>
+      <c r="G5" s="24" t="n"/>
       <c r="H5" s="25" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I5" s="24" t="inlineStr"/>
-      <c r="J5" s="24" t="inlineStr"/>
+      <c r="I5" s="24" t="n"/>
+      <c r="J5" s="24" t="n"/>
       <c r="K5" s="24" t="inlineStr">
         <is>
           <t>RW-01 · RG-05 · P-1</t>
@@ -18180,8 +18240,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr"/>
-      <c r="J6" s="24" t="inlineStr"/>
+      <c r="I6" s="24" t="n"/>
+      <c r="J6" s="24" t="inlineStr">
+        <is>
+          <t>분석을 지우면 같이 지움 (ON DELETE CASCADE)</t>
+        </is>
+      </c>
       <c r="K6" s="24" t="inlineStr">
         <is>
           <t>RW-01 · RG-05 · P-1</t>
@@ -18189,15 +18253,15 @@
       </c>
       <c r="L6" s="25" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="M6" s="25" t="inlineStr">
         <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N6" s="24" t="inlineStr"/>
+          <t>v1.5 초안</t>
+        </is>
+      </c>
+      <c r="N6" s="24" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="23" t="inlineStr">
@@ -18212,38 +18276,30 @@
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>guide_id</t>
+          <t>challenge_key</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>생활습관 팩트 ID</t>
+          <t>챌린지 키</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F7" s="25" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G7" s="24" t="inlineStr">
-        <is>
-          <t>lifestyle_guides.id</t>
-        </is>
-      </c>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="n"/>
+      <c r="G7" s="24" t="n"/>
       <c r="H7" s="25" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I7" s="24" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="n"/>
       <c r="J7" s="24" t="inlineStr">
         <is>
-          <t>질환 기준 추천일 때</t>
+          <t>soup / walk / alcohol (9/23에 정한 세 가지)</t>
         </is>
       </c>
       <c r="K7" s="24" t="inlineStr">
@@ -18258,10 +18314,10 @@
       </c>
       <c r="M7" s="25" t="inlineStr">
         <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N7" s="24" t="inlineStr"/>
+          <t>v1.5 초안</t>
+        </is>
+      </c>
+      <c r="N7" s="24" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
@@ -18276,38 +18332,30 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>medication_link_id</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>약-생활수칙 연결 ID</t>
+          <t>제목</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F8" s="25" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G8" s="24" t="inlineStr">
-        <is>
-          <t>lifestyle_medication_links.id</t>
-        </is>
-      </c>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="F8" s="25" t="n"/>
+      <c r="G8" s="24" t="n"/>
       <c r="H8" s="25" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I8" s="24" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="n"/>
       <c r="J8" s="24" t="inlineStr">
         <is>
-          <t>약 기준 추천일 때</t>
+          <t>국물 남기기 등</t>
         </is>
       </c>
       <c r="K8" s="24" t="inlineStr">
@@ -18325,7 +18373,7 @@
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N8" s="24" t="inlineStr"/>
+      <c r="N8" s="24" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="23" t="inlineStr">
@@ -18340,38 +18388,30 @@
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>action_id</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>실천 항목 ID</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F9" s="25" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G9" s="24" t="inlineStr">
-        <is>
-          <t>lifestyle_guide_actions.id</t>
-        </is>
-      </c>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="n"/>
+      <c r="G9" s="24" t="n"/>
       <c r="H9" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I9" s="24" t="inlineStr"/>
+      <c r="I9" s="24" t="n"/>
       <c r="J9" s="24" t="inlineStr">
         <is>
-          <t>어떤 실천 항목(출처 포함)에서 나온 추천인지</t>
+          <t>팩트표 글 그대로 (예: 1일 나트륨 2,000mg 이하)</t>
         </is>
       </c>
       <c r="K9" s="24" t="inlineStr">
@@ -18386,10 +18426,10 @@
       </c>
       <c r="M9" s="25" t="inlineStr">
         <is>
-          <t>v1.2</t>
-        </is>
-      </c>
-      <c r="N9" s="24" t="inlineStr"/>
+          <t>v1.5 초안</t>
+        </is>
+      </c>
+      <c r="N9" s="24" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
@@ -18404,30 +18444,30 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>reason_label</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>제목</t>
+          <t>추천 이유 라벨</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>varchar(100)</t>
-        </is>
-      </c>
-      <c r="F10" s="25" t="inlineStr"/>
-      <c r="G10" s="24" t="inlineStr"/>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="n"/>
+      <c r="G10" s="24" t="n"/>
       <c r="H10" s="25" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I10" s="24" t="inlineStr"/>
+      <c r="I10" s="24" t="n"/>
       <c r="J10" s="24" t="inlineStr">
         <is>
-          <t>국물 남기기 등</t>
+          <t>고혈압 / 약과 함께 등 (화면 라벨)</t>
         </is>
       </c>
       <c r="K10" s="24" t="inlineStr">
@@ -18437,15 +18477,15 @@
       </c>
       <c r="L10" s="25" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="M10" s="25" t="inlineStr">
         <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N10" s="24" t="inlineStr"/>
+          <t>v1.5 초안</t>
+        </is>
+      </c>
+      <c r="N10" s="24" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
@@ -18460,30 +18500,30 @@
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>reason_label</t>
+          <t>caution_label</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>추천 이유 라벨</t>
+          <t>주의 라벨</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
-        </is>
-      </c>
-      <c r="F11" s="25" t="inlineStr"/>
-      <c r="G11" s="24" t="inlineStr"/>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="F11" s="25" t="n"/>
+      <c r="G11" s="24" t="n"/>
       <c r="H11" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I11" s="24" t="inlineStr"/>
+      <c r="I11" s="24" t="n"/>
       <c r="J11" s="24" t="inlineStr">
         <is>
-          <t>고혈압 / 약과 함께 등 (화면 라벨)</t>
+          <t>의료진이 정한 강도로 (허혈성심질환 걷기)</t>
         </is>
       </c>
       <c r="K11" s="24" t="inlineStr">
@@ -18498,10 +18538,10 @@
       </c>
       <c r="M11" s="25" t="inlineStr">
         <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N11" s="24" t="inlineStr"/>
+          <t>v1.5 초안</t>
+        </is>
+      </c>
+      <c r="N11" s="24" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="23" t="inlineStr">
@@ -18529,14 +18569,14 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="F12" s="25" t="inlineStr"/>
-      <c r="G12" s="24" t="inlineStr"/>
+      <c r="F12" s="25" t="n"/>
+      <c r="G12" s="24" t="n"/>
       <c r="H12" s="25" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I12" s="24" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="n"/>
       <c r="J12" s="24" t="inlineStr">
         <is>
           <t>check / quantity</t>
@@ -18549,15 +18589,15 @@
       </c>
       <c r="L12" s="25" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="M12" s="25" t="inlineStr">
         <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N12" s="24" t="inlineStr"/>
+          <t>v1.5 초안</t>
+        </is>
+      </c>
+      <c r="N12" s="24" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="23" t="inlineStr">
@@ -18585,14 +18625,14 @@
           <t>decimal(10,2)</t>
         </is>
       </c>
-      <c r="F13" s="25" t="inlineStr"/>
-      <c r="G13" s="24" t="inlineStr"/>
+      <c r="F13" s="25" t="n"/>
+      <c r="G13" s="24" t="n"/>
       <c r="H13" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I13" s="24" t="inlineStr"/>
+      <c r="I13" s="24" t="n"/>
       <c r="J13" s="24" t="inlineStr">
         <is>
           <t>수량형 목표 (예: 30)</t>
@@ -18613,7 +18653,7 @@
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N13" s="24" t="inlineStr"/>
+      <c r="N13" s="24" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
@@ -18641,14 +18681,14 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="F14" s="25" t="inlineStr"/>
-      <c r="G14" s="24" t="inlineStr"/>
+      <c r="F14" s="25" t="n"/>
+      <c r="G14" s="24" t="n"/>
       <c r="H14" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I14" s="24" t="inlineStr"/>
+      <c r="I14" s="24" t="n"/>
       <c r="J14" s="24" t="inlineStr">
         <is>
           <t>분 등</t>
@@ -18669,7 +18709,7 @@
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N14" s="24" t="inlineStr"/>
+      <c r="N14" s="24" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="23" t="inlineStr">
@@ -18684,28 +18724,32 @@
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>rank</t>
+          <t>fact_refs</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>순위</t>
+          <t>팩트표 근거</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>smallint</t>
-        </is>
-      </c>
-      <c r="F15" s="25" t="inlineStr"/>
-      <c r="G15" s="24" t="inlineStr"/>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="n"/>
+      <c r="G15" s="24" t="n"/>
       <c r="H15" s="25" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I15" s="24" t="inlineStr"/>
-      <c r="J15" s="24" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="n"/>
+      <c r="J15" s="24" t="inlineStr">
+        <is>
+          <t>팩트표 근거 "질환 id:항목 이름" 목록. guide_id, medication_link_id, action_id 대신 (팩트표가 JSON 파일)</t>
+        </is>
+      </c>
       <c r="K15" s="24" t="inlineStr">
         <is>
           <t>RW-01 · RG-05 · P-1</t>
@@ -18718,117 +18762,105 @@
       </c>
       <c r="M15" s="25" t="inlineStr">
         <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N15" s="24" t="inlineStr"/>
+          <t>v1.5 초안</t>
+        </is>
+      </c>
+      <c r="N15" s="24" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="23" t="inlineStr">
         <is>
-          <t>habit_goals</t>
+          <t>recommendations</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>실천 목표</t>
+          <t>생활습관 추천</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>rank</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>순위</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F16" s="25" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr"/>
+          <t>smallint</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="n"/>
+      <c r="G16" s="24" t="n"/>
       <c r="H16" s="25" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I16" s="24" t="inlineStr"/>
-      <c r="J16" s="24" t="inlineStr"/>
+      <c r="I16" s="24" t="n"/>
+      <c r="J16" s="24" t="n"/>
       <c r="K16" s="24" t="inlineStr">
         <is>
-          <t>RW-02 · P-2 · P-3</t>
+          <t>RW-01 · RG-05 · P-1</t>
         </is>
       </c>
       <c r="L16" s="25" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="M16" s="25" t="inlineStr">
         <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N16" s="24" t="inlineStr">
-        <is>
-          <t>최대 3개 활성 (REQ-111)</t>
-        </is>
-      </c>
+          <t>v1.5 초안</t>
+        </is>
+      </c>
+      <c r="N16" s="24" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="23" t="inlineStr">
         <is>
-          <t>habit_goals</t>
+          <t>recommendations</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>실천 목표</t>
+          <t>생활습관 추천</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>사용자 ID</t>
+          <t>생성 일시</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F17" s="25" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G17" s="24" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F17" s="25" t="n"/>
+      <c r="G17" s="24" t="n"/>
       <c r="H17" s="25" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I17" s="24" t="inlineStr"/>
-      <c r="J17" s="24" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="J17" s="24" t="n"/>
       <c r="K17" s="24" t="inlineStr">
         <is>
-          <t>RW-02 · P-2 · P-3</t>
+          <t>RW-01 · RG-05 · P-1</t>
         </is>
       </c>
       <c r="L17" s="25" t="inlineStr">
@@ -18838,10 +18870,14 @@
       </c>
       <c r="M17" s="25" t="inlineStr">
         <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N17" s="24" t="inlineStr"/>
+          <t>v1.5 초안</t>
+        </is>
+      </c>
+      <c r="N17" s="24" t="inlineStr">
+        <is>
+          <t>인덱스: (analysis_id, challenge_key) [unique]</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="23" t="inlineStr">
@@ -18856,12 +18892,12 @@
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>recommendation_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>추천 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -18871,25 +18907,17 @@
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G18" s="24" t="inlineStr">
-        <is>
-          <t>recommendations.id</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr"/>
       <c r="H18" s="25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I18" s="24" t="inlineStr"/>
-      <c r="J18" s="24" t="inlineStr">
-        <is>
-          <t>추천(분석)이 지워지면 비움 (ON DELETE SET NULL) — 목표 · 기록 · 포인트는 남김 (기록 삭제 · 동의 철회)</t>
-        </is>
-      </c>
+      <c r="J18" s="24" t="inlineStr"/>
       <c r="K18" s="24" t="inlineStr">
         <is>
           <t>RW-02 · P-2 · P-3</t>
@@ -18902,10 +18930,14 @@
       </c>
       <c r="M18" s="25" t="inlineStr">
         <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N18" s="24" t="inlineStr"/>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="N18" s="24" t="inlineStr">
+        <is>
+          <t>최대 3개 활성 (REQ-111)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
@@ -18920,21 +18952,29 @@
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>제목</t>
+          <t>사용자 ID</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>varchar(100)</t>
-        </is>
-      </c>
-      <c r="F19" s="25" t="inlineStr"/>
-      <c r="G19" s="24" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F19" s="25" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
       <c r="H19" s="25" t="inlineStr">
         <is>
           <t>Y</t>
@@ -18972,30 +19012,38 @@
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>goal_type</t>
+          <t>recommendation_id</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>목표 유형</t>
+          <t>추천 ID</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="F20" s="25" t="inlineStr"/>
-      <c r="G20" s="24" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F20" s="25" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>recommendations.id</t>
+        </is>
+      </c>
       <c r="H20" s="25" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I20" s="24" t="inlineStr"/>
       <c r="J20" s="24" t="inlineStr">
         <is>
-          <t>check / quantity</t>
+          <t>추천(분석)이 지워지면 비움 (ON DELETE SET NULL) — 목표 · 기록 · 포인트는 남김 (기록 삭제 · 동의 철회)</t>
         </is>
       </c>
       <c r="K20" s="24" t="inlineStr">
@@ -19010,7 +19058,7 @@
       </c>
       <c r="M20" s="25" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.3</t>
         </is>
       </c>
       <c r="N20" s="24" t="inlineStr"/>
@@ -19028,24 +19076,24 @@
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>target_value</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>목표 수치</t>
+          <t>제목</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>decimal(10,2)</t>
+          <t>varchar(100)</t>
         </is>
       </c>
       <c r="F21" s="25" t="inlineStr"/>
       <c r="G21" s="24" t="inlineStr"/>
       <c r="H21" s="25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I21" s="24" t="inlineStr"/>
@@ -19080,12 +19128,12 @@
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>goal_type</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>목표 유형</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -19097,11 +19145,15 @@
       <c r="G22" s="24" t="inlineStr"/>
       <c r="H22" s="25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I22" s="24" t="inlineStr"/>
-      <c r="J22" s="24" t="inlineStr"/>
+      <c r="J22" s="24" t="inlineStr">
+        <is>
+          <t>check / quantity</t>
+        </is>
+      </c>
       <c r="K22" s="24" t="inlineStr">
         <is>
           <t>RW-02 · P-2 · P-3</t>
@@ -19132,24 +19184,24 @@
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>target_value</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>시작일</t>
+          <t>목표 수치</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>decimal(10,2)</t>
         </is>
       </c>
       <c r="F23" s="25" t="inlineStr"/>
       <c r="G23" s="24" t="inlineStr"/>
       <c r="H23" s="25" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I23" s="24" t="inlineStr"/>
@@ -19184,17 +19236,17 @@
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>종료일</t>
+          <t>단위</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="F24" s="25" t="inlineStr"/>
@@ -19205,11 +19257,7 @@
         </is>
       </c>
       <c r="I24" s="24" t="inlineStr"/>
-      <c r="J24" s="24" t="inlineStr">
-        <is>
-          <t>주 단위 (REQ-116 재선택 흐름 🟡)</t>
-        </is>
-      </c>
+      <c r="J24" s="24" t="inlineStr"/>
       <c r="K24" s="24" t="inlineStr">
         <is>
           <t>RW-02 · P-2 · P-3</t>
@@ -19240,32 +19288,28 @@
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>start_date</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>시작일</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>date</t>
         </is>
       </c>
       <c r="F25" s="25" t="inlineStr"/>
       <c r="G25" s="24" t="inlineStr"/>
       <c r="H25" s="25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I25" s="24" t="inlineStr"/>
-      <c r="J25" s="24" t="inlineStr">
-        <is>
-          <t>active / ended</t>
-        </is>
-      </c>
+      <c r="J25" s="24" t="inlineStr"/>
       <c r="K25" s="24" t="inlineStr">
         <is>
           <t>RW-02 · P-2 · P-3</t>
@@ -19296,17 +19340,17 @@
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>end_date</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>종료일</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>date</t>
         </is>
       </c>
       <c r="F26" s="25" t="inlineStr"/>
@@ -19316,12 +19360,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I26" s="24" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="J26" s="24" t="inlineStr"/>
+      <c r="I26" s="24" t="inlineStr"/>
+      <c r="J26" s="24" t="inlineStr">
+        <is>
+          <t>끝낸 날 (뺀 목표, 동의 철회). 주 단위 다시 고르기 REQ-116은 뒤로</t>
+        </is>
+      </c>
       <c r="K26" s="24" t="inlineStr">
         <is>
           <t>RW-02 · P-2 · P-3</t>
@@ -19329,12 +19373,12 @@
       </c>
       <c r="L26" s="25" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="M26" s="25" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.5 초안</t>
         </is>
       </c>
       <c r="N26" s="24" t="inlineStr"/>
@@ -19342,45 +19386,45 @@
     <row r="27">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>habit_records</t>
+          <t>habit_goals</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>실천 기록</t>
+          <t>실천 목표</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F27" s="25" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="F27" s="25" t="inlineStr"/>
       <c r="G27" s="24" t="inlineStr"/>
       <c r="H27" s="25" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I27" s="24" t="inlineStr"/>
-      <c r="J27" s="24" t="inlineStr"/>
+      <c r="J27" s="24" t="inlineStr">
+        <is>
+          <t>active / ended</t>
+        </is>
+      </c>
       <c r="K27" s="24" t="inlineStr">
         <is>
-          <t>RW-03 · RW-04 · P-4 · P-5</t>
+          <t>RW-02 · P-2 · P-3</t>
         </is>
       </c>
       <c r="L27" s="25" t="inlineStr">
@@ -19398,49 +19442,45 @@
     <row r="28">
       <c r="A28" s="23" t="inlineStr">
         <is>
-          <t>habit_records</t>
+          <t>habit_goals</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>실천 기록</t>
+          <t>실천 목표</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>goal_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>목표 ID</t>
+          <t>생성 일시</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F28" s="25" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G28" s="24" t="inlineStr">
-        <is>
-          <t>habit_goals.id</t>
-        </is>
-      </c>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F28" s="25" t="inlineStr"/>
+      <c r="G28" s="24" t="inlineStr"/>
       <c r="H28" s="25" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I28" s="24" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="J28" s="24" t="inlineStr"/>
       <c r="K28" s="24" t="inlineStr">
         <is>
-          <t>RW-03 · RW-04 · P-4 · P-5</t>
+          <t>RW-02 · P-2 · P-3</t>
         </is>
       </c>
       <c r="L28" s="25" t="inlineStr">
@@ -19468,20 +19508,24 @@
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>record_date</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>기록일</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="F29" s="25" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F29" s="25" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G29" s="24" t="inlineStr"/>
       <c r="H29" s="25" t="inlineStr">
         <is>
@@ -19520,32 +19564,36 @@
       </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>goal_id</t>
         </is>
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>기록 수치</t>
+          <t>목표 ID</t>
         </is>
       </c>
       <c r="E30" s="24" t="inlineStr">
         <is>
-          <t>decimal(10,2)</t>
-        </is>
-      </c>
-      <c r="F30" s="25" t="inlineStr"/>
-      <c r="G30" s="24" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F30" s="25" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>habit_goals.id</t>
+        </is>
+      </c>
       <c r="H30" s="25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I30" s="24" t="inlineStr"/>
-      <c r="J30" s="24" t="inlineStr">
-        <is>
-          <t>수량형 누적값</t>
-        </is>
-      </c>
+      <c r="J30" s="24" t="inlineStr"/>
       <c r="K30" s="24" t="inlineStr">
         <is>
           <t>RW-03 · RW-04 · P-4 · P-5</t>
@@ -19576,17 +19624,17 @@
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>record_date</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>완료 여부</t>
+          <t>기록일</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>date</t>
         </is>
       </c>
       <c r="F31" s="25" t="inlineStr"/>
@@ -19596,11 +19644,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I31" s="24" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="I31" s="24" t="inlineStr"/>
       <c r="J31" s="24" t="inlineStr"/>
       <c r="K31" s="24" t="inlineStr">
         <is>
@@ -19632,17 +19676,17 @@
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>value</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>기록 수치</t>
         </is>
       </c>
       <c r="E32" s="24" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>decimal(10,2)</t>
         </is>
       </c>
       <c r="F32" s="25" t="inlineStr"/>
@@ -19652,12 +19696,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I32" s="24" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="J32" s="24" t="inlineStr"/>
+      <c r="I32" s="24" t="inlineStr"/>
+      <c r="J32" s="24" t="inlineStr">
+        <is>
+          <t>수량형 그날 총량 (P-4에서 앱이 총량을 보내 다시 보내도 두 번 더해지지 않음)</t>
+        </is>
+      </c>
       <c r="K32" s="24" t="inlineStr">
         <is>
           <t>RW-03 · RW-04 · P-4 · P-5</t>
@@ -19665,62 +19709,58 @@
       </c>
       <c r="L32" s="25" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="M32" s="25" t="inlineStr">
         <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N32" s="24" t="inlineStr">
-        <is>
-          <t>인덱스: (goal_id, record_date) [unique, note: '같은 날 중복 완료 방지']</t>
-        </is>
-      </c>
+          <t>v1.5 초안</t>
+        </is>
+      </c>
+      <c r="N32" s="24" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="23" t="inlineStr">
         <is>
-          <t>rewards</t>
+          <t>habit_records</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>포인트</t>
+          <t>실천 기록</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>완료 여부</t>
         </is>
       </c>
       <c r="E33" s="24" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F33" s="25" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="F33" s="25" t="inlineStr"/>
       <c r="G33" s="24" t="inlineStr"/>
       <c r="H33" s="25" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I33" s="24" t="inlineStr"/>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="J33" s="24" t="inlineStr"/>
       <c r="K33" s="24" t="inlineStr">
         <is>
-          <t>RW-05 · RW-06 · P-6</t>
+          <t>RW-03 · RW-04 · P-4 · P-5</t>
         </is>
       </c>
       <c r="L33" s="25" t="inlineStr">
@@ -19738,49 +19778,45 @@
     <row r="34">
       <c r="A34" s="23" t="inlineStr">
         <is>
-          <t>rewards</t>
+          <t>habit_records</t>
         </is>
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>포인트</t>
+          <t>실천 기록</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>사용자 ID</t>
+          <t>생성 일시</t>
         </is>
       </c>
       <c r="E34" s="24" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F34" s="25" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G34" s="24" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F34" s="25" t="inlineStr"/>
+      <c r="G34" s="24" t="inlineStr"/>
       <c r="H34" s="25" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I34" s="24" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="J34" s="24" t="inlineStr"/>
       <c r="K34" s="24" t="inlineStr">
         <is>
-          <t>RW-05 · RW-06 · P-6</t>
+          <t>RW-03 · RW-04 · P-4 · P-5</t>
         </is>
       </c>
       <c r="L34" s="25" t="inlineStr">
@@ -19793,7 +19829,11 @@
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N34" s="24" t="inlineStr"/>
+      <c r="N34" s="24" t="inlineStr">
+        <is>
+          <t>인덱스: (goal_id, record_date) [unique, note: '같은 날 중복 완료 방지']</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="23" t="inlineStr">
@@ -19808,12 +19848,12 @@
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>record_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>실천 기록 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E35" s="24" t="inlineStr">
@@ -19823,25 +19863,17 @@
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G35" s="24" t="inlineStr">
-        <is>
-          <t>habit_records.id</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr"/>
       <c r="H35" s="25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I35" s="24" t="inlineStr"/>
-      <c r="J35" s="24" t="inlineStr">
-        <is>
-          <t>목표 완료 보상일 때 (all_done은 비움)</t>
-        </is>
-      </c>
+      <c r="J35" s="24" t="inlineStr"/>
       <c r="K35" s="24" t="inlineStr">
         <is>
           <t>RW-05 · RW-06 · P-6</t>
@@ -19854,7 +19886,7 @@
       </c>
       <c r="M35" s="25" t="inlineStr">
         <is>
-          <t>v1.3</t>
+          <t>v1.0</t>
         </is>
       </c>
       <c r="N35" s="24" t="inlineStr"/>
@@ -19872,32 +19904,36 @@
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>reward_type</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>보상 종류</t>
+          <t>사용자 ID</t>
         </is>
       </c>
       <c r="E36" s="24" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="F36" s="25" t="inlineStr"/>
-      <c r="G36" s="24" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F36" s="25" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
       <c r="H36" s="25" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
       <c r="I36" s="24" t="inlineStr"/>
-      <c r="J36" s="24" t="inlineStr">
-        <is>
-          <t>goal_done / all_done(하루 전체 완료 보너스)</t>
-        </is>
-      </c>
+      <c r="J36" s="24" t="inlineStr"/>
       <c r="K36" s="24" t="inlineStr">
         <is>
           <t>RW-05 · RW-06 · P-6</t>
@@ -19928,28 +19964,40 @@
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>record_id</t>
         </is>
       </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
-          <t>포인트</t>
+          <t>실천 기록 ID</t>
         </is>
       </c>
       <c r="E37" s="24" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F37" s="25" t="inlineStr"/>
-      <c r="G37" s="24" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F37" s="25" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>habit_records.id</t>
+        </is>
+      </c>
       <c r="H37" s="25" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I37" s="24" t="inlineStr"/>
-      <c r="J37" s="24" t="inlineStr"/>
+      <c r="J37" s="24" t="inlineStr">
+        <is>
+          <t>목표 완료 보상일 때 (all_done은 비움)</t>
+        </is>
+      </c>
       <c r="K37" s="24" t="inlineStr">
         <is>
           <t>RW-05 · RW-06 · P-6</t>
@@ -19962,7 +20010,7 @@
       </c>
       <c r="M37" s="25" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.3</t>
         </is>
       </c>
       <c r="N37" s="24" t="inlineStr"/>
@@ -19980,17 +20028,17 @@
       </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
-          <t>reward_date</t>
+          <t>reward_type</t>
         </is>
       </c>
       <c r="D38" s="24" t="inlineStr">
         <is>
-          <t>지급일</t>
+          <t>보상 종류</t>
         </is>
       </c>
       <c r="E38" s="24" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="F38" s="25" t="inlineStr"/>
@@ -20001,7 +20049,11 @@
         </is>
       </c>
       <c r="I38" s="24" t="inlineStr"/>
-      <c r="J38" s="24" t="inlineStr"/>
+      <c r="J38" s="24" t="inlineStr">
+        <is>
+          <t>goal_done / all_done(하루 전체 완료 보너스)</t>
+        </is>
+      </c>
       <c r="K38" s="24" t="inlineStr">
         <is>
           <t>RW-05 · RW-06 · P-6</t>
@@ -20032,31 +20084,27 @@
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>points</t>
         </is>
       </c>
       <c r="D39" s="24" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>포인트</t>
         </is>
       </c>
       <c r="E39" s="24" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F39" s="25" t="inlineStr"/>
       <c r="G39" s="24" t="inlineStr"/>
       <c r="H39" s="25" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I39" s="24" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I39" s="24" t="inlineStr"/>
       <c r="J39" s="24" t="inlineStr"/>
       <c r="K39" s="24" t="inlineStr">
         <is>
@@ -20073,14 +20121,122 @@
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N39" s="24" t="inlineStr">
+      <c r="N39" s="24" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>rewards</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>reward_date</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>지급일</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F40" s="25" t="inlineStr"/>
+      <c r="G40" s="24" t="inlineStr"/>
+      <c r="H40" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I40" s="24" t="inlineStr"/>
+      <c r="J40" s="24" t="inlineStr"/>
+      <c r="K40" s="24" t="inlineStr">
+        <is>
+          <t>RW-05 · RW-06 · P-6</t>
+        </is>
+      </c>
+      <c r="L40" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M40" s="25" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="N40" s="24" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="23" t="inlineStr">
+        <is>
+          <t>rewards</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>생성 일시</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F41" s="25" t="inlineStr"/>
+      <c r="G41" s="24" t="inlineStr"/>
+      <c r="H41" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I41" s="24" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="J41" s="24" t="inlineStr"/>
+      <c r="K41" s="24" t="inlineStr">
+        <is>
+          <t>RW-05 · RW-06 · P-6</t>
+        </is>
+      </c>
+      <c r="L41" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M41" s="25" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="N41" s="24" t="inlineStr">
         <is>
           <t>인덱스: (user_id, reward_date, reward_type, record_id) [unique, NULLS NOT DISTINCT] — 중복 지급 방지 (REQ-113). record_id가 빈 all_done도 하루 1번만 (PostgreSQL 15+, Tortoise로 안 만들어져 마이그레이션에 SQL 직접)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N39"/>
+  <autoFilter ref="A4:N41"/>
   <dataValidations count="3">
     <dataValidation sqref="H5:H300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>

--- a/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.5_초안.xlsx
@@ -4265,7 +4265,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E185"/>
+  <dimension ref="A1:E187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7844,6 +7844,46 @@
         </is>
       </c>
       <c r="E185" s="10" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="10" t="n"/>
+      <c r="B186" s="10" t="inlineStr">
+        <is>
+          <t>실천·보상 / habit_goals.status: 필수와 기본값 변경</t>
+        </is>
+      </c>
+      <c r="C186" s="10" t="inlineStr">
+        <is>
+          <t>필수 N, 기본값 없음</t>
+        </is>
+      </c>
+      <c r="D186" s="10" t="inlineStr">
+        <is>
+          <t>필수 Y, 기본값 active
+사유: 서버 마이그레이션 18번(NOT NULL DEFAULT 'active')과 맞춤 (10/31 채연)</t>
+        </is>
+      </c>
+      <c r="E186" s="10" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="10" t="n"/>
+      <c r="B187" s="10" t="inlineStr">
+        <is>
+          <t>실천·보상 / 탭 설명 (2행)과 요약 / 실천·보상 담당 · 범위</t>
+        </is>
+      </c>
+      <c r="C187" s="10" t="inlineStr">
+        <is>
+          <t>성규 · 추천 · 목표 · 기록 · 포인트</t>
+        </is>
+      </c>
+      <c r="D187" s="10" t="inlineStr">
+        <is>
+          <t>서버 수인(#155) 이어서 채연 · 화면 채연 · 추천 · 목표 · 기록 · 포인트
+사유: 성규님 조기 수료(10/6)와 10/30 회의 결정, #155 머지(10/31) 반영</t>
+        </is>
+      </c>
+      <c r="E187" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -8043,7 +8083,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>성규 · 추천 · 목표 · 기록 · 포인트</t>
+          <t>서버 수인(#155) 이어서 채연 · 화면 채연 · 추천 · 목표 · 기록 · 포인트</t>
         </is>
       </c>
       <c r="C9" s="16">
@@ -18063,7 +18103,7 @@
     <row r="2">
       <c r="A2" s="42" t="inlineStr">
         <is>
-          <t>성규 · 추천 · 목표 · 기록 · 포인트</t>
+          <t>서버 수인(#155) 이어서 채연 · 화면 채연 · 추천 · 목표 · 기록 · 포인트</t>
         </is>
       </c>
     </row>
@@ -19413,10 +19453,14 @@
       <c r="G27" s="24" t="inlineStr"/>
       <c r="H27" s="25" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I27" s="24" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
       <c r="J27" s="24" t="inlineStr">
         <is>
           <t>active / ended</t>
